--- a/PeerGrading/Input/form_exports/forms_responses.xlsx
+++ b/PeerGrading/Input/form_exports/forms_responses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzh-my.sharepoint.com/personal/renjie_cui_business_uzh_ch/Documents/PeerGrading/Input/form_exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="318" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3EAD73C-6D11-41A0-9508-F46B9360AE44}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CBD8D65-4695-4C34-92BB-16C2C2188FF8}"/>
   <bookViews>
     <workbookView xWindow="17280" yWindow="-16200" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7518" uniqueCount="1423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="1462">
   <si>
     <t>Responseid</t>
   </si>
@@ -4305,6 +4305,123 @@
   </si>
   <si>
     <t>2026-03-04T19:28:41.7544099Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:32:23.2161673Z</t>
+  </si>
+  <si>
+    <t>The information was well prepared and clearly presented.</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:32:23.2162078Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:34:10.7835417Z</t>
+  </si>
+  <si>
+    <t>The speaker showed good confidence while presenting.</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:34:10.7835848Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:35:18.4540848Z</t>
+  </si>
+  <si>
+    <t>Good balance between visuals and spoken explanation.</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:35:18.4541380Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:36:42.3827453Z</t>
+  </si>
+  <si>
+    <t>The presentation was interesting and engaging.</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:36:42.3828101Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:37:34.3910725Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:37:34.3911378Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:37:42.6974093Z</t>
+  </si>
+  <si>
+    <t>The presentation showed good preparation and effort.</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:37:42.6974503Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:38:55.0830185Z</t>
+  </si>
+  <si>
+    <t>The speaker communicated the ideas clearly and effectively.</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:38:55.0830703Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:39:43.5485937Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:39:43.5486326Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:40:29.1895567Z</t>
+  </si>
+  <si>
+    <t>The examples helped to understand the topic better.</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:40:29.1896101Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:41:12.7058905Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:41:12.7059302Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:41:43.6373925Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:41:43.6374339Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:41:49.2567103Z</t>
+  </si>
+  <si>
+    <t>Very technical presentation but the key points were explained clearly and effectively.</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:41:49.2567497Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:42:11.3387463Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:42:11.3387876Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:42:40.9457496Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:42:40.9457885Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:42:48.3346651Z</t>
+  </si>
+  <si>
+    <t>Well delivered and easy to follow.</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:42:48.3347398Z</t>
   </si>
 </sst>
 </file>
@@ -4408,8 +4525,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N617" totalsRowShown="0">
-  <autoFilter ref="A1:N617" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N632" totalsRowShown="0">
+  <autoFilter ref="A1:N632" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Responseid" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SubmittedAt"/>
@@ -4727,7 +4844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N617"/>
+  <dimension ref="A1:N632"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -31706,7 +31823,7 @@
       </c>
     </row>
     <row r="614" spans="1:14">
-      <c r="A614" s="5">
+      <c r="A614">
         <v>618</v>
       </c>
       <c r="B614" s="1" t="s">
@@ -31750,7 +31867,7 @@
       </c>
     </row>
     <row r="615" spans="1:14">
-      <c r="A615" s="5">
+      <c r="A615">
         <v>619</v>
       </c>
       <c r="B615" s="1" t="s">
@@ -31794,7 +31911,7 @@
       </c>
     </row>
     <row r="616" spans="1:14">
-      <c r="A616" s="5">
+      <c r="A616">
         <v>620</v>
       </c>
       <c r="B616" s="1" t="s">
@@ -31838,7 +31955,7 @@
       </c>
     </row>
     <row r="617" spans="1:14">
-      <c r="A617" s="5">
+      <c r="A617">
         <v>621</v>
       </c>
       <c r="B617" s="1" t="s">
@@ -31879,6 +31996,666 @@
       </c>
       <c r="N617" s="4" t="s">
         <v>1422</v>
+      </c>
+    </row>
+    <row r="618" spans="1:14">
+      <c r="A618" s="5">
+        <v>622</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C618" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D618" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E618" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F618" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G618" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H618" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I618" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J618" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K618" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L618" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M618" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="N618" s="4" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="619" spans="1:14">
+      <c r="A619" s="5">
+        <v>623</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C619" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D619" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E619" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F619" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G619" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H619" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I619" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J619" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K619" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L619" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M619" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="N619" s="4" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="620" spans="1:14">
+      <c r="A620" s="5">
+        <v>624</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C620" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D620" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E620" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F620" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G620" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H620" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I620" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J620" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K620" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L620" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M620" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="N620" s="4" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="621" spans="1:14">
+      <c r="A621" s="5">
+        <v>625</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C621" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D621" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E621" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F621" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G621" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H621" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I621" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J621" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K621" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L621" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M621" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="N621" s="4" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="622" spans="1:14">
+      <c r="A622" s="5">
+        <v>626</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C622" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D622" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E622" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F622" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G622" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H622" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I622" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J622" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K622" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L622" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M622" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N622" s="4" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="623" spans="1:14">
+      <c r="A623" s="5">
+        <v>627</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C623" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D623" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E623" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="F623" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G623" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H623" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I623" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J623" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K623" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L623" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M623" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="N623" s="4" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="624" spans="1:14">
+      <c r="A624" s="5">
+        <v>628</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C624" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D624" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E624" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="F624" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G624" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H624" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I624" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J624" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K624" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L624" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M624" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="N624" s="4" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="625" spans="1:14">
+      <c r="A625" s="5">
+        <v>629</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C625" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D625" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E625" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F625" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G625" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H625" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I625" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J625" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K625" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L625" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M625" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N625" s="4" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="626" spans="1:14">
+      <c r="A626" s="5">
+        <v>630</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C626" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D626" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E626" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F626" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G626" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H626" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I626" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J626" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K626" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L626" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M626" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="N626" s="4" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="627" spans="1:14">
+      <c r="A627" s="5">
+        <v>631</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C627" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D627" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E627" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F627" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G627" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H627" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I627" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J627" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K627" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L627" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M627" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N627" s="4" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="628" spans="1:14">
+      <c r="A628" s="5">
+        <v>632</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C628" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D628" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E628" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F628" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G628" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H628" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I628" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J628" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K628" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L628" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M628" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N628" s="4" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="629" spans="1:14">
+      <c r="A629" s="5">
+        <v>633</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C629" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D629" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E629" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F629" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G629" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H629" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I629" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J629" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K629" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L629" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M629" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="N629" s="4" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="630" spans="1:14">
+      <c r="A630" s="5">
+        <v>634</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C630" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D630" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E630" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="F630" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G630" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H630" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I630" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J630" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K630" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L630" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M630" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N630" s="4" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="631" spans="1:14">
+      <c r="A631" s="5">
+        <v>635</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C631" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D631" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E631" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F631" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G631" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H631" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I631" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J631" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K631" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L631" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M631" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N631" s="4" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="632" spans="1:14">
+      <c r="A632" s="5">
+        <v>636</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C632" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D632" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E632" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F632" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G632" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H632" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I632" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J632" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K632" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L632" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M632" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="N632" s="4" t="s">
+        <v>1461</v>
       </c>
     </row>
   </sheetData>

--- a/PeerGrading/Input/form_exports/forms_responses.xlsx
+++ b/PeerGrading/Input/form_exports/forms_responses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzh-my.sharepoint.com/personal/renjie_cui_business_uzh_ch/Documents/PeerGrading/Input/form_exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CBD8D65-4695-4C34-92BB-16C2C2188FF8}"/>
+  <xr:revisionPtr revIDLastSave="335" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{542380F8-6E33-415B-9FAD-32D7F529470C}"/>
   <bookViews>
     <workbookView xWindow="17280" yWindow="-16200" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7713" uniqueCount="1462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7739" uniqueCount="1466">
   <si>
     <t>Responseid</t>
   </si>
@@ -4422,6 +4422,18 @@
   </si>
   <si>
     <t>2026-03-06T13:42:48.3347398Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:44:22.3693009Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:44:22.3693530Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:49:18.7307023Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T13:49:18.7307458Z</t>
   </si>
 </sst>
 </file>
@@ -4525,8 +4537,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N632" totalsRowShown="0">
-  <autoFilter ref="A1:N632" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N634" totalsRowShown="0">
+  <autoFilter ref="A1:N634" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Responseid" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SubmittedAt"/>
@@ -4844,7 +4856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N632"/>
+  <dimension ref="A1:N634"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -32658,6 +32670,94 @@
         <v>1461</v>
       </c>
     </row>
+    <row r="633" spans="1:14">
+      <c r="A633" s="5">
+        <v>637</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C633" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D633" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E633" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F633" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G633" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H633" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I633" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J633" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K633" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L633" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M633" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N633" s="4" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="634" spans="1:14">
+      <c r="A634" s="5">
+        <v>638</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C634" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D634" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E634" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F634" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G634" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H634" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I634" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J634" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K634" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L634" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M634" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="N634" s="4" t="s">
+        <v>1465</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/PeerGrading/Input/form_exports/forms_responses.xlsx
+++ b/PeerGrading/Input/form_exports/forms_responses.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29910"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzh-my.sharepoint.com/personal/renjie_cui_business_uzh_ch/Documents/PeerGrading/Input/form_exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="335" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{542380F8-6E33-415B-9FAD-32D7F529470C}"/>
+  <xr:revisionPtr revIDLastSave="455" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C161927-4325-4A9D-84E4-F055601FD2F6}"/>
   <bookViews>
     <workbookView xWindow="17280" yWindow="-16200" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7739" uniqueCount="1466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9974" uniqueCount="1969">
   <si>
     <t>Responseid</t>
   </si>
@@ -4434,6 +4434,1515 @@
   </si>
   <si>
     <t>2026-03-06T13:49:18.7307458Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:16:32.7678430Z</t>
+  </si>
+  <si>
+    <t>Pascal	Suter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice illustrations </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:16:32.7678962Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:17:30.6651823Z</t>
+  </si>
+  <si>
+    <t>Really enjoyed your visuals and the presentation was very easy to follow. Appreciated the example using the Suez canal issue.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:17:30.6652311Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:17:52.3732795Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good Organized slides </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:17:52.3733196Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:18:07.2905752Z</t>
+  </si>
+  <si>
+    <t>I like how you adressed all the student questions and spent a decent amount of time on it.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:18:07.2906167Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:18:16.7592465Z</t>
+  </si>
+  <si>
+    <t>Very well explained, good pace</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:18:16.7593232Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:18:33.3395258Z</t>
+  </si>
+  <si>
+    <t>Nice visuals, nice that you included an example, concise answers to OLAT questions</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:18:33.3395732Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:01.8244631Z</t>
+  </si>
+  <si>
+    <t>good visuals on the slides, easy to follow! well done, i liked how you used an example to explain the topic</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:01.8245045Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:09.4949429Z</t>
+  </si>
+  <si>
+    <t>I really liked his intro and he presented very well with good visuals</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:09.4949965Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:11.7436396Z</t>
+  </si>
+  <si>
+    <t>A small introduction would have been nice, otherwise very good</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:11.7436807Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:12.0785807Z</t>
+  </si>
+  <si>
+    <t>Good slide and presented well</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:12.0786241Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:12.9360153Z</t>
+  </si>
+  <si>
+    <t>nice visuals, easy to follow</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:12.9360580Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:13.3405614Z</t>
+  </si>
+  <si>
+    <t>good use of practical examples and good job showing how transportation mode affects emissions, costs and delivery speed</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:13.3406368Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:15.6953860Z</t>
+  </si>
+  <si>
+    <t>cool slides</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:15.6954255Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:16.6298183Z</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:16.6298607Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:17.5526553Z</t>
+  </si>
+  <si>
+    <t>great presentation, good speed</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:17.5526977Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:18.3233950Z</t>
+  </si>
+  <si>
+    <t>Very good visuals on the presentation!</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:18.3234344Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:18.5608097Z</t>
+  </si>
+  <si>
+    <t>topic was explained quite well and questions on the forum were adressed accordingly</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:18.5608519Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:18.5792432Z</t>
+  </si>
+  <si>
+    <t>Very nice looking presentation, well spoken, had a bit the disatvantage that we looked at the same topic during class</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:18.5792827Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:19.1022110Z</t>
+  </si>
+  <si>
+    <t>efficient</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:19.1022542Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:19.4781192Z</t>
+  </si>
+  <si>
+    <t>Great presentation with good slides.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:19.4781615Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:20.9727466Z</t>
+  </si>
+  <si>
+    <t>very nice slides with animation (e.g., sold out Schild), OLAT questions were addressed appropriately, nice presenting style (very calm and composed)</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:20.9727855Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:21.1517249Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very clear presentation. You spoke little too fast though. </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:21.1517627Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:21.2740044Z</t>
+  </si>
+  <si>
+    <t>Very clean slides, good presentation style, freely spoken, questions answered</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:21.2740440Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:21.4932954Z</t>
+  </si>
+  <si>
+    <t>Very good presentation!</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:21.4933778Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:22.4630081Z</t>
+  </si>
+  <si>
+    <t>Easy to follow and clean powerpoint.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:22.4630561Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:25.9333135Z</t>
+  </si>
+  <si>
+    <t>Good examples but maybe speak more freely</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:25.9333519Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:26.4373177Z</t>
+  </si>
+  <si>
+    <t>great slides to explain concept and well presented</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:26.4373576Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:30.3522191Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">really good presentation! </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:30.3522584Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:34.9299024Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i liked the fact that while the visuals were easy to follow, he still provided a detailed presentation </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:34.9299415Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:34.8987906Z</t>
+  </si>
+  <si>
+    <t>Good one</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:34.8988444Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:39.4525597Z</t>
+  </si>
+  <si>
+    <t>good presentation, nice pictures, very nice slides, nice animations, answered questions very good</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:39.4526007Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:41.8308167Z</t>
+  </si>
+  <si>
+    <t>good presentation skills</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:41.8308558Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:45.8575731Z</t>
+  </si>
+  <si>
+    <t>massimiliano.nascioli@uzh.ch</t>
+  </si>
+  <si>
+    <t>Well presented and very fluent</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:45.8576272Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:48.2373566Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Examples well presented with good visuals, maybe too fast </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:19:48.2373958Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:20:01.1870181Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:20:01.1870567Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:20:05.8966767Z</t>
+  </si>
+  <si>
+    <t>Good eye contact, good timing</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:20:05.8967270Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:20:15.2454870Z</t>
+  </si>
+  <si>
+    <t>Really good presentation, I liked your slides. Pace was maybe just a bit too fast</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:20:15.2455319Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:20:33.1162863Z</t>
+  </si>
+  <si>
+    <t>Good!</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:20:33.1163282Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:21:21.9983885Z</t>
+  </si>
+  <si>
+    <t>Philip Alexander	Schnider</t>
+  </si>
+  <si>
+    <t>very interesting</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:21:21.9984288Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:21:54.6233492Z</t>
+  </si>
+  <si>
+    <t>Good presentation skill and clear slides, nothing to add</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:21:54.6233895Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:22:04.6997053Z</t>
+  </si>
+  <si>
+    <t>Slides are well done, would like more energy</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:22:04.6997555Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:22:49.5377689Z</t>
+  </si>
+  <si>
+    <t>Nice slides, good breakdown of a complicated topic, good use of real-life examples</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:22:49.5378117Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:23:14.5411987Z</t>
+  </si>
+  <si>
+    <t>Straight to the point, clear slides and good presentation with a small case study presentation. Very good!</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:23:14.5412411Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:05.4974091Z</t>
+  </si>
+  <si>
+    <t>Liked the presentation, but could be a bit more enthusiastic and speak more freely</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:05.4974479Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:06.6176898Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:06.6177659Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:06.8328556Z</t>
+  </si>
+  <si>
+    <t>nice structure, sensable slides, adressed questions</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:06.8329054Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:09.6706251Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:09.6707086Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:23.6608289Z</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:23.6608721Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:28.8230625Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:28.8231033Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:33.9609153Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows interesting statistics and answer Great questions </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:33.9609559Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:39.8878382Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:24:39.8878903Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:02.4039940Z</t>
+  </si>
+  <si>
+    <t>Strong statistics that explains why last-mile logistics is such an important sustainability issue. Clear problem framing</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:02.4040367Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:06.1846234Z</t>
+  </si>
+  <si>
+    <t>Good structure going from figures to innovations to questions (maybe a bit too long)</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:06.1846743Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:25.8965754Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good visuals on the slides, a lot of strong statistics which made it interesting to listen to! </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:25.8966134Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:28.5725091Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nice presentation, the text could be bigger so it is more readable </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:28.5725500Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:29.3744611Z</t>
+  </si>
+  <si>
+    <t>great composure while the presentation wasn't showing up on screen properly. Very calm and collected</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:29.3745051Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:32.4336900Z</t>
+  </si>
+  <si>
+    <t>calmly presented, good explained, freely spoken, slides a little bit full</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:32.4337296Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:34.5829969Z</t>
+  </si>
+  <si>
+    <t>The presentation looked like a SAP requests. it hat some technical issues wich were in no means his fault. Very clear and well spoken. interesting topic</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:34.5830361Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:35.5166247Z</t>
+  </si>
+  <si>
+    <t>Very interesting.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:35.5166955Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:38.0045334Z</t>
+  </si>
+  <si>
+    <t>great presentation, easy to follow</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:38.0045796Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:38.0353845Z</t>
+  </si>
+  <si>
+    <t>Very clean slides, confident talking</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:38.0354262Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:38.2546468Z</t>
+  </si>
+  <si>
+    <t>Good way of presenting the slides (questions and answers), maybe the texts are too small</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:38.2548980Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:38.7179354Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Well done! </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:38.7179761Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:39.7655095Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nice that you included actual evidence, good presentation style, presentation structured very well, questions nicely addressed </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:39.7655475Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:39.8226051Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good, clear powerpoint that is easy to follow. </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:39.8226470Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:40.2447492Z</t>
+  </si>
+  <si>
+    <t>nice slides, easy to follow</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:40.2448282Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:40.5580687Z</t>
+  </si>
+  <si>
+    <t>not timed so well, but interesting presentation</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:40.5581091Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:42.0414775Z</t>
+  </si>
+  <si>
+    <t>A bit too long but I really enjoyed it !</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:42.0415169Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:44.1639602Z</t>
+  </si>
+  <si>
+    <t>Good presentation unfortunately not so good time managed</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:44.1640015Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:47.8076207Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:47.8076604Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:48.7919294Z</t>
+  </si>
+  <si>
+    <t>Very good looking presentation and did a great job explaining the problem</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:48.7919686Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:50.4460457Z</t>
+  </si>
+  <si>
+    <t>I learned about how the effect of e-commerce has really changed logistics. I liked the OLAT question answers. Very interesting. Considering the presenting issues was well presented.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:50.4460845Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:50.5517049Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:50.5517471Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:53.6198944Z</t>
+  </si>
+  <si>
+    <t>very good presentation</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:25:53.6199480Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:00.6120762Z</t>
+  </si>
+  <si>
+    <t>Not completely freely speaking but overall great presentation</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:00.6121168Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:03.8428106Z</t>
+  </si>
+  <si>
+    <t>You spokenvery naturally and calmly, the pace was also good!</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:03.8428877Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:08.2484462Z</t>
+  </si>
+  <si>
+    <t>i would make the writings on the presentation slightly bigger</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:08.2484888Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:08.7313075Z</t>
+  </si>
+  <si>
+    <t>Easy to follow</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:08.7313631Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:23.5007953Z</t>
+  </si>
+  <si>
+    <t>good example</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:23.5008347Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:34.3419148Z</t>
+  </si>
+  <si>
+    <t>Oberato vero good but might be more concise</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:34.3419638Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:36.4395515Z</t>
+  </si>
+  <si>
+    <t>great visuals and invclsuion of the olat questions</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:26:36.4396049Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:27:26.0583762Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">great vivid presentation and very informative </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:27:26.0584258Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:28:11.8559715Z</t>
+  </si>
+  <si>
+    <t>Dylan	Ashraf</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:28:11.8560155Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:21.5832324Z</t>
+  </si>
+  <si>
+    <t>advantages and disadvantages of intermodal transport well explained, good examples in addition, text on slides might have been a bit bigger</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:21.5832745Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:23.7939556Z</t>
+  </si>
+  <si>
+    <t>Good clear voice and pacing throughout the presentation. Could tell you practiced a couple of times.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:23.7939943Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:26.8495639Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great breakdown of a complicated topic, easy to understand graphics, nice real-life examples </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:26.8496036Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:40.2640439Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nice presentation and examples (success stories), questions nicely addressed </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:40.2641208Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:45.5929801Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good infographics on the slides, nice pacing when presenting. </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:45.5930477Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:47.7868751Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great explanation of the topic </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:29:47.7869147Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:22.8656934Z</t>
+  </si>
+  <si>
+    <t>easy to understand, nice structure</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:22.8657498Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:23.9036397Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:23.9036908Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:24.0141944Z</t>
+  </si>
+  <si>
+    <t>Excellent , easy to follow and straight to the point.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:24.0142424Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:26.9593323Z</t>
+  </si>
+  <si>
+    <t>Interesting presentation with good presentation!</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:26.9593721Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:27.3463267Z</t>
+  </si>
+  <si>
+    <t>nice English, freely spoken, good slides, very calm presented</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:27.3463662Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:27.7199456Z</t>
+  </si>
+  <si>
+    <t>I really liked the structure of his presentation and how he discussed the issues and successes</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:27.7199850Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:29.0999449Z</t>
+  </si>
+  <si>
+    <t>The presenter was very confident and direct.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:29.1000110Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:29.3497970Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:29.3498479Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:29.4331563Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:29.4331968Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:29.7310886Z</t>
+  </si>
+  <si>
+    <t>Texts maybe too small, a bit difficult to follow, interesting examples</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:29.7311304Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:30.3555197Z</t>
+  </si>
+  <si>
+    <t>quite small writig on the presentations. Well and clear spoken. Challenges in this topic were explained good with good examples.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:30.3555704Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:31.8196180Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was interesting with the success stories. </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:31.8196558Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:31.9008908Z</t>
+  </si>
+  <si>
+    <t>Thank you for this great presentation !</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:31.9009303Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:35.4182362Z</t>
+  </si>
+  <si>
+    <t>Good Presentiation</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:35.4183130Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:38.3124168Z</t>
+  </si>
+  <si>
+    <t>text a bit too small, however, good presentation overall</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:38.3124607Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:38.3595036Z</t>
+  </si>
+  <si>
+    <t>clear explanation of the problem and good explanation of intermodal transport</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:38.3595647Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:38.4108014Z</t>
+  </si>
+  <si>
+    <t>Well spoken nice visuals</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:38.4108813Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:39.2903116Z</t>
+  </si>
+  <si>
+    <t>I liked the slides as they were not full with pictures and text, therefore it was easy to follow, you spoke very confidently</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:39.2903543Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:41.1048387Z</t>
+  </si>
+  <si>
+    <t>great visuals</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:41.1048803Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:41.6105198Z</t>
+  </si>
+  <si>
+    <t>nice presentation style, text could have been bigger</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:41.6105608Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:41.7336868Z</t>
+  </si>
+  <si>
+    <t>great and calm style of speaking</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:41.7337276Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:42.2919397Z</t>
+  </si>
+  <si>
+    <t>good presentation style</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:42.2919827Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:43.0045107Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:43.0045525Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:43.7647850Z</t>
+  </si>
+  <si>
+    <t>Appreciated the fact you covered the issues because it shows how even good solutions can be hard to organize. Also I appreciated the examples of strong implementation.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:43.7648397Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:44.0251458Z</t>
+  </si>
+  <si>
+    <t>sentences could be bigger. but overall its a great presentation</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:44.0252104Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:47.2692903Z</t>
+  </si>
+  <si>
+    <t>Calmly talked, very confident speaking</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:47.2693427Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:49.8288873Z</t>
+  </si>
+  <si>
+    <t>Easy to follow, clearly spoken</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:49.8289296Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:56.6800017Z</t>
+  </si>
+  <si>
+    <t>Good in general</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:56.6800396Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:57.6800580Z</t>
+  </si>
+  <si>
+    <t>Amazing presentation, easy to follow, great flow and structure.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:57.6800978Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:58.6241041Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:30:58.6241997Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:12.8930935Z</t>
+  </si>
+  <si>
+    <t>everything was covered and was quite clear</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:12.8931341Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:21.6083755Z</t>
+  </si>
+  <si>
+    <t>Sophie Jennifer	Sharp</t>
+  </si>
+  <si>
+    <t>perfect</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:21.6084151Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:29.3218350Z</t>
+  </si>
+  <si>
+    <t>Great presentation, very clear and easy to follow</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:29.3218903Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:35.3025692Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:35.3026087Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:37.6578421Z</t>
+  </si>
+  <si>
+    <t>Very well done!</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:37.6578822Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:47.3866753Z</t>
+  </si>
+  <si>
+    <t>I like how you categoirized the Olat questions into sub topics, was easy to follow and showed you did your research</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:47.3867307Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:49.7568675Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great introduction into the topic </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:49.7569164Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:52.5857271Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clear explanation and clear slides </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:31:52.5857700Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:32:10.0813590Z</t>
+  </si>
+  <si>
+    <t>good presenation style</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:32:10.0813981Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:32:27.0962633Z</t>
+  </si>
+  <si>
+    <t>Should the US be engaging in the Iraninan war?</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:32:27.0963109Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:32:47.8590080Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:32:47.8590488Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:32:53.2628162Z</t>
+  </si>
+  <si>
+    <t>Good presentation, nice structure. Nothing to add</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:32:53.2628657Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:33:27.7888506Z</t>
+  </si>
+  <si>
+    <t>I appreciated your clustering of the OLAT questions. Helped provide an overview of information relevant to the topic as a whole. I like your examples of the cities because it provides clear examples of implementation.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:33:27.7888899Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:33:32.2545946Z</t>
+  </si>
+  <si>
+    <t>nice that you showed leading examples, nice visuals</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:33:32.2546355Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:04.0384103Z</t>
+  </si>
+  <si>
+    <t>Great idea with clustering the questions!</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:04.0384870Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:04.6390293Z</t>
+  </si>
+  <si>
+    <t>Heavy slides, otherwise very good</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:04.6390729Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:07.3938045Z</t>
+  </si>
+  <si>
+    <t>good structure, slides are a bit text heavy</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:07.3938437Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:07.4624738Z</t>
+  </si>
+  <si>
+    <t>clear explanation and implementation of olat questions. Intersting topic, slides a bit loaded at times</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:07.4625146Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:07.5979222Z</t>
+  </si>
+  <si>
+    <t>Loved insights into impacts to business</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:07.5979623Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:08.0658430Z</t>
+  </si>
+  <si>
+    <t>Very good presentation, maybe interract more with the PPT and tighten its content</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:08.0659010Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:08.8061823Z</t>
+  </si>
+  <si>
+    <t>freely spoken, everything good explained, very good English, slides are a little bit full, good examples</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:08.8062694Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:09.0677733Z</t>
+  </si>
+  <si>
+    <t>Great presentation but too much text on slides.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:09.0678214Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:09.6375780Z</t>
+  </si>
+  <si>
+    <t>clear speaking style and and a nice real life example.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:09.6376547Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:09.8400494Z</t>
+  </si>
+  <si>
+    <t>Good job</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:09.8400885Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:10.2714712Z</t>
+  </si>
+  <si>
+    <t>Well done and clear slides</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:10.2715109Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:10.7379350Z</t>
+  </si>
+  <si>
+    <t>Very well done presenation, I really liked her slides as well as the content. Well done!</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:10.7379774Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:12.3015769Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very good, a lot of interesting information. It was a little bit hard to read the text, because it was a bit to small at some slides. </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:12.3016282Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:12.7634509Z</t>
+  </si>
+  <si>
+    <t>Very well and clearly spoken, not nervous at all. Nice to listen to and good real life examples used. But the presentation was impossible to read</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:12.7635263Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:14.8301986Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:14.8302394Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:16.5212220Z</t>
+  </si>
+  <si>
+    <t>nice designed slides</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:16.5212621Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:18.9045320Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nice presentation, too much text on the slides and a lot of reading from the slides from the presenter </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:18.9045754Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:19.0334243Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The presentation was good but you read too much your Power Point. </t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:19.0334772Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:20.8584727Z</t>
+  </si>
+  <si>
+    <t>More free speaking, else confident and calm presenting</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:20.8585268Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:21.2100470Z</t>
+  </si>
+  <si>
+    <t>Well spoken, but read less from the slides and look in the audience more</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:21.2100882Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:21.9575673Z</t>
+  </si>
+  <si>
+    <t>confident presentation style</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:21.9576215Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:23.8762235Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:23.8762745Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:25.8745960Z</t>
+  </si>
+  <si>
+    <t>Easy to follow, good topic</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:25.8746660Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:26.7009433Z</t>
+  </si>
+  <si>
+    <t>I liked how you divided the questions into themes and your presentation style was really good</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:26.7009852Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:27.8115525Z</t>
+  </si>
+  <si>
+    <t>You spoke very calmly and confidently, so it was easy to follow, you could do a little bit more eye contact, but great presentation</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:27.8115947Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:36.1445269Z</t>
+  </si>
+  <si>
+    <t>I would've written a little bit less in every slide, but overall it's a great presentation.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:36.1445809Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:48.7624236Z</t>
+  </si>
+  <si>
+    <t>good presentation, slides a bit too cluttered and too much text =&gt; hard to read. Otherwise good.</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:48.7624674Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:49.8109298Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:49.8109821Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:52.2281606Z</t>
+  </si>
+  <si>
+    <t>Too much texts and maybe too small, i like how she divided Information in categories</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:34:52.2282086Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:35:05.6533916Z</t>
+  </si>
+  <si>
+    <t>Was a bit not focused, i suppose</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:35:05.6534564Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:35:18.1172824Z</t>
+  </si>
+  <si>
+    <t>Clear structure and using cities like Amsterdam, Zurich and Norway helped demonstrate how different regions are applying these policies in practice</t>
+  </si>
+  <si>
+    <t>2026-03-09T13:35:18.1173521Z</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:04:04.3551279Z</t>
+  </si>
+  <si>
+    <t>great presentation</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:04:04.3551930Z</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:04:28.7761310Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very nice </t>
+  </si>
+  <si>
+    <t>2026-03-10T13:04:28.7761746Z</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:04:52.4584318Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very well detailed </t>
+  </si>
+  <si>
+    <t>2026-03-10T13:04:52.4584727Z</t>
+  </si>
+  <si>
+    <t>2026-03-10T13:05:26.9348757Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">excellent presentation, good visuals </t>
+  </si>
+  <si>
+    <t>2026-03-10T13:05:26.9349163Z</t>
+  </si>
+  <si>
+    <t>2026-03-13T14:10:10.9205483Z</t>
+  </si>
+  <si>
+    <t>Very good presentation, it was both clear and well-paced.</t>
+  </si>
+  <si>
+    <t>2026-03-13T14:10:10.9205935Z</t>
+  </si>
+  <si>
+    <t>2026-03-13T14:14:58.7774735Z</t>
+  </si>
+  <si>
+    <t>Great presentation, clear and well-structured. The visuals were a little hard to keep up with due to the time constraints, but it remains a great presentation.</t>
+  </si>
+  <si>
+    <t>2026-03-13T14:14:58.7775399Z</t>
+  </si>
+  <si>
+    <t>2026-03-13T14:16:00.5675362Z</t>
+  </si>
+  <si>
+    <t>Very good presentation, with great examples that helped understanding.</t>
+  </si>
+  <si>
+    <t>2026-03-13T14:16:00.5675778Z</t>
+  </si>
+  <si>
+    <t>2026-03-13T14:18:50.1393895Z</t>
+  </si>
+  <si>
+    <t>Excellent presentation on an interesting topic with great visuals.</t>
+  </si>
+  <si>
+    <t>2026-03-13T14:18:50.1394683Z</t>
   </si>
 </sst>
 </file>
@@ -4537,8 +6046,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N634" totalsRowShown="0">
-  <autoFilter ref="A1:N634" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N806" totalsRowShown="0">
+  <autoFilter ref="A1:N806" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Responseid" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SubmittedAt"/>
@@ -4856,7 +6365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N634"/>
+  <dimension ref="A1:N806"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -32011,7 +33520,7 @@
       </c>
     </row>
     <row r="618" spans="1:14">
-      <c r="A618" s="5">
+      <c r="A618">
         <v>622</v>
       </c>
       <c r="B618" s="1" t="s">
@@ -32055,7 +33564,7 @@
       </c>
     </row>
     <row r="619" spans="1:14">
-      <c r="A619" s="5">
+      <c r="A619">
         <v>623</v>
       </c>
       <c r="B619" s="1" t="s">
@@ -32099,7 +33608,7 @@
       </c>
     </row>
     <row r="620" spans="1:14">
-      <c r="A620" s="5">
+      <c r="A620">
         <v>624</v>
       </c>
       <c r="B620" s="1" t="s">
@@ -32143,7 +33652,7 @@
       </c>
     </row>
     <row r="621" spans="1:14">
-      <c r="A621" s="5">
+      <c r="A621">
         <v>625</v>
       </c>
       <c r="B621" s="1" t="s">
@@ -32187,7 +33696,7 @@
       </c>
     </row>
     <row r="622" spans="1:14">
-      <c r="A622" s="5">
+      <c r="A622">
         <v>626</v>
       </c>
       <c r="B622" s="1" t="s">
@@ -32231,7 +33740,7 @@
       </c>
     </row>
     <row r="623" spans="1:14">
-      <c r="A623" s="5">
+      <c r="A623">
         <v>627</v>
       </c>
       <c r="B623" s="1" t="s">
@@ -32275,7 +33784,7 @@
       </c>
     </row>
     <row r="624" spans="1:14">
-      <c r="A624" s="5">
+      <c r="A624">
         <v>628</v>
       </c>
       <c r="B624" s="1" t="s">
@@ -32319,7 +33828,7 @@
       </c>
     </row>
     <row r="625" spans="1:14">
-      <c r="A625" s="5">
+      <c r="A625">
         <v>629</v>
       </c>
       <c r="B625" s="1" t="s">
@@ -32363,7 +33872,7 @@
       </c>
     </row>
     <row r="626" spans="1:14">
-      <c r="A626" s="5">
+      <c r="A626">
         <v>630</v>
       </c>
       <c r="B626" s="1" t="s">
@@ -32407,7 +33916,7 @@
       </c>
     </row>
     <row r="627" spans="1:14">
-      <c r="A627" s="5">
+      <c r="A627">
         <v>631</v>
       </c>
       <c r="B627" s="1" t="s">
@@ -32451,7 +33960,7 @@
       </c>
     </row>
     <row r="628" spans="1:14">
-      <c r="A628" s="5">
+      <c r="A628">
         <v>632</v>
       </c>
       <c r="B628" s="1" t="s">
@@ -32495,7 +34004,7 @@
       </c>
     </row>
     <row r="629" spans="1:14">
-      <c r="A629" s="5">
+      <c r="A629">
         <v>633</v>
       </c>
       <c r="B629" s="1" t="s">
@@ -32539,7 +34048,7 @@
       </c>
     </row>
     <row r="630" spans="1:14">
-      <c r="A630" s="5">
+      <c r="A630">
         <v>634</v>
       </c>
       <c r="B630" s="1" t="s">
@@ -32583,7 +34092,7 @@
       </c>
     </row>
     <row r="631" spans="1:14">
-      <c r="A631" s="5">
+      <c r="A631">
         <v>635</v>
       </c>
       <c r="B631" s="1" t="s">
@@ -32627,7 +34136,7 @@
       </c>
     </row>
     <row r="632" spans="1:14">
-      <c r="A632" s="5">
+      <c r="A632">
         <v>636</v>
       </c>
       <c r="B632" s="1" t="s">
@@ -32671,7 +34180,7 @@
       </c>
     </row>
     <row r="633" spans="1:14">
-      <c r="A633" s="5">
+      <c r="A633">
         <v>637</v>
       </c>
       <c r="B633" s="1" t="s">
@@ -32715,7 +34224,7 @@
       </c>
     </row>
     <row r="634" spans="1:14">
-      <c r="A634" s="5">
+      <c r="A634">
         <v>638</v>
       </c>
       <c r="B634" s="1" t="s">
@@ -32756,6 +34265,7572 @@
       </c>
       <c r="N634" s="4" t="s">
         <v>1465</v>
+      </c>
+    </row>
+    <row r="635" spans="1:14">
+      <c r="A635">
+        <v>639</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C635" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D635" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E635" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F635" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G635" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H635" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I635" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J635" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K635" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L635" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M635" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="N635" s="4" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="636" spans="1:14">
+      <c r="A636">
+        <v>640</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C636" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D636" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E636" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F636" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G636" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H636" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I636" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J636" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K636" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L636" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M636" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="N636" s="4" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="637" spans="1:14">
+      <c r="A637">
+        <v>641</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C637" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D637" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E637" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F637" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G637" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H637" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I637" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J637" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K637" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L637" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M637" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="N637" s="4" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="638" spans="1:14">
+      <c r="A638">
+        <v>642</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C638" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D638" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E638" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F638" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G638" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H638" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I638" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J638" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K638" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L638" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M638" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="N638" s="4" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="639" spans="1:14">
+      <c r="A639">
+        <v>643</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C639" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D639" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E639" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F639" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G639" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H639" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I639" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J639" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K639" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L639" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M639" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="N639" s="4" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="640" spans="1:14">
+      <c r="A640">
+        <v>644</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C640" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D640" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E640" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F640" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G640" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H640" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I640" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J640" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K640" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L640" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M640" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="N640" s="4" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="641" spans="1:14">
+      <c r="A641">
+        <v>645</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C641" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D641" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E641" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F641" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G641" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H641" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I641" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J641" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K641" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L641" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M641" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="N641" s="4" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="642" spans="1:14">
+      <c r="A642">
+        <v>646</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C642" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D642" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E642" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F642" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G642" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H642" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I642" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J642" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K642" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L642" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M642" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="N642" s="4" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="643" spans="1:14">
+      <c r="A643">
+        <v>647</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C643" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D643" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E643" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F643" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G643" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H643" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I643" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J643" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K643" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L643" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M643" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="N643" s="4" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="644" spans="1:14">
+      <c r="A644">
+        <v>648</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C644" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D644" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E644" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F644" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G644" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H644" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I644" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J644" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K644" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L644" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M644" s="3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="N644" s="4" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="645" spans="1:14">
+      <c r="A645">
+        <v>649</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C645" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D645" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E645" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F645" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G645" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H645" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I645" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J645" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K645" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L645" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M645" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="N645" s="4" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="646" spans="1:14">
+      <c r="A646">
+        <v>650</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C646" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D646" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E646" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F646" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G646" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H646" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I646" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J646" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K646" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L646" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M646" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="N646" s="4" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="647" spans="1:14">
+      <c r="A647">
+        <v>651</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C647" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D647" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E647" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F647" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G647" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H647" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I647" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J647" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K647" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L647" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M647" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="N647" s="4" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="648" spans="1:14">
+      <c r="A648">
+        <v>652</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C648" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D648" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E648" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F648" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G648" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H648" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I648" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J648" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K648" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L648" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M648" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N648" s="4" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="649" spans="1:14">
+      <c r="A649">
+        <v>653</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C649" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D649" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E649" s="2"/>
+      <c r="F649" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G649" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H649" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I649" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J649" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K649" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L649" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M649" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="N649" s="4" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="650" spans="1:14">
+      <c r="A650">
+        <v>654</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C650" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D650" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E650" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F650" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G650" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H650" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I650" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J650" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K650" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L650" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M650" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="N650" s="4" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="651" spans="1:14">
+      <c r="A651">
+        <v>656</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C651" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D651" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E651" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F651" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G651" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H651" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I651" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J651" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K651" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L651" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M651" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="N651" s="4" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="652" spans="1:14">
+      <c r="A652">
+        <v>655</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C652" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D652" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E652" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F652" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G652" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H652" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I652" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J652" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K652" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L652" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M652" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="N652" s="4" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="653" spans="1:14">
+      <c r="A653">
+        <v>657</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C653" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D653" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E653" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F653" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G653" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H653" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I653" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J653" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K653" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L653" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M653" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="N653" s="4" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="654" spans="1:14">
+      <c r="A654">
+        <v>658</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C654" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D654" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E654" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F654" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G654" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H654" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I654" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J654" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K654" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L654" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M654" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="N654" s="4" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="655" spans="1:14">
+      <c r="A655">
+        <v>659</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C655" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D655" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E655" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F655" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G655" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H655" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I655" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J655" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K655" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L655" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M655" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="N655" s="4" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="656" spans="1:14">
+      <c r="A656">
+        <v>661</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C656" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D656" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E656" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F656" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G656" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H656" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I656" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J656" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K656" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L656" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M656" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="N656" s="4" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="657" spans="1:14">
+      <c r="A657">
+        <v>660</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C657" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D657" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E657" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F657" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G657" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H657" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I657" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J657" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K657" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L657" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M657" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="N657" s="4" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="658" spans="1:14">
+      <c r="A658">
+        <v>662</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C658" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D658" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E658" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F658" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G658" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H658" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I658" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J658" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K658" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L658" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M658" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="N658" s="4" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="659" spans="1:14">
+      <c r="A659">
+        <v>663</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C659" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D659" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E659" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F659" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G659" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H659" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I659" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J659" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K659" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L659" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M659" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="N659" s="4" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="660" spans="1:14">
+      <c r="A660">
+        <v>664</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C660" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D660" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E660" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F660" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G660" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H660" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I660" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J660" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K660" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L660" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M660" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="N660" s="4" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="661" spans="1:14">
+      <c r="A661">
+        <v>665</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C661" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D661" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E661" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F661" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G661" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H661" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I661" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J661" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K661" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L661" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M661" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="N661" s="4" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="662" spans="1:14">
+      <c r="A662">
+        <v>666</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C662" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D662" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E662" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F662" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G662" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H662" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I662" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J662" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K662" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L662" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M662" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="N662" s="4" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="663" spans="1:14">
+      <c r="A663">
+        <v>668</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C663" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D663" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E663" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F663" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G663" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H663" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I663" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J663" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K663" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L663" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M663" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="N663" s="4" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="664" spans="1:14">
+      <c r="A664">
+        <v>667</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C664" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D664" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E664" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F664" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G664" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H664" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I664" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J664" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K664" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L664" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M664" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="N664" s="4" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="665" spans="1:14">
+      <c r="A665">
+        <v>669</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C665" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D665" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E665" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F665" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G665" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H665" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I665" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J665" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K665" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L665" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M665" s="3" t="s">
+        <v>1558</v>
+      </c>
+      <c r="N665" s="4" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="666" spans="1:14">
+      <c r="A666">
+        <v>670</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C666" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D666" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E666" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F666" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G666" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H666" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I666" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J666" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K666" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L666" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M666" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="N666" s="4" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="667" spans="1:14">
+      <c r="A667">
+        <v>671</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C667" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D667" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E667" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F667" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G667" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H667" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I667" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J667" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K667" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L667" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M667" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="N667" s="4" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="668" spans="1:14">
+      <c r="A668">
+        <v>672</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C668" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D668" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E668" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F668" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G668" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H668" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I668" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J668" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K668" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L668" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M668" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N668" s="4" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="669" spans="1:14">
+      <c r="A669">
+        <v>673</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C669" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D669" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E669" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F669" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G669" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H669" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I669" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J669" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K669" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L669" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M669" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N669" s="4" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="670" spans="1:14">
+      <c r="A670">
+        <v>674</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C670" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D670" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E670" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F670" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G670" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H670" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I670" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J670" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K670" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L670" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M670" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="N670" s="4" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="671" spans="1:14">
+      <c r="A671">
+        <v>675</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C671" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D671" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E671" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F671" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G671" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H671" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I671" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J671" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K671" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L671" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M671" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="N671" s="4" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="672" spans="1:14">
+      <c r="A672">
+        <v>676</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C672" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D672" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E672" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F672" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G672" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H672" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I672" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J672" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K672" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L672" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M672" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="N672" s="4" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="673" spans="1:14">
+      <c r="A673">
+        <v>677</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C673" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D673" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E673" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F673" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G673" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H673" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I673" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J673" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K673" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L673" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M673" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="N673" s="4" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="674" spans="1:14">
+      <c r="A674">
+        <v>678</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C674" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D674" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E674" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F674" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G674" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H674" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I674" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J674" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K674" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L674" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M674" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="N674" s="4" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="675" spans="1:14">
+      <c r="A675">
+        <v>679</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C675" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D675" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E675" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F675" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G675" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H675" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I675" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J675" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K675" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L675" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M675" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="N675" s="4" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="676" spans="1:14">
+      <c r="A676">
+        <v>680</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C676" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D676" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E676" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F676" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G676" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H676" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I676" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J676" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K676" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L676" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M676" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="N676" s="4" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="677" spans="1:14">
+      <c r="A677">
+        <v>681</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C677" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D677" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E677" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F677" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G677" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H677" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I677" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J677" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K677" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L677" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M677" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="N677" s="4" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="678" spans="1:14">
+      <c r="A678">
+        <v>682</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C678" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D678" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E678" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F678" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G678" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H678" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I678" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J678" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K678" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L678" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M678" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="N678" s="4" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="679" spans="1:14">
+      <c r="A679">
+        <v>683</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C679" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D679" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E679" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F679" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G679" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H679" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I679" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J679" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K679" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L679" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M679" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N679" s="4" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="680" spans="1:14">
+      <c r="A680">
+        <v>684</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C680" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D680" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E680" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F680" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G680" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H680" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I680" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J680" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K680" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L680" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M680" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="N680" s="4" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="681" spans="1:14">
+      <c r="A681">
+        <v>685</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C681" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D681" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E681" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F681" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G681" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H681" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I681" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J681" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K681" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L681" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M681" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N681" s="4" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="682" spans="1:14">
+      <c r="A682">
+        <v>686</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C682" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D682" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E682" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F682" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G682" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H682" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I682" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J682" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K682" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L682" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M682" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="N682" s="4" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="683" spans="1:14">
+      <c r="A683">
+        <v>687</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C683" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D683" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E683" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F683" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G683" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H683" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I683" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J683" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K683" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L683" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M683" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="N683" s="4" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="684" spans="1:14">
+      <c r="A684">
+        <v>688</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C684" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D684" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E684" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F684" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G684" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H684" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I684" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J684" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K684" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L684" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M684" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="N684" s="4" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="685" spans="1:14">
+      <c r="A685">
+        <v>689</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C685" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D685" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E685" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F685" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H685" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I685" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J685" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K685" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L685" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M685" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="N685" s="4" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="686" spans="1:14">
+      <c r="A686">
+        <v>690</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C686" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D686" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E686" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F686" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G686" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H686" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I686" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J686" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K686" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L686" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M686" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="N686" s="4" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="687" spans="1:14">
+      <c r="A687">
+        <v>691</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C687" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D687" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E687" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F687" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G687" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H687" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I687" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J687" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K687" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L687" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M687" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="N687" s="4" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="688" spans="1:14">
+      <c r="A688">
+        <v>692</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C688" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D688" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E688" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F688" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G688" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H688" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I688" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J688" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K688" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L688" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M688" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="N688" s="4" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="689" spans="1:14">
+      <c r="A689">
+        <v>693</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C689" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D689" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E689" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F689" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G689" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H689" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I689" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J689" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K689" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L689" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M689" s="3" t="s">
+        <v>1627</v>
+      </c>
+      <c r="N689" s="4" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="690" spans="1:14">
+      <c r="A690">
+        <v>694</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C690" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D690" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E690" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F690" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G690" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H690" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I690" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J690" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K690" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L690" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M690" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="N690" s="4" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="691" spans="1:14">
+      <c r="A691">
+        <v>695</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C691" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D691" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E691" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F691" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G691" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H691" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I691" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J691" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K691" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L691" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M691" s="3" t="s">
+        <v>1633</v>
+      </c>
+      <c r="N691" s="4" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="692" spans="1:14">
+      <c r="A692">
+        <v>696</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C692" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D692" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E692" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F692" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G692" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H692" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I692" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J692" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K692" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L692" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M692" s="3" t="s">
+        <v>1636</v>
+      </c>
+      <c r="N692" s="4" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="693" spans="1:14">
+      <c r="A693">
+        <v>697</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C693" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D693" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E693" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F693" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G693" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H693" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I693" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J693" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K693" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L693" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M693" s="3" t="s">
+        <v>1639</v>
+      </c>
+      <c r="N693" s="4" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="694" spans="1:14">
+      <c r="A694">
+        <v>698</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C694" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D694" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E694" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F694" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G694" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H694" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I694" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J694" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K694" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L694" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M694" s="3" t="s">
+        <v>1642</v>
+      </c>
+      <c r="N694" s="4" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="695" spans="1:14">
+      <c r="A695">
+        <v>700</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C695" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D695" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E695" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F695" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G695" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H695" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I695" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J695" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K695" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L695" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M695" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="N695" s="4" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="696" spans="1:14">
+      <c r="A696">
+        <v>699</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C696" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D696" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E696" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F696" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G696" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H696" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I696" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J696" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K696" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L696" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M696" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="N696" s="4" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="697" spans="1:14">
+      <c r="A697">
+        <v>701</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C697" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D697" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E697" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F697" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G697" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H697" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I697" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J697" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K697" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L697" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M697" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="N697" s="4" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="698" spans="1:14">
+      <c r="A698">
+        <v>703</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C698" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D698" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E698" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F698" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G698" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H698" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I698" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J698" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K698" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L698" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M698" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="N698" s="4" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="699" spans="1:14">
+      <c r="A699">
+        <v>702</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C699" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D699" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E699" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F699" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G699" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H699" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I699" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J699" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K699" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L699" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M699" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N699" s="4" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="700" spans="1:14">
+      <c r="A700">
+        <v>704</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C700" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D700" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E700" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F700" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G700" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H700" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I700" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J700" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K700" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L700" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M700" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="N700" s="4" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="701" spans="1:14">
+      <c r="A701">
+        <v>705</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C701" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D701" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E701" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F701" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G701" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H701" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I701" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J701" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K701" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L701" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M701" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="N701" s="4" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="702" spans="1:14">
+      <c r="A702">
+        <v>706</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C702" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D702" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E702" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F702" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G702" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H702" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I702" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J702" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K702" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L702" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M702" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N702" s="4" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="703" spans="1:14">
+      <c r="A703">
+        <v>707</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C703" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D703" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E703" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F703" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G703" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H703" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I703" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J703" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K703" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L703" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M703" s="3" t="s">
+        <v>1669</v>
+      </c>
+      <c r="N703" s="4" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="704" spans="1:14">
+      <c r="A704">
+        <v>708</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C704" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D704" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E704" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F704" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G704" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H704" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I704" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J704" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K704" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L704" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M704" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N704" s="4" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="705" spans="1:14">
+      <c r="A705">
+        <v>709</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C705" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D705" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E705" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F705" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G705" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H705" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I705" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J705" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K705" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L705" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M705" s="3" t="s">
+        <v>1674</v>
+      </c>
+      <c r="N705" s="4" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="706" spans="1:14">
+      <c r="A706">
+        <v>711</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C706" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D706" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E706" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F706" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G706" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H706" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I706" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J706" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K706" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L706" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M706" s="3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="N706" s="4" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="707" spans="1:14">
+      <c r="A707">
+        <v>710</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C707" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D707" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E707" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F707" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G707" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H707" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I707" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J707" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K707" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L707" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M707" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N707" s="4" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="708" spans="1:14">
+      <c r="A708">
+        <v>712</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C708" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D708" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E708" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F708" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G708" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H708" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I708" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J708" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K708" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L708" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M708" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="N708" s="4" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="709" spans="1:14">
+      <c r="A709">
+        <v>713</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C709" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D709" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E709" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F709" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G709" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H709" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I709" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J709" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K709" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L709" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M709" s="3" t="s">
+        <v>1685</v>
+      </c>
+      <c r="N709" s="4" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="710" spans="1:14">
+      <c r="A710">
+        <v>714</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C710" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D710" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E710" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F710" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G710" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H710" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I710" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J710" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K710" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L710" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M710" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="N710" s="4" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="711" spans="1:14">
+      <c r="A711">
+        <v>715</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C711" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D711" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E711" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F711" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G711" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H711" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I711" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J711" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K711" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L711" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M711" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="N711" s="4" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="712" spans="1:14">
+      <c r="A712">
+        <v>716</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C712" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D712" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E712" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M712" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="N712" s="4" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="713" spans="1:14">
+      <c r="A713">
+        <v>717</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C713" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D713" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E713" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G713" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K713" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M713" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="N713" s="4" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="714" spans="1:14">
+      <c r="A714">
+        <v>718</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C714" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D714" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E714" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F714" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I714" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J714" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K714" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L714" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M714" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N714" s="4" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="715" spans="1:14">
+      <c r="A715">
+        <v>719</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C715" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D715" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E715" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F715" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G715" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H715" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I715" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J715" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K715" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L715" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M715" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="N715" s="4" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="716" spans="1:14">
+      <c r="A716">
+        <v>720</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C716" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D716" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E716" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M716" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="N716" s="4" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="717" spans="1:14">
+      <c r="A717">
+        <v>721</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C717" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D717" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E717" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M717" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="N717" s="4" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="718" spans="1:14">
+      <c r="A718">
+        <v>722</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C718" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D718" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E718" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M718" s="3" t="s">
+        <v>1712</v>
+      </c>
+      <c r="N718" s="4" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="719" spans="1:14">
+      <c r="A719">
+        <v>723</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C719" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D719" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E719" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M719" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="N719" s="4" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="720" spans="1:14">
+      <c r="A720">
+        <v>724</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C720" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D720" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E720" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F720" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G720" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H720" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I720" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J720" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K720" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L720" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M720" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="N720" s="4" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="721" spans="1:14">
+      <c r="A721">
+        <v>725</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C721" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D721" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E721" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M721" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="N721" s="4" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="722" spans="1:14">
+      <c r="A722">
+        <v>726</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C722" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D722" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E722" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M722" s="3" t="s">
+        <v>1724</v>
+      </c>
+      <c r="N722" s="4" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="723" spans="1:14">
+      <c r="A723">
+        <v>727</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C723" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D723" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E723" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M723" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="N723" s="4" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="724" spans="1:14">
+      <c r="A724">
+        <v>728</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C724" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D724" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E724" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M724" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="N724" s="4" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="725" spans="1:14">
+      <c r="A725">
+        <v>729</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C725" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D725" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E725" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M725" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="N725" s="4" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="726" spans="1:14">
+      <c r="A726">
+        <v>730</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C726" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D726" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E726" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K726" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M726" s="3" t="s">
+        <v>1735</v>
+      </c>
+      <c r="N726" s="4" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="727" spans="1:14">
+      <c r="A727">
+        <v>731</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C727" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D727" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E727" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F727" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G727" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H727" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I727" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J727" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K727" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L727" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M727" s="3" t="s">
+        <v>1738</v>
+      </c>
+      <c r="N727" s="4" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="728" spans="1:14">
+      <c r="A728">
+        <v>732</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C728" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D728" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E728" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M728" s="3" t="s">
+        <v>1741</v>
+      </c>
+      <c r="N728" s="4" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="729" spans="1:14">
+      <c r="A729">
+        <v>733</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C729" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D729" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E729" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M729" s="3" t="s">
+        <v>1744</v>
+      </c>
+      <c r="N729" s="4" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="730" spans="1:14">
+      <c r="A730">
+        <v>735</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C730" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D730" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E730" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F730" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G730" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H730" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I730" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J730" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K730" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L730" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M730" s="3" t="s">
+        <v>1747</v>
+      </c>
+      <c r="N730" s="4" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="731" spans="1:14">
+      <c r="A731">
+        <v>734</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C731" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D731" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E731" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M731" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="N731" s="4" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="732" spans="1:14">
+      <c r="A732">
+        <v>737</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C732" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D732" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E732" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M732" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="N732" s="4" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="733" spans="1:14">
+      <c r="A733">
+        <v>736</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C733" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D733" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E733" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F733" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G733" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H733" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I733" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J733" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K733" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L733" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M733" s="3" t="s">
+        <v>1754</v>
+      </c>
+      <c r="N733" s="4" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="734" spans="1:14">
+      <c r="A734">
+        <v>738</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C734" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D734" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E734" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F734" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H734" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K734" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L734" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M734" s="3" t="s">
+        <v>1757</v>
+      </c>
+      <c r="N734" s="4" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="735" spans="1:14">
+      <c r="A735">
+        <v>739</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C735" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D735" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E735" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G735" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I735" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M735" s="3" t="s">
+        <v>1760</v>
+      </c>
+      <c r="N735" s="4" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="736" spans="1:14">
+      <c r="A736">
+        <v>740</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C736" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D736" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E736" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G736" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M736" s="3" t="s">
+        <v>1763</v>
+      </c>
+      <c r="N736" s="4" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="737" spans="1:14">
+      <c r="A737">
+        <v>741</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C737" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D737" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E737" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M737" s="3" t="s">
+        <v>1766</v>
+      </c>
+      <c r="N737" s="4" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="738" spans="1:14">
+      <c r="A738">
+        <v>742</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C738" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D738" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E738" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I738" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J738" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K738" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M738" s="3" t="s">
+        <v>1769</v>
+      </c>
+      <c r="N738" s="4" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="739" spans="1:14">
+      <c r="A739">
+        <v>743</v>
+      </c>
+      <c r="B739" s="1" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C739" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D739" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E739" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F739" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G739" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H739" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I739" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L739" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M739" s="3" t="s">
+        <v>1772</v>
+      </c>
+      <c r="N739" s="4" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="740" spans="1:14">
+      <c r="A740">
+        <v>744</v>
+      </c>
+      <c r="B740" s="1" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C740" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D740" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E740" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F740" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G740" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H740" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I740" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J740" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K740" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L740" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M740" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="N740" s="4" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="741" spans="1:14">
+      <c r="A741">
+        <v>745</v>
+      </c>
+      <c r="B741" s="1" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C741" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D741" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E741" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G741" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M741" s="3" t="s">
+        <v>1778</v>
+      </c>
+      <c r="N741" s="4" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="742" spans="1:14">
+      <c r="A742">
+        <v>746</v>
+      </c>
+      <c r="B742" s="1" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C742" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D742" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E742" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G742" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H742" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I742" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L742" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M742" s="3" t="s">
+        <v>1781</v>
+      </c>
+      <c r="N742" s="4" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="743" spans="1:14">
+      <c r="A743">
+        <v>747</v>
+      </c>
+      <c r="B743" s="1" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C743" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D743" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E743" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F743" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G743" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H743" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I743" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J743" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K743" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L743" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M743" s="3" t="s">
+        <v>1784</v>
+      </c>
+      <c r="N743" s="4" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="744" spans="1:14">
+      <c r="A744">
+        <v>748</v>
+      </c>
+      <c r="B744" s="1" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C744" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D744" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E744" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M744" s="3" t="s">
+        <v>1787</v>
+      </c>
+      <c r="N744" s="4" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="745" spans="1:14">
+      <c r="A745">
+        <v>749</v>
+      </c>
+      <c r="B745" s="1" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C745" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D745" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E745" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H745" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M745" s="3" t="s">
+        <v>1790</v>
+      </c>
+      <c r="N745" s="4" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="746" spans="1:14">
+      <c r="A746">
+        <v>750</v>
+      </c>
+      <c r="B746" s="1" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C746" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D746" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E746" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G746" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H746" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K746" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L746" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M746" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N746" s="4" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="747" spans="1:14">
+      <c r="A747">
+        <v>751</v>
+      </c>
+      <c r="B747" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C747" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D747" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E747" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M747" s="3" t="s">
+        <v>1795</v>
+      </c>
+      <c r="N747" s="4" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="748" spans="1:14">
+      <c r="A748">
+        <v>752</v>
+      </c>
+      <c r="B748" s="1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C748" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D748" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E748" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G748" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K748" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M748" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="N748" s="4" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="749" spans="1:14">
+      <c r="A749">
+        <v>753</v>
+      </c>
+      <c r="B749" s="1" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C749" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D749" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E749" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F749" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G749" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H749" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I749" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J749" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K749" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L749" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M749" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="N749" s="4" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="750" spans="1:14">
+      <c r="A750">
+        <v>754</v>
+      </c>
+      <c r="B750" s="1" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C750" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D750" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E750" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M750" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="N750" s="4" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="751" spans="1:14">
+      <c r="A751">
+        <v>755</v>
+      </c>
+      <c r="B751" s="1" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C751" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D751" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E751" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G751" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H751" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M751" s="3" t="s">
+        <v>1807</v>
+      </c>
+      <c r="N751" s="4" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="752" spans="1:14">
+      <c r="A752">
+        <v>756</v>
+      </c>
+      <c r="B752" s="1" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C752" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D752" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E752" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G752" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M752" s="3" t="s">
+        <v>1810</v>
+      </c>
+      <c r="N752" s="4" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="753" spans="1:14">
+      <c r="A753">
+        <v>757</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C753" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D753" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E753" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F753" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J753" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K753" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M753" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N753" s="4" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="754" spans="1:14">
+      <c r="A754">
+        <v>758</v>
+      </c>
+      <c r="B754" s="1" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C754" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D754" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E754" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F754" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G754" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H754" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I754" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J754" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K754" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L754" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M754" s="3" t="s">
+        <v>1815</v>
+      </c>
+      <c r="N754" s="4" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="755" spans="1:14">
+      <c r="A755">
+        <v>759</v>
+      </c>
+      <c r="B755" s="1" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C755" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D755" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E755" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M755" s="3" t="s">
+        <v>1819</v>
+      </c>
+      <c r="N755" s="4" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="756" spans="1:14">
+      <c r="A756">
+        <v>760</v>
+      </c>
+      <c r="B756" s="1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C756" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D756" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E756" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M756" s="3" t="s">
+        <v>1822</v>
+      </c>
+      <c r="N756" s="4" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="757" spans="1:14">
+      <c r="A757">
+        <v>761</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C757" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D757" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E757" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F757" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G757" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H757" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I757" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J757" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K757" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="L757" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M757" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N757" s="4" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="758" spans="1:14">
+      <c r="A758">
+        <v>762</v>
+      </c>
+      <c r="B758" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C758" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D758" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E758" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F758" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G758" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H758" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I758" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J758" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K758" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L758" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M758" s="3" t="s">
+        <v>1827</v>
+      </c>
+      <c r="N758" s="4" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="759" spans="1:14">
+      <c r="A759">
+        <v>763</v>
+      </c>
+      <c r="B759" s="1" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C759" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D759" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E759" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F759" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G759" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H759" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I759" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J759" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K759" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L759" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M759" s="3" t="s">
+        <v>1830</v>
+      </c>
+      <c r="N759" s="4" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="760" spans="1:14">
+      <c r="A760">
+        <v>764</v>
+      </c>
+      <c r="B760" s="1" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C760" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D760" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E760" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M760" s="3" t="s">
+        <v>1833</v>
+      </c>
+      <c r="N760" s="4" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="761" spans="1:14">
+      <c r="A761">
+        <v>765</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C761" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D761" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E761" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M761" s="3" t="s">
+        <v>1836</v>
+      </c>
+      <c r="N761" s="4" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="762" spans="1:14">
+      <c r="A762">
+        <v>766</v>
+      </c>
+      <c r="B762" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C762" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D762" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E762" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F762" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G762" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H762" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I762" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J762" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K762" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L762" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M762" s="3" t="s">
+        <v>1839</v>
+      </c>
+      <c r="N762" s="4" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="763" spans="1:14">
+      <c r="A763">
+        <v>767</v>
+      </c>
+      <c r="B763" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C763" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D763" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E763" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M763" s="3" t="s">
+        <v>1842</v>
+      </c>
+      <c r="N763" s="4" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="764" spans="1:14">
+      <c r="A764">
+        <v>768</v>
+      </c>
+      <c r="B764" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C764" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D764" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E764" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F764" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G764" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H764" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I764" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J764" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K764" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="L764" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M764" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N764" s="4" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="765" spans="1:14">
+      <c r="A765">
+        <v>769</v>
+      </c>
+      <c r="B765" s="1" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C765" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D765" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E765" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M765" s="3" t="s">
+        <v>1847</v>
+      </c>
+      <c r="N765" s="4" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="766" spans="1:14">
+      <c r="A766">
+        <v>770</v>
+      </c>
+      <c r="B766" s="1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C766" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D766" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E766" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M766" s="3" t="s">
+        <v>1850</v>
+      </c>
+      <c r="N766" s="4" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="767" spans="1:14">
+      <c r="A767">
+        <v>771</v>
+      </c>
+      <c r="B767" s="1" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C767" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D767" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E767" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M767" s="3" t="s">
+        <v>1853</v>
+      </c>
+      <c r="N767" s="4" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="768" spans="1:14">
+      <c r="A768">
+        <v>772</v>
+      </c>
+      <c r="B768" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C768" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D768" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E768" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F768" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G768" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H768" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I768" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J768" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K768" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L768" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M768" s="3" t="s">
+        <v>1856</v>
+      </c>
+      <c r="N768" s="4" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="769" spans="1:14">
+      <c r="A769">
+        <v>773</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C769" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D769" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E769" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K769" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M769" s="3" t="s">
+        <v>1859</v>
+      </c>
+      <c r="N769" s="4" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="770" spans="1:14">
+      <c r="A770">
+        <v>776</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C770" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D770" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E770" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F770" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G770" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H770" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I770" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J770" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K770" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L770" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M770" s="3" t="s">
+        <v>1862</v>
+      </c>
+      <c r="N770" s="4" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="771" spans="1:14">
+      <c r="A771">
+        <v>775</v>
+      </c>
+      <c r="B771" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C771" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D771" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E771" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F771" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G771" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H771" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I771" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J771" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K771" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L771" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M771" s="3" t="s">
+        <v>1865</v>
+      </c>
+      <c r="N771" s="4" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="772" spans="1:14">
+      <c r="A772">
+        <v>774</v>
+      </c>
+      <c r="B772" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C772" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D772" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E772" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M772" s="3" t="s">
+        <v>1868</v>
+      </c>
+      <c r="N772" s="4" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="773" spans="1:14">
+      <c r="A773">
+        <v>777</v>
+      </c>
+      <c r="B773" s="1" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C773" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D773" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E773" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F773" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G773" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H773" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I773" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J773" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K773" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L773" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M773" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="N773" s="4" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="774" spans="1:14">
+      <c r="A774">
+        <v>778</v>
+      </c>
+      <c r="B774" s="1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C774" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D774" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E774" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M774" s="3" t="s">
+        <v>1874</v>
+      </c>
+      <c r="N774" s="4" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="775" spans="1:14">
+      <c r="A775">
+        <v>779</v>
+      </c>
+      <c r="B775" s="1" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C775" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D775" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E775" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M775" s="3" t="s">
+        <v>1877</v>
+      </c>
+      <c r="N775" s="4" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="776" spans="1:14">
+      <c r="A776">
+        <v>780</v>
+      </c>
+      <c r="B776" s="1" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C776" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D776" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E776" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K776" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M776" s="3" t="s">
+        <v>1880</v>
+      </c>
+      <c r="N776" s="4" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="777" spans="1:14">
+      <c r="A777">
+        <v>781</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C777" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D777" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E777" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M777" s="3" t="s">
+        <v>1883</v>
+      </c>
+      <c r="N777" s="4" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="778" spans="1:14">
+      <c r="A778">
+        <v>782</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C778" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D778" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E778" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M778" s="3" t="s">
+        <v>1886</v>
+      </c>
+      <c r="N778" s="4" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="779" spans="1:14">
+      <c r="A779">
+        <v>783</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C779" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D779" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E779" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M779" s="3" t="s">
+        <v>1889</v>
+      </c>
+      <c r="N779" s="4" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="780" spans="1:14">
+      <c r="A780">
+        <v>784</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C780" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D780" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E780" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G780" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K780" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M780" s="3" t="s">
+        <v>1892</v>
+      </c>
+      <c r="N780" s="4" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="781" spans="1:14">
+      <c r="A781">
+        <v>785</v>
+      </c>
+      <c r="B781" s="1" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C781" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D781" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E781" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G781" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K781" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L781" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M781" s="3" t="s">
+        <v>1895</v>
+      </c>
+      <c r="N781" s="4" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="782" spans="1:14">
+      <c r="A782">
+        <v>786</v>
+      </c>
+      <c r="B782" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C782" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D782" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E782" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F782" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G782" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H782" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I782" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J782" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K782" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L782" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M782" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N782" s="4" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="783" spans="1:14">
+      <c r="A783">
+        <v>787</v>
+      </c>
+      <c r="B783" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C783" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D783" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E783" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G783" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K783" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M783" s="3" t="s">
+        <v>1900</v>
+      </c>
+      <c r="N783" s="4" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="784" spans="1:14">
+      <c r="A784">
+        <v>788</v>
+      </c>
+      <c r="B784" s="1" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C784" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D784" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E784" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F784" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G784" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H784" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I784" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J784" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K784" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L784" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M784" s="3" t="s">
+        <v>1903</v>
+      </c>
+      <c r="N784" s="4" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="785" spans="1:14">
+      <c r="A785">
+        <v>789</v>
+      </c>
+      <c r="B785" s="1" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C785" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D785" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E785" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G785" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K785" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L785" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M785" s="3" t="s">
+        <v>1906</v>
+      </c>
+      <c r="N785" s="4" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="786" spans="1:14">
+      <c r="A786">
+        <v>790</v>
+      </c>
+      <c r="B786" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C786" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D786" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E786" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F786" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G786" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I786" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K786" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M786" s="3" t="s">
+        <v>1909</v>
+      </c>
+      <c r="N786" s="4" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="787" spans="1:14">
+      <c r="A787">
+        <v>791</v>
+      </c>
+      <c r="B787" s="1" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C787" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D787" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E787" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J787" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M787" s="3" t="s">
+        <v>1912</v>
+      </c>
+      <c r="N787" s="4" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="788" spans="1:14">
+      <c r="A788">
+        <v>792</v>
+      </c>
+      <c r="B788" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C788" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D788" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E788" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G788" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H788" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I788" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J788" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L788" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M788" s="3" t="s">
+        <v>1915</v>
+      </c>
+      <c r="N788" s="4" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="789" spans="1:14">
+      <c r="A789">
+        <v>794</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C789" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D789" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E789" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F789" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G789" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H789" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I789" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J789" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K789" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L789" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M789" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N789" s="4" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="790" spans="1:14">
+      <c r="A790">
+        <v>793</v>
+      </c>
+      <c r="B790" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C790" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D790" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E790" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F790" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G790" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H790" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I790" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J790" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K790" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L790" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M790" s="3" t="s">
+        <v>1920</v>
+      </c>
+      <c r="N790" s="4" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="791" spans="1:14">
+      <c r="A791">
+        <v>795</v>
+      </c>
+      <c r="B791" s="1" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C791" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D791" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E791" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M791" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="N791" s="4" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="792" spans="1:14">
+      <c r="A792">
+        <v>796</v>
+      </c>
+      <c r="B792" s="1" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C792" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D792" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E792" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K792" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M792" s="3" t="s">
+        <v>1926</v>
+      </c>
+      <c r="N792" s="4" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="793" spans="1:14">
+      <c r="A793">
+        <v>797</v>
+      </c>
+      <c r="B793" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C793" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D793" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E793" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G793" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H793" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K793" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M793" s="3" t="s">
+        <v>1929</v>
+      </c>
+      <c r="N793" s="4" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="794" spans="1:14">
+      <c r="A794">
+        <v>798</v>
+      </c>
+      <c r="B794" s="1" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C794" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D794" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E794" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G794" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J794" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K794" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M794" s="3" t="s">
+        <v>1932</v>
+      </c>
+      <c r="N794" s="4" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="795" spans="1:14">
+      <c r="A795">
+        <v>799</v>
+      </c>
+      <c r="B795" s="1" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C795" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D795" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E795" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M795" s="3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="N795" s="4" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="796" spans="1:14">
+      <c r="A796">
+        <v>800</v>
+      </c>
+      <c r="B796" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C796" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D796" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E796" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F796" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G796" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H796" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I796" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J796" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K796" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L796" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M796" s="3" t="s">
+        <v>1937</v>
+      </c>
+      <c r="N796" s="4" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="797" spans="1:14">
+      <c r="A797">
+        <v>801</v>
+      </c>
+      <c r="B797" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C797" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D797" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E797" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F797" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G797" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H797" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I797" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J797" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K797" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L797" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M797" s="3" t="s">
+        <v>1940</v>
+      </c>
+      <c r="N797" s="4" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="798" spans="1:14">
+      <c r="A798">
+        <v>802</v>
+      </c>
+      <c r="B798" s="1" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C798" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D798" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E798" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F798" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G798" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H798" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I798" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J798" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K798" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L798" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M798" s="3" t="s">
+        <v>1943</v>
+      </c>
+      <c r="N798" s="4" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="799" spans="1:14">
+      <c r="A799">
+        <v>803</v>
+      </c>
+      <c r="B799" s="1" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C799" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D799" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E799" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M799" s="3" t="s">
+        <v>1946</v>
+      </c>
+      <c r="N799" s="4" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="800" spans="1:14">
+      <c r="A800">
+        <v>804</v>
+      </c>
+      <c r="B800" s="1" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C800" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D800" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E800" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F800" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H800" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K800" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L800" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M800" s="3" t="s">
+        <v>1949</v>
+      </c>
+      <c r="N800" s="4" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="801" spans="1:14">
+      <c r="A801">
+        <v>805</v>
+      </c>
+      <c r="B801" s="1" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C801" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D801" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E801" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M801" s="3" t="s">
+        <v>1952</v>
+      </c>
+      <c r="N801" s="4" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="802" spans="1:14">
+      <c r="A802">
+        <v>806</v>
+      </c>
+      <c r="B802" s="1" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C802" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D802" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E802" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M802" s="3" t="s">
+        <v>1955</v>
+      </c>
+      <c r="N802" s="4" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="803" spans="1:14">
+      <c r="A803" s="5">
+        <v>807</v>
+      </c>
+      <c r="B803" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C803" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D803" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E803" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F803" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G803" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H803" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I803" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J803" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K803" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L803" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M803" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="N803" s="4" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="804" spans="1:14">
+      <c r="A804" s="5">
+        <v>808</v>
+      </c>
+      <c r="B804" s="1" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C804" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D804" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E804" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F804" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K804" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M804" s="3" t="s">
+        <v>1961</v>
+      </c>
+      <c r="N804" s="4" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="805" spans="1:14">
+      <c r="A805" s="5">
+        <v>809</v>
+      </c>
+      <c r="B805" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C805" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D805" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E805" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F805" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G805" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H805" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I805" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J805" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K805" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L805" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M805" s="3" t="s">
+        <v>1964</v>
+      </c>
+      <c r="N805" s="4" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="806" spans="1:14">
+      <c r="A806" s="5">
+        <v>810</v>
+      </c>
+      <c r="B806" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C806" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D806" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E806" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G806" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J806" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K806" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M806" s="3" t="s">
+        <v>1967</v>
+      </c>
+      <c r="N806" s="4" t="s">
+        <v>1968</v>
       </c>
     </row>
   </sheetData>

--- a/PeerGrading/Input/form_exports/forms_responses.xlsx
+++ b/PeerGrading/Input/form_exports/forms_responses.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzh-my.sharepoint.com/personal/renjie_cui_business_uzh_ch/Documents/PeerGrading/Input/form_exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C161927-4325-4A9D-84E4-F055601FD2F6}"/>
+  <xr:revisionPtr revIDLastSave="576" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1D7A584-9540-48FC-8F4E-45E8B28E8044}"/>
   <bookViews>
     <workbookView xWindow="17280" yWindow="-16200" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9974" uniqueCount="1969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12132" uniqueCount="2447">
   <si>
     <t>Responseid</t>
   </si>
@@ -5943,6 +5943,1440 @@
   </si>
   <si>
     <t>2026-03-13T14:18:50.1394683Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:37:51.6295176Z</t>
+  </si>
+  <si>
+    <t>Enxhi	Kodragjini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice graphics </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:37:51.6295576Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:38:07.2442520Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good structured slides </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:38:07.2442921Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:38:39.8633125Z</t>
+  </si>
+  <si>
+    <t>Really nice slides, loud voice which is good</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:38:39.8633520Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:39:20.8809908Z</t>
+  </si>
+  <si>
+    <t>Great slides and illustrations</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:39:20.8810299Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:39:37.3560956Z</t>
+  </si>
+  <si>
+    <t>Nice slides, confident and informative. Can speak a bit slower</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:39:37.3561540Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:40:18.8958814Z</t>
+  </si>
+  <si>
+    <t>structured presentation</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:40:18.8959340Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:40:40.4814409Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:40:40.4814800Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:40:44.3470417Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">very good presentation, very interesting and illustrated slides </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:40:44.3470821Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:40:52.7097683Z</t>
+  </si>
+  <si>
+    <t>nice presentation slides</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:40:52.7098080Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:05.3576327Z</t>
+  </si>
+  <si>
+    <t>Practical relation with Tools presented, a little bit fast spoken</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:05.3576999Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:16.1081267Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:16.1081695Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:16.2079533Z</t>
+  </si>
+  <si>
+    <t>I didn't not know about the specific software solutions available to firms. This was very interesting and I really appreciated your slides. Very clear and nicely formatted.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:16.2080323Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:36.2175673Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">great information and visuals, however presentation felt too memorized </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:36.2176291Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:36.6905438Z</t>
+  </si>
+  <si>
+    <t>Great presentation. There was a lot of text in slides that were impossible to read, but otherwise the visuals were clear</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:36.6905853Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:40.2741643Z</t>
+  </si>
+  <si>
+    <t>talked a bit too fast but the slides were easy to follow</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:40.2742431Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:40.7565661Z</t>
+  </si>
+  <si>
+    <t>very good</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:40.7566058Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:43.8070713Z</t>
+  </si>
+  <si>
+    <t>Wasn’t really well explained, the slides were too heavy</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:43.8071203Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:44.8974594Z</t>
+  </si>
+  <si>
+    <t>nice presentation</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:44.8974994Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:45.7007287Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confident presenting style, topic was very well explained &amp; slides were clear </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:45.7007773Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:47.7357531Z</t>
+  </si>
+  <si>
+    <t>Very nice presentation, she understood the topic very well event though it is very technical bus she was able to cummunicate the key factors very clear and I could follow her easily. Bautiful visuals on the presentation.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:47.7358209Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:47.8001001Z</t>
+  </si>
+  <si>
+    <t>Well designed slides but you spoke a bit fast sometimes so it was hard to follow when you dont know the topic already</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:47.8001406Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:48.2918000Z</t>
+  </si>
+  <si>
+    <t>Visuals are well chosen but maybe some of them are too distracting, few too small texts</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:48.2918387Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:48.7991413Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thank you for your presentation. You spoke a bit too fast and looked too much the screen. </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:48.7992098Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:51.3971007Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:51.3971425Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:52.2003953Z</t>
+  </si>
+  <si>
+    <t>Well put together slides but spoken a little bit too fast</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:52.2004436Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:52.6404203Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reading </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:52.6404874Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:54.3524405Z</t>
+  </si>
+  <si>
+    <t>clear explanation of LCA and the explanation of why companies use LCA software was clear and convincing</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:54.3524849Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:57.3308241Z</t>
+  </si>
+  <si>
+    <t>Igor	Timotijevic</t>
+  </si>
+  <si>
+    <t>was good.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:57.3308637Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:57.7085342Z</t>
+  </si>
+  <si>
+    <t>Spoken clearly, nice slides, more focus on the audience, not the slides</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:57.7085751Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:58.6367059Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great slides, maybe focalize more on fewer software </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:41:58.6367453Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:00.9553251Z</t>
+  </si>
+  <si>
+    <t>overwhelming</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:00.9553778Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:00.9756417Z</t>
+  </si>
+  <si>
+    <t>good presentation, nice slides, good explanations</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:00.9756820Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:01.9202482Z</t>
+  </si>
+  <si>
+    <t>Very good</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:01.9202884Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:05.8105857Z</t>
+  </si>
+  <si>
+    <t>She had a really good presentation and the slides were very well made</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:05.8106278Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:12.8708586Z</t>
+  </si>
+  <si>
+    <t>The presentation was great! You could face the audience more instead of looking at the slides and do more eye contact, but the presentation was really good! Also the slides contained a little bit too much text.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:12.8709009Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:13.6571410Z</t>
+  </si>
+  <si>
+    <t>I liked the style of the presentation.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:13.6571801Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:29.5481129Z</t>
+  </si>
+  <si>
+    <t>The eye contact was a bit missing, and pace a bit fast. However, good presentation overall!</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:29.5481544Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:40.5614431Z</t>
+  </si>
+  <si>
+    <t>The presentation was well timed and exposed with great examples.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:40.5614834Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:59.1958953Z</t>
+  </si>
+  <si>
+    <t>Clear explanation</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:42:59.1959339Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:43:10.5168073Z</t>
+  </si>
+  <si>
+    <t>Great slides and easy to follow presenting</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:43:10.5168483Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:43:33.2307536Z</t>
+  </si>
+  <si>
+    <t>Very good presentation, very clear and comprehensive. The only areas for improvement would be time management and the visuals, which were a bit difficult to follow and contained too much information.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:43:33.2308003Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:44:01.8494441Z</t>
+  </si>
+  <si>
+    <t>Impressive Slides</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:44:01.8494842Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:44:27.6550193Z</t>
+  </si>
+  <si>
+    <t>Really like the slide adressing the student questions, very clean and to the point</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:44:27.6550585Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:45:03.2102578Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nice presentation, I like that you looked at the audience </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:45:03.2102985Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:45:51.9699665Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:45:51.9700073Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:45:53.8852591Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:45:53.8853349Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:46:10.5413920Z</t>
+  </si>
+  <si>
+    <t>I liked the fact that the presentation was really simple, but still delivered its message perfectly.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:46:10.5414456Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:46:59.0163827Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice breakdown of a complicated topic </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:46:59.0164221Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:01.1500633Z</t>
+  </si>
+  <si>
+    <t>Good structure, a few more visuals (especially for answering OLAT questions) would have been nice</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:01.1501489Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:01.3719021Z</t>
+  </si>
+  <si>
+    <t>Great integration of OLAT questions, I enjoyed the free speaking style</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:01.3719405Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:02.4383812Z</t>
+  </si>
+  <si>
+    <t>Good presentation explain well the topic</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:02.4384222Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:03.2080350Z</t>
+  </si>
+  <si>
+    <t>well freely spoken. But some more slides would have been nice to better understand whst point you were focusing on at the moment</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:03.2080748Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:04.8011101Z</t>
+  </si>
+  <si>
+    <t>Explained well that LCA considers the entire lifecycle rather than focusing on a single stage and interesting focus on services rather than products</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:04.8011535Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:05.1024456Z</t>
+  </si>
+  <si>
+    <t>Interesting topic</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:05.1024867Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:06.3276858Z</t>
+  </si>
+  <si>
+    <t>Lots of focus on the Student questions</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:06.3277240Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:06.3271232Z</t>
+  </si>
+  <si>
+    <t>nice presentation style</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:06.3271707Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:06.0837880Z</t>
+  </si>
+  <si>
+    <t>Slides a bit bland. Hard to read from the last row.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:06.0838289Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:09.3829697Z</t>
+  </si>
+  <si>
+    <t>Nice slides, mostly freely spoken</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:09.3830086Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.2731324Z</t>
+  </si>
+  <si>
+    <t>Easy to follow but maybe too slow</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.2731720Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.2976309Z</t>
+  </si>
+  <si>
+    <t>I liked how you summarized the OLAT questions. I especially liked the outlining of the specific LCA problems with service organizations. Practice would have helped the flow but this is a cosmetic adjustment to your presentation.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.2976791Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.3320626Z</t>
+  </si>
+  <si>
+    <t>Good examples</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.3321387Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.4387921Z</t>
+  </si>
+  <si>
+    <t>I really liked how he built on the information from today’s class and had a very well done presentation</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.4388468Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.7022386Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thank you for your presentation ! </t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.7022781Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.6841947Z</t>
+  </si>
+  <si>
+    <t>informative presentation</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:10.6842342Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:12.6182710Z</t>
+  </si>
+  <si>
+    <t>Good topic, easy to follow</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:12.6183130Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:13.0042943Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:13.0043362Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:14.6220831Z</t>
+  </si>
+  <si>
+    <t>Really great presentation, but you could face the audience more and do more eye contact rather than facing/looking at the slides.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:14.6221232Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:18.8042631Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:18.8043036Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:20.4778934Z</t>
+  </si>
+  <si>
+    <t>Excellent presentation, comprehensive, clear, and well-timed.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:20.4780063Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:23.2268354Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:23.2268764Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:23.7612802Z</t>
+  </si>
+  <si>
+    <t>Great timing ! Thank you for your presentation</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:23.7613209Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:28.7192534Z</t>
+  </si>
+  <si>
+    <t>good presentation, very calmly spoken, nice slides, good explanations</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:28.7192933Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:32.2513185Z</t>
+  </si>
+  <si>
+    <t>Really good presentation, well timed and good presenting style</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:32.2513608Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:36.2622155Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:36.2622868Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:51.6567238Z</t>
+  </si>
+  <si>
+    <t>Well explained, straight to the point and didn’t mix multiple concepts, very clear</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:51.6567629Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:58.1374867Z</t>
+  </si>
+  <si>
+    <t>The topic was well explained and the presenter maintained a very good eye contact with the audience. In addition, I much appreciated how Igor prepared the slides: they were very well made and simple.</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:58.1375398Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:58.8168846Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:47:58.8169496Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:48:07.9880818Z</t>
+  </si>
+  <si>
+    <t>innovative idea of the topic</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:48:07.9881242Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:01:31.2923122Z</t>
+  </si>
+  <si>
+    <t>nice presentation, easy to follow</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:01:31.2924277Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:01:49.1250023Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good explanation </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:01:49.1250767Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:02:27.3728029Z</t>
+  </si>
+  <si>
+    <t>Simone	Martinecz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good designed slides </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:02:27.3728989Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:02:56.8165481Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:02:56.8165913Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:03:19.8326983Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great captivating style of presenting! </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:03:19.8327371Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:03:26.0831050Z</t>
+  </si>
+  <si>
+    <t>Good way of delivering message</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:03:26.0831463Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:04:06.6440078Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could tell you knew your stuff, good eye contact with the audience </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:04:06.6440576Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:04:46.2367302Z</t>
+  </si>
+  <si>
+    <t>Great and original way of exposing the topic</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:04:46.2367834Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:04:58.9009780Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:04:58.9010171Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:08.2022098Z</t>
+  </si>
+  <si>
+    <t>Good introduction with coffee-example, very enthusiastic presentation-style</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:08.2022548Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:20.3641534Z</t>
+  </si>
+  <si>
+    <t>The presenter created a highly interactive atmosphere, which kept the audience involved and making the presentation easy to follow.</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:20.3642014Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:20.6334759Z</t>
+  </si>
+  <si>
+    <t>I liked your interaction with the class. Really pulls me into the topic and personalizes it to my life. Also I really liked your slides because the style helped me understand the topic through pictures and short text.</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:20.6335192Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:49.0081152Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:49.0081577Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:52.0697619Z</t>
+  </si>
+  <si>
+    <t>Nice engaging presentation style, learning goals at the beginning gave a good overview</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:05:52.0698300Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:06:32.6597497Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:06:32.6597925Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:18.1264606Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nice interactive presentation, beautiful slides with all the key notes presented in big notes. A bit stressed and restless while speaking </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:18.1265008Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:19.1588749Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:19.1589252Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:23.0449710Z</t>
+  </si>
+  <si>
+    <t>very good example with the coffee</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:23.0450149Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:25.4691322Z</t>
+  </si>
+  <si>
+    <t>Great energy, very good presentation and clear topic</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:25.4691937Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:26.2066227Z</t>
+  </si>
+  <si>
+    <t>clear explanation of the concept and good distinction between water types</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:26.2066633Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:29.0162364Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interactive presentation, very dynamic </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:29.0162784Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:29.2561580Z</t>
+  </si>
+  <si>
+    <t>very well presented</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:29.2562029Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:29.5977842Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">great example with the cup of coffee to explain and introduce the topic </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:29.5978249Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:29.8643610Z</t>
+  </si>
+  <si>
+    <t>very motivated, nice introduction with the coffee example, maybe a little rushed</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:29.8644108Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:30.0174897Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very energic presentation </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:30.0175316Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:30.3166882Z</t>
+  </si>
+  <si>
+    <t>Thank you for your good presentation !</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:30.3167505Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:32.3954449Z</t>
+  </si>
+  <si>
+    <t>talked a bit too fast but good overall</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:32.3954853Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:34.2680698Z</t>
+  </si>
+  <si>
+    <t>positive presenting energy and good examples</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:34.2681095Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:34.6900726Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did a great job at answering the questions and was very good at presenting </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:34.6901228Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:40.3079604Z</t>
+  </si>
+  <si>
+    <t>Very good presentation style, the topics were clearly illustrated</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:40.3080388Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:40.5727694Z</t>
+  </si>
+  <si>
+    <t>I like the intro at the beginning, dynamic</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:40.5728414Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:40.8914068Z</t>
+  </si>
+  <si>
+    <t>Quite good</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:40.8914510Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:41.0383577Z</t>
+  </si>
+  <si>
+    <t>Feels a bit rushed but otherwise conceptually very good</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:41.0384349Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:48.1289702Z</t>
+  </si>
+  <si>
+    <t>A bit fast paced, good slides</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:48.1290102Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:49.6768519Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great presentation, tried to make it interactive like me, not easy… keep up! </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:49.6768915Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:55.9297308Z</t>
+  </si>
+  <si>
+    <t>good entry question, good explanation, good slides, spoke a little fast</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:55.9298031Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:56.0424293Z</t>
+  </si>
+  <si>
+    <t>Caught the crowd, and very good</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:56.0425086Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:57.5130668Z</t>
+  </si>
+  <si>
+    <t>Very good presentation, I liked the slides and your presentation style is perfect too!</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:07:57.5131415Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:11.7453887Z</t>
+  </si>
+  <si>
+    <t>Valentin	Python</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:11.7454409Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:14.0720440Z</t>
+  </si>
+  <si>
+    <t>Amazing presentation, really confident and engaging. However, pace was maybe a bit too fast sometimes</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:14.0720975Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:18.9186999Z</t>
+  </si>
+  <si>
+    <t>I liked the initial hook, as well as the visuals. I would probably pay more attention to the design, but overall it was an excellent job.</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:18.9187401Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:21.2382397Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very cool style of presentation, very interactive and passionate. </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:21.2382798Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:33.7991617Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:33.7992014Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:36.1426391Z</t>
+  </si>
+  <si>
+    <t>Great presentation! It was clear, engaging, and highly interactive. The only area for improvement is time management.</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:36.1426828Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:53.6271250Z</t>
+  </si>
+  <si>
+    <t>perfect style of the presentation</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:08:53.6271664Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:44.4719241Z</t>
+  </si>
+  <si>
+    <t>Took into account what we already learnt during the course and went straight to the core of his presentation. Very clear and clean slides - nothing to add!</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:44.4719632Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:59.6252082Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicely adapted to content of the course (e.g. skipping definition) </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:09:59.6252481Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:10:08.5655275Z</t>
+  </si>
+  <si>
+    <t>I Like how you implemented the student questions throughout the slideshow labeled with green stars</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:10:08.5655888Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:11:25.4433402Z</t>
+  </si>
+  <si>
+    <t>The presenter demonstrated a strong understanding of the topic. Overall, it was a solid and well-executed presentation.</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:11:25.4433802Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:12:42.8044021Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:12:42.8044693Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:00.6820862Z</t>
+  </si>
+  <si>
+    <t>Great attention to answering students' questions during the presentation</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:00.6821604Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:00.6394576Z</t>
+  </si>
+  <si>
+    <t>nice idea use the stars, good presentation</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:00.6394974Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:03.2936401Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very in depth explanation and informative slides, however too deep and slides too loaded, bit difficult to follow </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:03.2936803Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:03.7019913Z</t>
+  </si>
+  <si>
+    <t>try making more eye contact with the crowd</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:03.7020325Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:05.0011688Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very well and calm spoken, not nervous at all. Nice examples used </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:05.0012223Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:05.7502237Z</t>
+  </si>
+  <si>
+    <t>good explanations, calmly spoken, slides a little full</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:05.7502637Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:07.0579990Z</t>
+  </si>
+  <si>
+    <t>Good examples.</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:07.0580411Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:10.9436929Z</t>
+  </si>
+  <si>
+    <t>well structured presentation &amp; nice presentation style, (your last name is so cool)</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:10.9437750Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:14.2128491Z</t>
+  </si>
+  <si>
+    <t>Good presentation, would have like to see more visual representations of concepts</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:14.2129502Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:15.3595773Z</t>
+  </si>
+  <si>
+    <t>I appreciated how you adjusted your presentation to present the newest information. I didn't know about mandatory LCA requirements within Europe. I appreciate how you covered so many of OLAT questions.</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:15.3596195Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:17.1781666Z</t>
+  </si>
+  <si>
+    <t>Good slides, freely spoken, good presentation skills</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:17.1782083Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:17.1975683Z</t>
+  </si>
+  <si>
+    <t>Thank you !</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:17.1976097Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:17.6290415Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:17.6290820Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:20.0544655Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:20.0545070Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:20.0594166Z</t>
+  </si>
+  <si>
+    <t>The presentation style and slides were great!</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:20.0594570Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:20.4289844Z</t>
+  </si>
+  <si>
+    <t>Good overview of key LCA challenges and strong link to the ISO framework</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:20.4290240Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:22.5097282Z</t>
+  </si>
+  <si>
+    <t>Competently presented and very easy to follow.</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:22.5098085Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:24.1341086Z</t>
+  </si>
+  <si>
+    <t>Unclear what the stars on slide 4&amp;5 are about, maybe include some images, well explained tables</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:24.1341606Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:27.8534301Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:27.8534825Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:30.9143082Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nice background knowledge </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:30.9143617Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:32.6734779Z</t>
+  </si>
+  <si>
+    <t>very nicely presented</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:32.6735176Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:35.5805193Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:35.5805615Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:36.0331885Z</t>
+  </si>
+  <si>
+    <t>Very well spoken</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:36.0332313Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:37.5081203Z</t>
+  </si>
+  <si>
+    <t>Nice presentation, nice background knowledge. Excellent job</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:37.5082016Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:39.1689875Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did a great job discussing the topic and answering the questions </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:39.1690308Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:42.6630015Z</t>
+  </si>
+  <si>
+    <t>You addressed well the main key points, thank you!</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:42.6630448Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:42.8320137Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I like the connection of the green stars that answer the questions, but could be also confusing </t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:42.8320828Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:44.1653089Z</t>
+  </si>
+  <si>
+    <t>In general good, was calm and confident</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:44.1653490Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:46.4298738Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:46.4299152Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:46.8835739Z</t>
+  </si>
+  <si>
+    <t>very nice presentation</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:46.8836140Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:48.9289151Z</t>
+  </si>
+  <si>
+    <t>Great presentation! Very clear and engaging. Well done!</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:13:48.9289570Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:14:00.8699276Z</t>
+  </si>
+  <si>
+    <t>Good overview</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:14:00.8699680Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:14:20.2222830Z</t>
+  </si>
+  <si>
+    <t>structured slides</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:14:20.2223222Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:17:39.3557473Z</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:17:39.3557888Z</t>
+  </si>
+  <si>
+    <t>2026-03-19T12:47:03.9779383Z</t>
+  </si>
+  <si>
+    <t>clear structure on slides - very good</t>
+  </si>
+  <si>
+    <t>2026-03-19T12:47:03.9779792Z</t>
+  </si>
+  <si>
+    <t>2026-03-19T12:49:56.2654576Z</t>
+  </si>
+  <si>
+    <t>good presentation, visuals not that special</t>
+  </si>
+  <si>
+    <t>2026-03-19T12:49:56.2655480Z</t>
+  </si>
+  <si>
+    <t>2026-03-19T12:54:13.4576285Z</t>
+  </si>
+  <si>
+    <t>very nice slides!</t>
+  </si>
+  <si>
+    <t>2026-03-19T12:54:13.4578489Z</t>
+  </si>
+  <si>
+    <t>2026-03-19T12:55:16.0786124Z</t>
+  </si>
+  <si>
+    <t>good clear presentation, slides okay</t>
+  </si>
+  <si>
+    <t>2026-03-19T12:55:16.0786528Z</t>
   </si>
 </sst>
 </file>
@@ -6046,8 +7480,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N806" totalsRowShown="0">
-  <autoFilter ref="A1:N806" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N972" totalsRowShown="0">
+  <autoFilter ref="A1:N972" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Responseid" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SubmittedAt"/>
@@ -6365,7 +7799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N806"/>
+  <dimension ref="A1:N972"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -41658,7 +43092,7 @@
       </c>
     </row>
     <row r="803" spans="1:14">
-      <c r="A803" s="5">
+      <c r="A803">
         <v>807</v>
       </c>
       <c r="B803" s="1" t="s">
@@ -41702,7 +43136,7 @@
       </c>
     </row>
     <row r="804" spans="1:14">
-      <c r="A804" s="5">
+      <c r="A804">
         <v>808</v>
       </c>
       <c r="B804" s="1" t="s">
@@ -41746,7 +43180,7 @@
       </c>
     </row>
     <row r="805" spans="1:14">
-      <c r="A805" s="5">
+      <c r="A805">
         <v>809</v>
       </c>
       <c r="B805" s="1" t="s">
@@ -41790,7 +43224,7 @@
       </c>
     </row>
     <row r="806" spans="1:14">
-      <c r="A806" s="5">
+      <c r="A806">
         <v>810</v>
       </c>
       <c r="B806" s="1" t="s">
@@ -41831,6 +43265,7310 @@
       </c>
       <c r="N806" s="4" t="s">
         <v>1968</v>
+      </c>
+    </row>
+    <row r="807" spans="1:14">
+      <c r="A807">
+        <v>811</v>
+      </c>
+      <c r="B807" s="1" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C807" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D807" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E807" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M807" s="3" t="s">
+        <v>1971</v>
+      </c>
+      <c r="N807" s="4" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="808" spans="1:14">
+      <c r="A808">
+        <v>812</v>
+      </c>
+      <c r="B808" s="1" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C808" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D808" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E808" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F808" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G808" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H808" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I808" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J808" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K808" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L808" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M808" s="3" t="s">
+        <v>1974</v>
+      </c>
+      <c r="N808" s="4" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="809" spans="1:14">
+      <c r="A809">
+        <v>813</v>
+      </c>
+      <c r="B809" s="1" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C809" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D809" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E809" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M809" s="3" t="s">
+        <v>1977</v>
+      </c>
+      <c r="N809" s="4" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="810" spans="1:14">
+      <c r="A810">
+        <v>814</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C810" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D810" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E810" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M810" s="3" t="s">
+        <v>1980</v>
+      </c>
+      <c r="N810" s="4" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="811" spans="1:14">
+      <c r="A811">
+        <v>815</v>
+      </c>
+      <c r="B811" s="1" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C811" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D811" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E811" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M811" s="3" t="s">
+        <v>1983</v>
+      </c>
+      <c r="N811" s="4" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="812" spans="1:14">
+      <c r="A812">
+        <v>816</v>
+      </c>
+      <c r="B812" s="1" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C812" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D812" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E812" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F812" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G812" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H812" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I812" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J812" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K812" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L812" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M812" s="3" t="s">
+        <v>1986</v>
+      </c>
+      <c r="N812" s="4" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="813" spans="1:14">
+      <c r="A813">
+        <v>817</v>
+      </c>
+      <c r="B813" s="1" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C813" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D813" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E813" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M813" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="N813" s="4" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="814" spans="1:14">
+      <c r="A814">
+        <v>818</v>
+      </c>
+      <c r="B814" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C814" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D814" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E814" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M814" s="3" t="s">
+        <v>1991</v>
+      </c>
+      <c r="N814" s="4" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="815" spans="1:14">
+      <c r="A815">
+        <v>819</v>
+      </c>
+      <c r="B815" s="1" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C815" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D815" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E815" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M815" s="3" t="s">
+        <v>1994</v>
+      </c>
+      <c r="N815" s="4" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="816" spans="1:14">
+      <c r="A816">
+        <v>820</v>
+      </c>
+      <c r="B816" s="1" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C816" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D816" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E816" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F816" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G816" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H816" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I816" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J816" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K816" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L816" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M816" s="3" t="s">
+        <v>1997</v>
+      </c>
+      <c r="N816" s="4" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="817" spans="1:14">
+      <c r="A817">
+        <v>821</v>
+      </c>
+      <c r="B817" s="1" t="s">
+        <v>1999</v>
+      </c>
+      <c r="C817" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D817" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E817" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F817" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G817" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I817" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K817" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L817" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M817" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N817" s="4" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="818" spans="1:14">
+      <c r="A818">
+        <v>822</v>
+      </c>
+      <c r="B818" s="1" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C818" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D818" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E818" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M818" s="3" t="s">
+        <v>2002</v>
+      </c>
+      <c r="N818" s="4" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="819" spans="1:14">
+      <c r="A819">
+        <v>823</v>
+      </c>
+      <c r="B819" s="1" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C819" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D819" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E819" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F819" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G819" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H819" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I819" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J819" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K819" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L819" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M819" s="3" t="s">
+        <v>2005</v>
+      </c>
+      <c r="N819" s="4" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="820" spans="1:14">
+      <c r="A820">
+        <v>824</v>
+      </c>
+      <c r="B820" s="1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C820" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D820" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E820" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J820" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M820" s="3" t="s">
+        <v>2008</v>
+      </c>
+      <c r="N820" s="4" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="821" spans="1:14">
+      <c r="A821">
+        <v>825</v>
+      </c>
+      <c r="B821" s="1" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C821" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D821" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E821" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F821" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H821" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I821" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J821" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M821" s="3" t="s">
+        <v>2011</v>
+      </c>
+      <c r="N821" s="4" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="822" spans="1:14">
+      <c r="A822">
+        <v>826</v>
+      </c>
+      <c r="B822" s="1" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C822" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D822" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E822" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M822" s="3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="N822" s="4" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="823" spans="1:14">
+      <c r="A823">
+        <v>827</v>
+      </c>
+      <c r="B823" s="1" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C823" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D823" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E823" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F823" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G823" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H823" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I823" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J823" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K823" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L823" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M823" s="3" t="s">
+        <v>2017</v>
+      </c>
+      <c r="N823" s="4" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="824" spans="1:14">
+      <c r="A824">
+        <v>828</v>
+      </c>
+      <c r="B824" s="1" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C824" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D824" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E824" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H824" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M824" s="3" t="s">
+        <v>2020</v>
+      </c>
+      <c r="N824" s="4" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="825" spans="1:14">
+      <c r="A825">
+        <v>829</v>
+      </c>
+      <c r="B825" s="1" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C825" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D825" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E825" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F825" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G825" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H825" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I825" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J825" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K825" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L825" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M825" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="N825" s="4" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="826" spans="1:14">
+      <c r="A826">
+        <v>830</v>
+      </c>
+      <c r="B826" s="1" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C826" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D826" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E826" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F826" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G826" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H826" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I826" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J826" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K826" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L826" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M826" s="3" t="s">
+        <v>2026</v>
+      </c>
+      <c r="N826" s="4" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="827" spans="1:14">
+      <c r="A827">
+        <v>831</v>
+      </c>
+      <c r="B827" s="1" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C827" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D827" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E827" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F827" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G827" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H827" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I827" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J827" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K827" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L827" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M827" s="3" t="s">
+        <v>2029</v>
+      </c>
+      <c r="N827" s="4" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="828" spans="1:14">
+      <c r="A828">
+        <v>832</v>
+      </c>
+      <c r="B828" s="1" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C828" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D828" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E828" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F828" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G828" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H828" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I828" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J828" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K828" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L828" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M828" s="3" t="s">
+        <v>2032</v>
+      </c>
+      <c r="N828" s="4" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="829" spans="1:14">
+      <c r="A829">
+        <v>833</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C829" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D829" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E829" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F829" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G829" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H829" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I829" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J829" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K829" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L829" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M829" s="3" t="s">
+        <v>2035</v>
+      </c>
+      <c r="N829" s="4" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="830" spans="1:14">
+      <c r="A830">
+        <v>834</v>
+      </c>
+      <c r="B830" s="1" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C830" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D830" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E830" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F830" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G830" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H830" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I830" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J830" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K830" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L830" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M830" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N830" s="4" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="831" spans="1:14">
+      <c r="A831">
+        <v>835</v>
+      </c>
+      <c r="B831" s="1" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C831" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D831" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E831" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F831" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G831" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H831" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I831" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J831" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K831" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L831" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M831" s="3" t="s">
+        <v>2040</v>
+      </c>
+      <c r="N831" s="4" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="832" spans="1:14">
+      <c r="A832">
+        <v>836</v>
+      </c>
+      <c r="B832" s="1" t="s">
+        <v>2042</v>
+      </c>
+      <c r="C832" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D832" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E832" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F832" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G832" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H832" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I832" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J832" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K832" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L832" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M832" s="3" t="s">
+        <v>2043</v>
+      </c>
+      <c r="N832" s="4" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="833" spans="1:14">
+      <c r="A833">
+        <v>837</v>
+      </c>
+      <c r="B833" s="1" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C833" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D833" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E833" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F833" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G833" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H833" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I833" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J833" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K833" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L833" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M833" s="3" t="s">
+        <v>2046</v>
+      </c>
+      <c r="N833" s="4" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="834" spans="1:14">
+      <c r="A834">
+        <v>838</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C834" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D834" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E834" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F834" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G834" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H834" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I834" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J834" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K834" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L834" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M834" s="3" t="s">
+        <v>2050</v>
+      </c>
+      <c r="N834" s="4" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="835" spans="1:14">
+      <c r="A835">
+        <v>839</v>
+      </c>
+      <c r="B835" s="1" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C835" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D835" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E835" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F835" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G835" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H835" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I835" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J835" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K835" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L835" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M835" s="3" t="s">
+        <v>2053</v>
+      </c>
+      <c r="N835" s="4" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="836" spans="1:14">
+      <c r="A836">
+        <v>840</v>
+      </c>
+      <c r="B836" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C836" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D836" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E836" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F836" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G836" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H836" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I836" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J836" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K836" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L836" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M836" s="3" t="s">
+        <v>2056</v>
+      </c>
+      <c r="N836" s="4" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="837" spans="1:14">
+      <c r="A837">
+        <v>841</v>
+      </c>
+      <c r="B837" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C837" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D837" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E837" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F837" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G837" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H837" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I837" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J837" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K837" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L837" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M837" s="3" t="s">
+        <v>2059</v>
+      </c>
+      <c r="N837" s="4" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="838" spans="1:14">
+      <c r="A838">
+        <v>842</v>
+      </c>
+      <c r="B838" s="1" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C838" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D838" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E838" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F838" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G838" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H838" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I838" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J838" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K838" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L838" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M838" s="3" t="s">
+        <v>2062</v>
+      </c>
+      <c r="N838" s="4" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="839" spans="1:14">
+      <c r="A839">
+        <v>843</v>
+      </c>
+      <c r="B839" s="1" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C839" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D839" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E839" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F839" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G839" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H839" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I839" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J839" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K839" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L839" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M839" s="3" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N839" s="4" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="840" spans="1:14">
+      <c r="A840">
+        <v>844</v>
+      </c>
+      <c r="B840" s="1" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C840" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D840" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E840" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F840" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G840" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H840" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I840" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J840" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K840" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L840" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M840" s="3" t="s">
+        <v>2068</v>
+      </c>
+      <c r="N840" s="4" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="841" spans="1:14">
+      <c r="A841">
+        <v>845</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C841" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D841" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E841" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F841" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G841" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H841" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I841" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J841" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K841" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L841" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M841" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="N841" s="4" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="842" spans="1:14">
+      <c r="A842">
+        <v>846</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C842" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D842" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E842" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F842" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G842" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H842" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I842" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J842" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K842" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L842" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M842" s="3" t="s">
+        <v>2074</v>
+      </c>
+      <c r="N842" s="4" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="843" spans="1:14">
+      <c r="A843">
+        <v>847</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C843" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D843" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E843" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F843" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G843" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H843" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I843" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J843" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K843" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L843" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M843" s="3" t="s">
+        <v>2077</v>
+      </c>
+      <c r="N843" s="4" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="844" spans="1:14">
+      <c r="A844">
+        <v>848</v>
+      </c>
+      <c r="B844" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C844" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D844" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E844" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F844" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G844" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H844" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I844" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J844" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K844" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L844" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M844" s="3" t="s">
+        <v>2080</v>
+      </c>
+      <c r="N844" s="4" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="845" spans="1:14">
+      <c r="A845">
+        <v>849</v>
+      </c>
+      <c r="B845" s="1" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C845" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D845" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E845" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F845" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G845" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H845" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I845" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J845" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K845" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L845" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M845" s="3" t="s">
+        <v>2083</v>
+      </c>
+      <c r="N845" s="4" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="846" spans="1:14">
+      <c r="A846">
+        <v>850</v>
+      </c>
+      <c r="B846" s="1" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C846" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D846" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E846" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F846" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G846" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H846" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I846" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J846" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K846" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L846" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M846" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="N846" s="4" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="847" spans="1:14">
+      <c r="A847">
+        <v>851</v>
+      </c>
+      <c r="B847" s="1" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C847" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D847" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E847" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F847" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G847" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H847" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I847" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J847" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K847" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L847" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M847" s="3" t="s">
+        <v>2089</v>
+      </c>
+      <c r="N847" s="4" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="848" spans="1:14">
+      <c r="A848">
+        <v>852</v>
+      </c>
+      <c r="B848" s="1" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C848" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D848" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E848" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F848" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G848" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H848" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I848" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J848" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K848" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L848" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M848" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="N848" s="4" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="849" spans="1:14">
+      <c r="A849">
+        <v>853</v>
+      </c>
+      <c r="B849" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C849" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D849" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E849" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F849" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G849" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H849" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I849" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J849" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K849" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L849" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M849" s="3" t="s">
+        <v>2095</v>
+      </c>
+      <c r="N849" s="4" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="850" spans="1:14">
+      <c r="A850">
+        <v>854</v>
+      </c>
+      <c r="B850" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C850" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D850" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E850" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F850" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G850" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H850" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I850" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J850" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K850" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L850" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M850" s="3" t="s">
+        <v>2098</v>
+      </c>
+      <c r="N850" s="4" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="851" spans="1:14">
+      <c r="A851">
+        <v>855</v>
+      </c>
+      <c r="B851" s="1" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C851" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D851" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E851" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F851" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G851" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H851" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I851" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J851" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K851" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L851" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M851" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N851" s="4" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="852" spans="1:14">
+      <c r="A852">
+        <v>856</v>
+      </c>
+      <c r="B852" s="1" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C852" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D852" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E852" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F852" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G852" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H852" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I852" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J852" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K852" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L852" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M852" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N852" s="4" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="853" spans="1:14">
+      <c r="A853">
+        <v>857</v>
+      </c>
+      <c r="B853" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C853" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D853" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E853" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F853" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G853" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H853" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I853" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J853" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K853" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L853" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M853" s="3" t="s">
+        <v>2105</v>
+      </c>
+      <c r="N853" s="4" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="854" spans="1:14">
+      <c r="A854">
+        <v>858</v>
+      </c>
+      <c r="B854" s="1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C854" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D854" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E854" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F854" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G854" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H854" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I854" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J854" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K854" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L854" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M854" s="3" t="s">
+        <v>2108</v>
+      </c>
+      <c r="N854" s="4" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="855" spans="1:14">
+      <c r="A855">
+        <v>859</v>
+      </c>
+      <c r="B855" s="1" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C855" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D855" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E855" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F855" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G855" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H855" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I855" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J855" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K855" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L855" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M855" s="3" t="s">
+        <v>2111</v>
+      </c>
+      <c r="N855" s="4" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="856" spans="1:14">
+      <c r="A856">
+        <v>860</v>
+      </c>
+      <c r="B856" s="1" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C856" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D856" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E856" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F856" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G856" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H856" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I856" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J856" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K856" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L856" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M856" s="3" t="s">
+        <v>2114</v>
+      </c>
+      <c r="N856" s="4" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="857" spans="1:14">
+      <c r="A857">
+        <v>861</v>
+      </c>
+      <c r="B857" s="1" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C857" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D857" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E857" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F857" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G857" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H857" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I857" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J857" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K857" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L857" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M857" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="N857" s="4" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="858" spans="1:14">
+      <c r="A858">
+        <v>862</v>
+      </c>
+      <c r="B858" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C858" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D858" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E858" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F858" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G858" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H858" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I858" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J858" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K858" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L858" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M858" s="3" t="s">
+        <v>2120</v>
+      </c>
+      <c r="N858" s="4" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="859" spans="1:14">
+      <c r="A859">
+        <v>863</v>
+      </c>
+      <c r="B859" s="1" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C859" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D859" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E859" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F859" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G859" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H859" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I859" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J859" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K859" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L859" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M859" s="3" t="s">
+        <v>2123</v>
+      </c>
+      <c r="N859" s="4" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="860" spans="1:14">
+      <c r="A860">
+        <v>864</v>
+      </c>
+      <c r="B860" s="1" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C860" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D860" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E860" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F860" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G860" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H860" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I860" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J860" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K860" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L860" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M860" s="3" t="s">
+        <v>2126</v>
+      </c>
+      <c r="N860" s="4" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="861" spans="1:14">
+      <c r="A861">
+        <v>866</v>
+      </c>
+      <c r="B861" s="1" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C861" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D861" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E861" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F861" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G861" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H861" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I861" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J861" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K861" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L861" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M861" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="N861" s="4" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="862" spans="1:14">
+      <c r="A862">
+        <v>867</v>
+      </c>
+      <c r="B862" s="1" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C862" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D862" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E862" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F862" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G862" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H862" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I862" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J862" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K862" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L862" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M862" s="3" t="s">
+        <v>2132</v>
+      </c>
+      <c r="N862" s="4" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="863" spans="1:14">
+      <c r="A863">
+        <v>865</v>
+      </c>
+      <c r="B863" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C863" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D863" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E863" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F863" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G863" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H863" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I863" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J863" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K863" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L863" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M863" s="3" t="s">
+        <v>2135</v>
+      </c>
+      <c r="N863" s="4" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="864" spans="1:14">
+      <c r="A864">
+        <v>868</v>
+      </c>
+      <c r="B864" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C864" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D864" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E864" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F864" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G864" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H864" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I864" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J864" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K864" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L864" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M864" s="3" t="s">
+        <v>2138</v>
+      </c>
+      <c r="N864" s="4" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="865" spans="1:14">
+      <c r="A865">
+        <v>869</v>
+      </c>
+      <c r="B865" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C865" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D865" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E865" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F865" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G865" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H865" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I865" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J865" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K865" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L865" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M865" s="3" t="s">
+        <v>2141</v>
+      </c>
+      <c r="N865" s="4" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="866" spans="1:14">
+      <c r="A866">
+        <v>870</v>
+      </c>
+      <c r="B866" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C866" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D866" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E866" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F866" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G866" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H866" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I866" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J866" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K866" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L866" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M866" s="3" t="s">
+        <v>2144</v>
+      </c>
+      <c r="N866" s="4" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="867" spans="1:14">
+      <c r="A867">
+        <v>871</v>
+      </c>
+      <c r="B867" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C867" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D867" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E867" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F867" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G867" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H867" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I867" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J867" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K867" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L867" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M867" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="N867" s="4" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="868" spans="1:14">
+      <c r="A868">
+        <v>872</v>
+      </c>
+      <c r="B868" s="1" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C868" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D868" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E868" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F868" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G868" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H868" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I868" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J868" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K868" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L868" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M868" s="3" t="s">
+        <v>2150</v>
+      </c>
+      <c r="N868" s="4" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="869" spans="1:14">
+      <c r="A869">
+        <v>873</v>
+      </c>
+      <c r="B869" s="1" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C869" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D869" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E869" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F869" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G869" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H869" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I869" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J869" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K869" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L869" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M869" s="3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="N869" s="4" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="870" spans="1:14">
+      <c r="A870">
+        <v>874</v>
+      </c>
+      <c r="B870" s="1" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C870" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D870" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E870" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F870" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G870" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H870" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I870" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J870" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K870" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L870" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M870" s="3" t="s">
+        <v>2156</v>
+      </c>
+      <c r="N870" s="4" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="871" spans="1:14">
+      <c r="A871">
+        <v>875</v>
+      </c>
+      <c r="B871" s="1" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C871" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D871" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E871" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F871" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G871" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H871" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I871" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J871" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K871" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L871" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M871" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="N871" s="4" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="872" spans="1:14">
+      <c r="A872">
+        <v>876</v>
+      </c>
+      <c r="B872" s="1" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C872" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D872" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E872" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F872" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G872" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H872" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I872" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J872" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K872" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L872" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M872" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="N872" s="4" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="873" spans="1:14">
+      <c r="A873">
+        <v>877</v>
+      </c>
+      <c r="B873" s="1" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C873" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D873" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E873" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F873" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G873" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H873" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I873" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J873" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K873" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L873" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M873" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="N873" s="4" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="874" spans="1:14">
+      <c r="A874">
+        <v>878</v>
+      </c>
+      <c r="B874" s="1" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C874" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D874" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E874" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F874" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G874" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H874" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I874" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J874" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K874" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L874" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M874" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="N874" s="4" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="875" spans="1:14">
+      <c r="A875">
+        <v>879</v>
+      </c>
+      <c r="B875" s="1" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C875" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D875" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E875" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F875" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G875" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H875" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I875" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J875" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K875" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L875" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M875" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="N875" s="4" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="876" spans="1:14">
+      <c r="A876">
+        <v>880</v>
+      </c>
+      <c r="B876" s="1" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C876" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D876" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E876" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F876" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G876" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H876" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I876" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J876" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K876" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L876" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M876" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N876" s="4" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="877" spans="1:14">
+      <c r="A877">
+        <v>881</v>
+      </c>
+      <c r="B877" s="1" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C877" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D877" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E877" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F877" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G877" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H877" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I877" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J877" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K877" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L877" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M877" s="3" t="s">
+        <v>2174</v>
+      </c>
+      <c r="N877" s="4" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="878" spans="1:14">
+      <c r="A878">
+        <v>882</v>
+      </c>
+      <c r="B878" s="1" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C878" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D878" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E878" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F878" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G878" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H878" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I878" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J878" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K878" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L878" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M878" s="3" t="s">
+        <v>2177</v>
+      </c>
+      <c r="N878" s="4" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="879" spans="1:14">
+      <c r="A879">
+        <v>883</v>
+      </c>
+      <c r="B879" s="1" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C879" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D879" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E879" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F879" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G879" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H879" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I879" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J879" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K879" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L879" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M879" s="3" t="s">
+        <v>2180</v>
+      </c>
+      <c r="N879" s="4" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="880" spans="1:14">
+      <c r="A880">
+        <v>884</v>
+      </c>
+      <c r="B880" s="1" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C880" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D880" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E880" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F880" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G880" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H880" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I880" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J880" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K880" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L880" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M880" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N880" s="4" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="881" spans="1:14">
+      <c r="A881">
+        <v>885</v>
+      </c>
+      <c r="B881" s="1" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C881" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D881" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E881" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F881" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G881" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H881" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I881" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J881" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K881" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L881" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M881" s="3" t="s">
+        <v>2185</v>
+      </c>
+      <c r="N881" s="4" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="882" spans="1:14">
+      <c r="A882">
+        <v>886</v>
+      </c>
+      <c r="B882" s="1" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C882" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D882" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E882" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F882" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G882" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H882" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I882" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J882" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K882" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L882" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M882" s="3" t="s">
+        <v>2188</v>
+      </c>
+      <c r="N882" s="4" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="883" spans="1:14">
+      <c r="A883">
+        <v>887</v>
+      </c>
+      <c r="B883" s="1" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C883" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D883" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E883" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F883" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G883" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H883" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I883" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J883" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K883" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L883" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M883" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N883" s="4" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="884" spans="1:14">
+      <c r="A884">
+        <v>888</v>
+      </c>
+      <c r="B884" s="1" t="s">
+        <v>2192</v>
+      </c>
+      <c r="C884" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D884" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E884" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F884" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G884" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H884" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I884" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J884" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K884" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L884" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M884" s="3" t="s">
+        <v>2193</v>
+      </c>
+      <c r="N884" s="4" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="885" spans="1:14">
+      <c r="A885">
+        <v>889</v>
+      </c>
+      <c r="B885" s="1" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C885" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D885" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E885" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F885" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G885" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H885" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I885" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J885" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K885" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L885" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M885" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="N885" s="4" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="886" spans="1:14">
+      <c r="A886">
+        <v>890</v>
+      </c>
+      <c r="B886" s="1" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C886" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D886" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E886" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F886" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G886" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H886" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I886" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J886" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K886" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L886" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M886" s="3" t="s">
+        <v>2199</v>
+      </c>
+      <c r="N886" s="4" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="887" spans="1:14">
+      <c r="A887">
+        <v>891</v>
+      </c>
+      <c r="B887" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C887" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D887" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E887" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F887" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G887" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H887" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I887" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J887" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K887" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L887" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M887" s="3" t="s">
+        <v>2203</v>
+      </c>
+      <c r="N887" s="4" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="888" spans="1:14">
+      <c r="A888">
+        <v>892</v>
+      </c>
+      <c r="B888" s="1" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C888" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D888" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E888" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F888" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G888" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H888" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I888" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J888" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K888" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L888" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M888" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N888" s="4" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="889" spans="1:14">
+      <c r="A889">
+        <v>893</v>
+      </c>
+      <c r="B889" s="1" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C889" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D889" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E889" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F889" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G889" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H889" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I889" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J889" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K889" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L889" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M889" s="3" t="s">
+        <v>2208</v>
+      </c>
+      <c r="N889" s="4" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="890" spans="1:14">
+      <c r="A890">
+        <v>894</v>
+      </c>
+      <c r="B890" s="1" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C890" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D890" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E890" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F890" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G890" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H890" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I890" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J890" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K890" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L890" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M890" s="3" t="s">
+        <v>2211</v>
+      </c>
+      <c r="N890" s="4" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="891" spans="1:14">
+      <c r="A891">
+        <v>895</v>
+      </c>
+      <c r="B891" s="1" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C891" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D891" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E891" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F891" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G891" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H891" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I891" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J891" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K891" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L891" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M891" s="3" t="s">
+        <v>2214</v>
+      </c>
+      <c r="N891" s="4" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="892" spans="1:14">
+      <c r="A892">
+        <v>896</v>
+      </c>
+      <c r="B892" s="1" t="s">
+        <v>2216</v>
+      </c>
+      <c r="C892" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D892" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E892" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F892" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G892" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H892" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I892" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J892" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K892" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L892" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M892" s="3" t="s">
+        <v>2217</v>
+      </c>
+      <c r="N892" s="4" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="893" spans="1:14">
+      <c r="A893">
+        <v>897</v>
+      </c>
+      <c r="B893" s="1" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C893" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D893" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E893" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F893" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G893" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H893" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I893" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J893" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K893" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L893" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M893" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N893" s="4" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="894" spans="1:14">
+      <c r="A894">
+        <v>898</v>
+      </c>
+      <c r="B894" s="1" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C894" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D894" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E894" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F894" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G894" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H894" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I894" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J894" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K894" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L894" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M894" s="3" t="s">
+        <v>2222</v>
+      </c>
+      <c r="N894" s="4" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="895" spans="1:14">
+      <c r="A895">
+        <v>899</v>
+      </c>
+      <c r="B895" s="1" t="s">
+        <v>2224</v>
+      </c>
+      <c r="C895" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D895" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E895" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F895" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G895" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H895" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I895" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J895" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K895" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L895" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M895" s="3" t="s">
+        <v>2225</v>
+      </c>
+      <c r="N895" s="4" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="896" spans="1:14">
+      <c r="A896">
+        <v>900</v>
+      </c>
+      <c r="B896" s="1" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C896" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D896" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E896" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F896" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G896" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H896" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I896" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J896" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K896" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L896" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M896" s="3" t="s">
+        <v>2228</v>
+      </c>
+      <c r="N896" s="4" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="897" spans="1:14">
+      <c r="A897">
+        <v>901</v>
+      </c>
+      <c r="B897" s="1" t="s">
+        <v>2230</v>
+      </c>
+      <c r="C897" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D897" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E897" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F897" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G897" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H897" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I897" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J897" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K897" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L897" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M897" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N897" s="4" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="898" spans="1:14">
+      <c r="A898">
+        <v>902</v>
+      </c>
+      <c r="B898" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="C898" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D898" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E898" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F898" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G898" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H898" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I898" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J898" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K898" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L898" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M898" s="3" t="s">
+        <v>2233</v>
+      </c>
+      <c r="N898" s="4" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="899" spans="1:14">
+      <c r="A899">
+        <v>903</v>
+      </c>
+      <c r="B899" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C899" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D899" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E899" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F899" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G899" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H899" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I899" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J899" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K899" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L899" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M899" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N899" s="4" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="900" spans="1:14">
+      <c r="A900">
+        <v>904</v>
+      </c>
+      <c r="B900" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C900" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D900" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E900" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F900" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G900" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H900" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I900" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J900" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K900" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L900" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M900" s="3" t="s">
+        <v>2238</v>
+      </c>
+      <c r="N900" s="4" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="901" spans="1:14">
+      <c r="A901">
+        <v>905</v>
+      </c>
+      <c r="B901" s="1" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C901" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D901" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E901" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F901" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G901" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H901" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I901" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J901" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K901" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L901" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M901" s="3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="N901" s="4" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="902" spans="1:14">
+      <c r="A902">
+        <v>906</v>
+      </c>
+      <c r="B902" s="1" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C902" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D902" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E902" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F902" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G902" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H902" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I902" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J902" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K902" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L902" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M902" s="3" t="s">
+        <v>2243</v>
+      </c>
+      <c r="N902" s="4" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="903" spans="1:14">
+      <c r="A903">
+        <v>907</v>
+      </c>
+      <c r="B903" s="1" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C903" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D903" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E903" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F903" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G903" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H903" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I903" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J903" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K903" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L903" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M903" s="3" t="s">
+        <v>2246</v>
+      </c>
+      <c r="N903" s="4" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="904" spans="1:14">
+      <c r="A904">
+        <v>908</v>
+      </c>
+      <c r="B904" s="1" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C904" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D904" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E904" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F904" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G904" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H904" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I904" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J904" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K904" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L904" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M904" s="3" t="s">
+        <v>2249</v>
+      </c>
+      <c r="N904" s="4" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="905" spans="1:14">
+      <c r="A905">
+        <v>909</v>
+      </c>
+      <c r="B905" s="1" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C905" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D905" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E905" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F905" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G905" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H905" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I905" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J905" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K905" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L905" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M905" s="3" t="s">
+        <v>2252</v>
+      </c>
+      <c r="N905" s="4" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="906" spans="1:14">
+      <c r="A906">
+        <v>910</v>
+      </c>
+      <c r="B906" s="1" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C906" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D906" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E906" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F906" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G906" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H906" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I906" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J906" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K906" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L906" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M906" s="3" t="s">
+        <v>2255</v>
+      </c>
+      <c r="N906" s="4" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="907" spans="1:14">
+      <c r="A907">
+        <v>911</v>
+      </c>
+      <c r="B907" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C907" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D907" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E907" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F907" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G907" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H907" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I907" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J907" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K907" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L907" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M907" s="3" t="s">
+        <v>2258</v>
+      </c>
+      <c r="N907" s="4" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="908" spans="1:14">
+      <c r="A908">
+        <v>912</v>
+      </c>
+      <c r="B908" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C908" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D908" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E908" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F908" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G908" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H908" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I908" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J908" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K908" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L908" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M908" s="3" t="s">
+        <v>2261</v>
+      </c>
+      <c r="N908" s="4" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="909" spans="1:14">
+      <c r="A909">
+        <v>913</v>
+      </c>
+      <c r="B909" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C909" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D909" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E909" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F909" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G909" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H909" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I909" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J909" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K909" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L909" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M909" s="3" t="s">
+        <v>2264</v>
+      </c>
+      <c r="N909" s="4" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="910" spans="1:14">
+      <c r="A910">
+        <v>914</v>
+      </c>
+      <c r="B910" s="1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C910" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D910" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E910" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F910" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G910" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H910" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I910" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J910" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K910" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L910" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M910" s="3" t="s">
+        <v>2267</v>
+      </c>
+      <c r="N910" s="4" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="911" spans="1:14">
+      <c r="A911">
+        <v>915</v>
+      </c>
+      <c r="B911" s="1" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C911" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D911" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E911" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F911" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G911" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H911" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I911" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J911" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K911" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L911" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M911" s="3" t="s">
+        <v>2270</v>
+      </c>
+      <c r="N911" s="4" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="912" spans="1:14">
+      <c r="A912">
+        <v>917</v>
+      </c>
+      <c r="B912" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C912" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D912" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E912" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F912" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G912" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H912" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I912" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J912" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K912" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L912" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M912" s="3" t="s">
+        <v>2273</v>
+      </c>
+      <c r="N912" s="4" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="913" spans="1:14">
+      <c r="A913">
+        <v>916</v>
+      </c>
+      <c r="B913" s="1" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C913" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D913" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E913" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F913" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G913" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H913" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I913" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J913" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K913" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L913" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M913" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="N913" s="4" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="914" spans="1:14">
+      <c r="A914">
+        <v>918</v>
+      </c>
+      <c r="B914" s="1" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C914" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D914" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E914" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F914" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G914" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H914" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I914" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J914" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K914" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L914" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M914" s="3" t="s">
+        <v>2279</v>
+      </c>
+      <c r="N914" s="4" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="915" spans="1:14">
+      <c r="A915">
+        <v>919</v>
+      </c>
+      <c r="B915" s="1" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C915" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D915" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E915" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F915" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G915" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H915" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I915" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J915" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K915" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L915" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M915" s="3" t="s">
+        <v>2282</v>
+      </c>
+      <c r="N915" s="4" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="916" spans="1:14">
+      <c r="A916">
+        <v>920</v>
+      </c>
+      <c r="B916" s="1" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C916" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D916" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E916" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F916" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G916" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H916" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I916" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J916" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K916" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L916" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M916" s="3" t="s">
+        <v>2285</v>
+      </c>
+      <c r="N916" s="4" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="917" spans="1:14">
+      <c r="A917">
+        <v>921</v>
+      </c>
+      <c r="B917" s="1" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C917" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D917" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E917" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F917" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G917" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H917" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I917" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J917" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K917" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L917" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M917" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="N917" s="4" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="918" spans="1:14">
+      <c r="A918">
+        <v>922</v>
+      </c>
+      <c r="B918" s="1" t="s">
+        <v>2290</v>
+      </c>
+      <c r="C918" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D918" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E918" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F918" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G918" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H918" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I918" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J918" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K918" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L918" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M918" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="N918" s="4" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="919" spans="1:14">
+      <c r="A919">
+        <v>923</v>
+      </c>
+      <c r="B919" s="1" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C919" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D919" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E919" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F919" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G919" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H919" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I919" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J919" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K919" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L919" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M919" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="N919" s="4" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="920" spans="1:14">
+      <c r="A920">
+        <v>925</v>
+      </c>
+      <c r="B920" s="1" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C920" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D920" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E920" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F920" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G920" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H920" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I920" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J920" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K920" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L920" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M920" s="3" t="s">
+        <v>2297</v>
+      </c>
+      <c r="N920" s="4" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="921" spans="1:14">
+      <c r="A921">
+        <v>924</v>
+      </c>
+      <c r="B921" s="1" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C921" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D921" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E921" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F921" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G921" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H921" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I921" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J921" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K921" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L921" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M921" s="3" t="s">
+        <v>2300</v>
+      </c>
+      <c r="N921" s="4" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="922" spans="1:14">
+      <c r="A922">
+        <v>926</v>
+      </c>
+      <c r="B922" s="1" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C922" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D922" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E922" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F922" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G922" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H922" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I922" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J922" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K922" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L922" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M922" s="3" t="s">
+        <v>2303</v>
+      </c>
+      <c r="N922" s="4" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="923" spans="1:14">
+      <c r="A923">
+        <v>927</v>
+      </c>
+      <c r="B923" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C923" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D923" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E923" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F923" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G923" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H923" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I923" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J923" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K923" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L923" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M923" s="3" t="s">
+        <v>1608</v>
+      </c>
+      <c r="N923" s="4" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="924" spans="1:14">
+      <c r="A924">
+        <v>928</v>
+      </c>
+      <c r="B924" s="1" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C924" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D924" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E924" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F924" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G924" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H924" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I924" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J924" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K924" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L924" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M924" s="3" t="s">
+        <v>2309</v>
+      </c>
+      <c r="N924" s="4" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="925" spans="1:14">
+      <c r="A925">
+        <v>929</v>
+      </c>
+      <c r="B925" s="1" t="s">
+        <v>2311</v>
+      </c>
+      <c r="C925" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D925" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E925" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F925" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G925" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H925" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I925" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J925" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K925" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L925" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M925" s="3" t="s">
+        <v>2312</v>
+      </c>
+      <c r="N925" s="4" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="926" spans="1:14">
+      <c r="A926">
+        <v>930</v>
+      </c>
+      <c r="B926" s="1" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C926" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D926" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E926" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F926" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G926" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H926" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I926" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J926" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K926" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L926" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M926" s="3" t="s">
+        <v>2315</v>
+      </c>
+      <c r="N926" s="4" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="927" spans="1:14">
+      <c r="A927">
+        <v>931</v>
+      </c>
+      <c r="B927" s="1" t="s">
+        <v>2317</v>
+      </c>
+      <c r="C927" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D927" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E927" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F927" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G927" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H927" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I927" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J927" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K927" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L927" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M927" s="3" t="s">
+        <v>2020</v>
+      </c>
+      <c r="N927" s="4" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="928" spans="1:14">
+      <c r="A928">
+        <v>932</v>
+      </c>
+      <c r="B928" s="1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C928" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D928" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E928" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F928" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G928" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H928" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I928" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J928" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K928" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L928" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M928" s="3" t="s">
+        <v>2320</v>
+      </c>
+      <c r="N928" s="4" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="929" spans="1:14">
+      <c r="A929">
+        <v>933</v>
+      </c>
+      <c r="B929" s="1" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C929" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D929" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E929" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F929" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G929" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H929" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I929" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J929" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K929" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L929" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M929" s="3" t="s">
+        <v>2323</v>
+      </c>
+      <c r="N929" s="4" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="930" spans="1:14">
+      <c r="A930">
+        <v>934</v>
+      </c>
+      <c r="B930" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C930" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D930" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E930" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F930" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G930" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H930" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I930" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J930" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K930" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L930" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M930" s="3" t="s">
+        <v>2326</v>
+      </c>
+      <c r="N930" s="4" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="931" spans="1:14">
+      <c r="A931">
+        <v>935</v>
+      </c>
+      <c r="B931" s="1" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C931" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D931" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E931" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F931" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G931" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H931" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I931" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J931" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K931" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L931" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M931" s="3" t="s">
+        <v>2329</v>
+      </c>
+      <c r="N931" s="4" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="932" spans="1:14">
+      <c r="A932">
+        <v>936</v>
+      </c>
+      <c r="B932" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="C932" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D932" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E932" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F932" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G932" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H932" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I932" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J932" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K932" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L932" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M932" s="3" t="s">
+        <v>2332</v>
+      </c>
+      <c r="N932" s="4" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="933" spans="1:14">
+      <c r="A933">
+        <v>937</v>
+      </c>
+      <c r="B933" s="1" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C933" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D933" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E933" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F933" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G933" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H933" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I933" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J933" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K933" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L933" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M933" s="3" t="s">
+        <v>2335</v>
+      </c>
+      <c r="N933" s="4" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="934" spans="1:14">
+      <c r="A934">
+        <v>938</v>
+      </c>
+      <c r="B934" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="C934" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D934" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E934" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F934" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G934" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H934" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I934" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J934" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K934" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L934" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M934" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N934" s="4" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="935" spans="1:14">
+      <c r="A935">
+        <v>940</v>
+      </c>
+      <c r="B935" s="1" t="s">
+        <v>2339</v>
+      </c>
+      <c r="C935" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D935" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E935" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F935" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G935" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H935" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I935" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J935" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K935" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L935" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M935" s="3" t="s">
+        <v>2340</v>
+      </c>
+      <c r="N935" s="4" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="936" spans="1:14">
+      <c r="A936">
+        <v>939</v>
+      </c>
+      <c r="B936" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="C936" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D936" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E936" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F936" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G936" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H936" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I936" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J936" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K936" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L936" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M936" s="3" t="s">
+        <v>2343</v>
+      </c>
+      <c r="N936" s="4" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="937" spans="1:14">
+      <c r="A937">
+        <v>941</v>
+      </c>
+      <c r="B937" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C937" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D937" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E937" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F937" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G937" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H937" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I937" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J937" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K937" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L937" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M937" s="3" t="s">
+        <v>2346</v>
+      </c>
+      <c r="N937" s="4" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="938" spans="1:14">
+      <c r="A938">
+        <v>942</v>
+      </c>
+      <c r="B938" s="1" t="s">
+        <v>2348</v>
+      </c>
+      <c r="C938" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D938" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E938" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F938" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G938" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H938" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I938" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J938" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K938" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L938" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M938" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="N938" s="4" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="939" spans="1:14">
+      <c r="A939">
+        <v>943</v>
+      </c>
+      <c r="B939" s="1" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C939" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D939" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E939" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F939" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G939" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H939" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I939" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J939" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K939" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L939" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M939" s="3" t="s">
+        <v>2352</v>
+      </c>
+      <c r="N939" s="4" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="940" spans="1:14">
+      <c r="A940">
+        <v>944</v>
+      </c>
+      <c r="B940" s="1" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C940" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D940" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E940" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F940" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G940" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H940" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I940" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J940" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K940" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L940" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M940" s="3" t="s">
+        <v>2355</v>
+      </c>
+      <c r="N940" s="4" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="941" spans="1:14">
+      <c r="A941">
+        <v>945</v>
+      </c>
+      <c r="B941" s="1" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C941" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D941" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E941" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F941" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G941" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H941" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I941" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J941" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K941" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L941" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M941" s="3" t="s">
+        <v>2358</v>
+      </c>
+      <c r="N941" s="4" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="942" spans="1:14">
+      <c r="A942">
+        <v>946</v>
+      </c>
+      <c r="B942" s="1" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C942" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D942" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E942" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F942" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G942" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H942" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I942" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J942" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K942" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L942" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M942" s="3" t="s">
+        <v>2361</v>
+      </c>
+      <c r="N942" s="4" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="943" spans="1:14">
+      <c r="A943">
+        <v>947</v>
+      </c>
+      <c r="B943" s="1" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C943" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D943" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E943" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F943" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G943" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H943" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I943" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J943" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K943" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L943" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M943" s="3" t="s">
+        <v>2364</v>
+      </c>
+      <c r="N943" s="4" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="944" spans="1:14">
+      <c r="A944">
+        <v>948</v>
+      </c>
+      <c r="B944" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="C944" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D944" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E944" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F944" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G944" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H944" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I944" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J944" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K944" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L944" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M944" s="3" t="s">
+        <v>2367</v>
+      </c>
+      <c r="N944" s="4" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="945" spans="1:14">
+      <c r="A945">
+        <v>949</v>
+      </c>
+      <c r="B945" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C945" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D945" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E945" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F945" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G945" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H945" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I945" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J945" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K945" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L945" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M945" s="3" t="s">
+        <v>2370</v>
+      </c>
+      <c r="N945" s="4" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="946" spans="1:14">
+      <c r="A946">
+        <v>950</v>
+      </c>
+      <c r="B946" s="1" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C946" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D946" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E946" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F946" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G946" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H946" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I946" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J946" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K946" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L946" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M946" s="3" t="s">
+        <v>2373</v>
+      </c>
+      <c r="N946" s="4" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="947" spans="1:14">
+      <c r="A947">
+        <v>951</v>
+      </c>
+      <c r="B947" s="1" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C947" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D947" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E947" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F947" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G947" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H947" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I947" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J947" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K947" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L947" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M947" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N947" s="4" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="948" spans="1:14">
+      <c r="A948">
+        <v>953</v>
+      </c>
+      <c r="B948" s="1" t="s">
+        <v>2377</v>
+      </c>
+      <c r="C948" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D948" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E948" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F948" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G948" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H948" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I948" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J948" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K948" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L948" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M948" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="N948" s="4" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="949" spans="1:14">
+      <c r="A949">
+        <v>952</v>
+      </c>
+      <c r="B949" s="1" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C949" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D949" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E949" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F949" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G949" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H949" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I949" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J949" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K949" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L949" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M949" s="3" t="s">
+        <v>2380</v>
+      </c>
+      <c r="N949" s="4" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="950" spans="1:14">
+      <c r="A950">
+        <v>954</v>
+      </c>
+      <c r="B950" s="1" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C950" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D950" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E950" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F950" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G950" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H950" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I950" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J950" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K950" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L950" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M950" s="3" t="s">
+        <v>2383</v>
+      </c>
+      <c r="N950" s="4" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="951" spans="1:14">
+      <c r="A951">
+        <v>955</v>
+      </c>
+      <c r="B951" s="1" t="s">
+        <v>2385</v>
+      </c>
+      <c r="C951" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D951" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E951" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F951" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G951" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H951" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I951" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J951" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K951" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L951" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M951" s="3" t="s">
+        <v>2386</v>
+      </c>
+      <c r="N951" s="4" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="952" spans="1:14">
+      <c r="A952">
+        <v>956</v>
+      </c>
+      <c r="B952" s="1" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C952" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D952" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E952" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F952" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G952" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H952" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I952" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J952" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K952" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L952" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M952" s="3" t="s">
+        <v>2389</v>
+      </c>
+      <c r="N952" s="4" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="953" spans="1:14">
+      <c r="A953">
+        <v>957</v>
+      </c>
+      <c r="B953" s="1" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C953" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D953" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E953" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F953" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G953" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H953" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I953" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J953" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K953" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L953" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M953" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N953" s="4" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="954" spans="1:14">
+      <c r="A954">
+        <v>958</v>
+      </c>
+      <c r="B954" s="1" t="s">
+        <v>2393</v>
+      </c>
+      <c r="C954" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D954" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E954" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F954" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G954" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H954" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I954" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J954" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K954" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L954" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M954" s="3" t="s">
+        <v>2394</v>
+      </c>
+      <c r="N954" s="4" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="955" spans="1:14">
+      <c r="A955">
+        <v>959</v>
+      </c>
+      <c r="B955" s="1" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C955" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D955" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E955" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F955" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G955" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H955" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I955" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J955" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K955" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L955" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M955" s="3" t="s">
+        <v>2397</v>
+      </c>
+      <c r="N955" s="4" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="956" spans="1:14">
+      <c r="A956">
+        <v>960</v>
+      </c>
+      <c r="B956" s="1" t="s">
+        <v>2399</v>
+      </c>
+      <c r="C956" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D956" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E956" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F956" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G956" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H956" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I956" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J956" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K956" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L956" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M956" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="N956" s="4" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="957" spans="1:14">
+      <c r="A957">
+        <v>961</v>
+      </c>
+      <c r="B957" s="1" t="s">
+        <v>2401</v>
+      </c>
+      <c r="C957" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D957" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E957" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F957" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G957" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H957" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I957" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J957" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K957" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L957" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M957" s="3" t="s">
+        <v>2402</v>
+      </c>
+      <c r="N957" s="4" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="958" spans="1:14">
+      <c r="A958">
+        <v>962</v>
+      </c>
+      <c r="B958" s="1" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C958" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D958" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E958" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F958" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G958" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H958" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I958" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J958" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K958" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L958" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M958" s="3" t="s">
+        <v>2405</v>
+      </c>
+      <c r="N958" s="4" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="959" spans="1:14">
+      <c r="A959">
+        <v>963</v>
+      </c>
+      <c r="B959" s="1" t="s">
+        <v>2407</v>
+      </c>
+      <c r="C959" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D959" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E959" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F959" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G959" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H959" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I959" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J959" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K959" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L959" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M959" s="3" t="s">
+        <v>2408</v>
+      </c>
+      <c r="N959" s="4" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="960" spans="1:14">
+      <c r="A960">
+        <v>965</v>
+      </c>
+      <c r="B960" s="1" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C960" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D960" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E960" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F960" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G960" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H960" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I960" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J960" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K960" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L960" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M960" s="3" t="s">
+        <v>2411</v>
+      </c>
+      <c r="N960" s="4" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="961" spans="1:14">
+      <c r="A961">
+        <v>964</v>
+      </c>
+      <c r="B961" s="1" t="s">
+        <v>2413</v>
+      </c>
+      <c r="C961" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D961" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E961" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F961" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G961" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H961" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I961" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J961" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K961" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L961" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M961" s="3" t="s">
+        <v>2414</v>
+      </c>
+      <c r="N961" s="4" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="962" spans="1:14">
+      <c r="A962">
+        <v>966</v>
+      </c>
+      <c r="B962" s="1" t="s">
+        <v>2416</v>
+      </c>
+      <c r="C962" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D962" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E962" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F962" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G962" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H962" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I962" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J962" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K962" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L962" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M962" s="3" t="s">
+        <v>2417</v>
+      </c>
+      <c r="N962" s="4" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="963" spans="1:14">
+      <c r="A963">
+        <v>967</v>
+      </c>
+      <c r="B963" s="1" t="s">
+        <v>2419</v>
+      </c>
+      <c r="C963" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D963" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E963" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F963" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G963" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H963" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I963" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J963" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K963" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L963" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M963" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="N963" s="4" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="964" spans="1:14">
+      <c r="A964">
+        <v>968</v>
+      </c>
+      <c r="B964" s="1" t="s">
+        <v>2421</v>
+      </c>
+      <c r="C964" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D964" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E964" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F964" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G964" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H964" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I964" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J964" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K964" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L964" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M964" s="3" t="s">
+        <v>2422</v>
+      </c>
+      <c r="N964" s="4" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="965" spans="1:14">
+      <c r="A965">
+        <v>969</v>
+      </c>
+      <c r="B965" s="1" t="s">
+        <v>2424</v>
+      </c>
+      <c r="C965" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D965" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E965" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F965" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G965" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H965" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I965" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J965" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K965" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L965" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M965" s="3" t="s">
+        <v>2425</v>
+      </c>
+      <c r="N965" s="4" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="966" spans="1:14">
+      <c r="A966">
+        <v>970</v>
+      </c>
+      <c r="B966" s="1" t="s">
+        <v>2427</v>
+      </c>
+      <c r="C966" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D966" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E966" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F966" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G966" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H966" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I966" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J966" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K966" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L966" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M966" s="3" t="s">
+        <v>2428</v>
+      </c>
+      <c r="N966" s="4" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="967" spans="1:14">
+      <c r="A967">
+        <v>971</v>
+      </c>
+      <c r="B967" s="1" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C967" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D967" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E967" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F967" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G967" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H967" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I967" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J967" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K967" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L967" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M967" s="3" t="s">
+        <v>2431</v>
+      </c>
+      <c r="N967" s="4" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="968" spans="1:14">
+      <c r="A968">
+        <v>972</v>
+      </c>
+      <c r="B968" s="1" t="s">
+        <v>2433</v>
+      </c>
+      <c r="C968" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D968" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E968" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F968" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G968" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H968" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I968" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J968" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K968" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L968" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M968" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="N968" s="4" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="969" spans="1:14">
+      <c r="A969" s="5">
+        <v>973</v>
+      </c>
+      <c r="B969" s="1" t="s">
+        <v>2435</v>
+      </c>
+      <c r="C969" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D969" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E969" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F969" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G969" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H969" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I969" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J969" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K969" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L969" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M969" s="3" t="s">
+        <v>2436</v>
+      </c>
+      <c r="N969" s="4" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="970" spans="1:14">
+      <c r="A970" s="5">
+        <v>974</v>
+      </c>
+      <c r="B970" s="1" t="s">
+        <v>2438</v>
+      </c>
+      <c r="C970" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D970" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E970" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F970" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G970" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H970" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I970" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J970" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K970" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L970" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M970" s="3" t="s">
+        <v>2439</v>
+      </c>
+      <c r="N970" s="4" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="971" spans="1:14">
+      <c r="A971" s="5">
+        <v>975</v>
+      </c>
+      <c r="B971" s="1" t="s">
+        <v>2441</v>
+      </c>
+      <c r="C971" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D971" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E971" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F971" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G971" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H971" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I971" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J971" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K971" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L971" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M971" s="3" t="s">
+        <v>2442</v>
+      </c>
+      <c r="N971" s="4" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="972" spans="1:14">
+      <c r="A972" s="5">
+        <v>976</v>
+      </c>
+      <c r="B972" s="1" t="s">
+        <v>2444</v>
+      </c>
+      <c r="C972" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D972" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E972" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F972" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G972" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H972" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I972" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J972" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K972" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L972" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M972" s="3" t="s">
+        <v>2445</v>
+      </c>
+      <c r="N972" s="4" t="s">
+        <v>2446</v>
       </c>
     </row>
   </sheetData>

--- a/PeerGrading/Input/form_exports/forms_responses.xlsx
+++ b/PeerGrading/Input/form_exports/forms_responses.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzh-my.sharepoint.com/personal/renjie_cui_business_uzh_ch/Documents/PeerGrading/Input/form_exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1128" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC54C41F-E6C2-4ABD-86A8-4A5071B58DE8}"/>
+  <xr:revisionPtr revIDLastSave="1220" documentId="8_{9C3C9BE7-B8B4-430B-A3DC-C1A29F196D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C32DB48F-1224-445E-9BB2-63198E218EA1}"/>
   <bookViews>
     <workbookView xWindow="17280" yWindow="-16200" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21739" uniqueCount="4502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23234" uniqueCount="4823">
   <si>
     <t>Responseid</t>
   </si>
@@ -13542,6 +13542,969 @@
   </si>
   <si>
     <t>2026-04-17T19:50:14.4732393Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:07:43.1090315Z</t>
+  </si>
+  <si>
+    <t>Anna-Lea	Wölfle</t>
+  </si>
+  <si>
+    <t>Nice Slides, Fluent spoken</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:07:43.1090726Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:07:54.0423384Z</t>
+  </si>
+  <si>
+    <t>good overview</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:07:54.0423790Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:07:56.4332002Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beautiful slides, good explanation of the topic and clear speaking </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:07:56.4332414Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:08:31.6195560Z</t>
+  </si>
+  <si>
+    <t>great</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:08:31.6195963Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:09:03.3798565Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Well organized slides. Well done addressing the questions from olat </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:09:03.3798988Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:08.3949148Z</t>
+  </si>
+  <si>
+    <t>good structure, nice data visuals</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:08.3949547Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:12.6903126Z</t>
+  </si>
+  <si>
+    <t>Great presentation.</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:12.6903798Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:12.6924751Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thnak you for your presentation. You spoke at the right speed. </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:12.6925159Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:13.2635739Z</t>
+  </si>
+  <si>
+    <t>Nice Slides, very confidently spoken, yet the presentation would benefit from a more freely spoken form</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:13.2636136Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:13.9683081Z</t>
+  </si>
+  <si>
+    <t>Interesting topics, with good answers to the questions from Olat!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:13.9683495Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:14.1896992Z</t>
+  </si>
+  <si>
+    <t>excellent presentation!!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:14.1897396Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:14.4827065Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:14.4827481Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:15.6493537Z</t>
+  </si>
+  <si>
+    <t>Very good and interesting</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:15.6493976Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:20.1461056Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:20.1461840Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:22.4832533Z</t>
+  </si>
+  <si>
+    <t>Great presentation!!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:22.4833230Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:23.7096503Z</t>
+  </si>
+  <si>
+    <t>Speak a bit more freely</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:23.7096923Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:27.7242465Z</t>
+  </si>
+  <si>
+    <t>well explained and clear voice - great job!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:27.7242884Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:29.2487363Z</t>
+  </si>
+  <si>
+    <t>Great confident presentation, thank you!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:29.2487781Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:31.8162320Z</t>
+  </si>
+  <si>
+    <t>I liked the information you provided, speak up a little next time</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:31.8163058Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:32.5479982Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice visuals on the slides and topic was well explained </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:32.5480384Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:33.1641730Z</t>
+  </si>
+  <si>
+    <t>good presentation style, bit crowded slides.</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:33.1642442Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:36.8031627Z</t>
+  </si>
+  <si>
+    <t>Well done :)</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:36.8032237Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:37.6941933Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:37.6942347Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:41.0620908Z</t>
+  </si>
+  <si>
+    <t>I really liked the slideshow and this was a good presentation</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:41.0621306Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:45.0243769Z</t>
+  </si>
+  <si>
+    <t>Great presentation and nicely designed slides</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:10:45.0244179Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:02.7957403Z</t>
+  </si>
+  <si>
+    <t>Great presentation. It could have been slightly more "freely spoken" and less by heart</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:02.7957805Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:21.2244196Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear and well structured presentation. Interesting topic and the presenter was engaging </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:21.2244965Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:26.5722501Z</t>
+  </si>
+  <si>
+    <t>The topic was well explained, within time and adresses olat questions as well</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:26.5722918Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:26.6678249Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:26.6678938Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:29.7632149Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:29.7632636Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:30.9486099Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good free talking </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:30.9486608Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:31.9584542Z</t>
+  </si>
+  <si>
+    <t>Stefanie	Rüde</t>
+  </si>
+  <si>
+    <t>good volume</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:31.9585000Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:58.2063821Z</t>
+  </si>
+  <si>
+    <t>Excellent pace was easy to follow</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:11:58.2064227Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:12:12.8209507Z</t>
+  </si>
+  <si>
+    <t>solid</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:12:12.8209945Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:12:24.3435527Z</t>
+  </si>
+  <si>
+    <t>Interesting topic, straight to the point, beautiful slides. slay.</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:12:24.3436255Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:12:34.1881145Z</t>
+  </si>
+  <si>
+    <t>Really nice slides, good explanation of the topic, presentation style was really it showed that you were really good informed in the topic</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:12:34.1881562Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:13:21.7578841Z</t>
+  </si>
+  <si>
+    <t>Slowly spoken, Maybe use a bit more pictures on slides</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:13:21.7579273Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:14:01.3272223Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:14:01.3272714Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:14:28.0299436Z</t>
+  </si>
+  <si>
+    <t>Interesting topic and well spoken</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:14:28.0299931Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:00.3287574Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good examples and well explained topic. </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:00.3288089Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:07.0026117Z</t>
+  </si>
+  <si>
+    <t>good information, too much text on slides</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:07.0026596Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:08.3363706Z</t>
+  </si>
+  <si>
+    <t>Structured slides</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:08.3364285Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:08.9644006Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:08.9644519Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:09.3053101Z</t>
+  </si>
+  <si>
+    <t>Good exemples, a lot of text on the slides though, thank you for the presentation!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:09.3053598Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:09.6373609Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great presentation. </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:09.6374314Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:10.0196016Z</t>
+  </si>
+  <si>
+    <t>good structure, sensible slides</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:10.0196406Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:11.2346374Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">read the slides too much </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:11.2346827Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:12.2522981Z</t>
+  </si>
+  <si>
+    <t>Nice slides, kind of missing the sources</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:12.2523387Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:12.5068503Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:12.5068960Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:14.6176033Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:14.6176800Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:15.6148487Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">try to be more engaging and maybe involve some graphs/images not just text on the slides </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:15.6148900Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:15.7373480Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:15.7374015Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:15.7581330Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good presentation, the questions were adressed precisely </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:15.7581844Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:20.1090006Z</t>
+  </si>
+  <si>
+    <t>Thnak you for this interesting presentation !</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:20.1090506Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:26.6884438Z</t>
+  </si>
+  <si>
+    <t>Very good, thank you!!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:26.6884847Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:26.7887099Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:26.7887549Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:29.7384359Z</t>
+  </si>
+  <si>
+    <t>You could speak more freely. And a bit less text on the slides otherwise good presentation</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:29.7384778Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:31.5353736Z</t>
+  </si>
+  <si>
+    <t>Nice slides and confident presentation</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:31.5354150Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:32.6744121Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:32.6744575Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:33.4484974Z</t>
+  </si>
+  <si>
+    <t>Great information, however presentation felt too rehearsed and monotonous.</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:33.4485363Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:33.6387960Z</t>
+  </si>
+  <si>
+    <t>Great presentation, well spoken and knew your stuff not reading from the screen!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:33.6388422Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:34.4818852Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:34.4819492Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:35.1282530Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:35.1282939Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:36.6922298Z</t>
+  </si>
+  <si>
+    <t>Very good presentiation, nice slides</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:36.6922718Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:38.1197394Z</t>
+  </si>
+  <si>
+    <t>very nice slides and great presentation style. You spoke calm and the message was clear</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:38.1197872Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:40.3465778Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good Presentation </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:40.3466176Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:44.0105091Z</t>
+  </si>
+  <si>
+    <t>Great presentation, however could have been slightly more engaging regarding the style</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:44.0105500Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:52.6752854Z</t>
+  </si>
+  <si>
+    <t>Arda	Aydin</t>
+  </si>
+  <si>
+    <t>interesting presentation!!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:52.6753640Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:54.9649975Z</t>
+  </si>
+  <si>
+    <t>great job</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:15:54.9650393Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:07.6358891Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:07.6359411Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:14.8574761Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:14.8575171Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:15.4251135Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good presentation, questions were well answered. Maybe the presenter could have been more entertaining </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:15.4251913Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:20.2641145Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">good slides and clear explanation </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:20.2641565Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:57.2397852Z</t>
+  </si>
+  <si>
+    <t>Great explanation of the topic</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:57.2398603Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:58.9803978Z</t>
+  </si>
+  <si>
+    <t>great slides and breakdown of the topic</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:16:58.9804382Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:18:08.3418408Z</t>
+  </si>
+  <si>
+    <t>very nice slides</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:18:08.3418826Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:18:24.4492316Z</t>
+  </si>
+  <si>
+    <t>speak slower, otherwise good</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:18:24.4492947Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:19:17.2511977Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slides were too heavy so it was a bit hard to follow the presentation </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:19:17.2512398Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:19:25.3522129Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">too quick and difficult to follow what you were saying </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:19:25.3523047Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:19:28.9461634Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:19:28.9462069Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:19:50.0172447Z</t>
+  </si>
+  <si>
+    <t>good, could speak a bit calmer</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:19:50.0173169Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:20.4048636Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:20.4049108Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:20.8870383Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I like the slides style, your speech it confident, yet to fast, take your time. You spoke freely </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:20.8871170Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:21.5122555Z</t>
+  </si>
+  <si>
+    <t>nice passion, chaotic slides</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:21.5122949Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:21.8824736Z</t>
+  </si>
+  <si>
+    <t>A slightly too fast but great presentation however.</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:21.8825125Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:24.6674145Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:24.6674578Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:27.0213525Z</t>
+  </si>
+  <si>
+    <t>I loved the passion, however presentation felt too chaotic and unorganized</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:27.0213965Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:28.2916232Z</t>
+  </si>
+  <si>
+    <t>very good presentation, the topic was explained very well with the olat questions also</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:28.2916635Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:28.5104696Z</t>
+  </si>
+  <si>
+    <t>Nice designed slides. Spoke a bit too fast.</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:28.5105099Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:29.3765612Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:29.3766018Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:33.8278474Z</t>
+  </si>
+  <si>
+    <t>Talk a bit slow, but great presentation, thank you!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:33.8278865Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:34.3294115Z</t>
+  </si>
+  <si>
+    <t>Slow down speach a little but very good</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:34.3294619Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:35.3754885Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good that you spoke freely and have a lot of knowledge on the subject. </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:35.3755484Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:39.1597464Z</t>
+  </si>
+  <si>
+    <t>Good Job</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:39.1598189Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:39.2310510Z</t>
+  </si>
+  <si>
+    <t>Very good and interesting topic</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:39.2311129Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:41.2702003Z</t>
+  </si>
+  <si>
+    <t>good slides and freely spoken</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:41.2702725Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:45.7227994Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:45.7228438Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:47.2929759Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good eye contact and confidence when presenting. Well done! </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:47.2930168Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:49.7306845Z</t>
+  </si>
+  <si>
+    <t>great presentation - well explained!</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:49.7307253Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:52.7387411Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:52.7388199Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:56.2402143Z</t>
+  </si>
+  <si>
+    <t>Bit too fast but overall interesting content</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:56.2402639Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:57.2809728Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tkan you for your presentation. </t>
+  </si>
+  <si>
+    <t>2026-04-27T12:20:57.2810148Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:21:00.7362775Z</t>
+  </si>
+  <si>
+    <t>You were really motivated but maybe a little bit too nervous</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:21:00.7363485Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:21:09.6302726Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:21:09.6303173Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:21:24.1659025Z</t>
+  </si>
+  <si>
+    <t>nice presentaion</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:21:24.1659440Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:21:37.2476887Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:21:37.2477357Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:25:50.2300048Z</t>
+  </si>
+  <si>
+    <t>Really good eye contact, good job speaking naturally not just reading off a script</t>
+  </si>
+  <si>
+    <t>2026-04-27T12:25:50.2300782Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T13:06:35.7715767Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T13:06:35.7716370Z</t>
+  </si>
+  <si>
+    <t>2026-04-27T13:07:47.3657719Z</t>
+  </si>
+  <si>
+    <t>Great presentation on an interesting topic!</t>
+  </si>
+  <si>
+    <t>2026-04-27T13:07:47.3658144Z</t>
+  </si>
+  <si>
+    <t>2026-04-29T09:23:41.3123130Z</t>
+  </si>
+  <si>
+    <t>The presentation was perfect!</t>
+  </si>
+  <si>
+    <t>2026-04-29T09:23:41.3123642Z</t>
+  </si>
+  <si>
+    <t>2026-04-29T09:24:10.1242336Z</t>
+  </si>
+  <si>
+    <t>2026-04-29T09:24:10.1242778Z</t>
+  </si>
+  <si>
+    <t>2026-04-29T09:24:50.0374218Z</t>
+  </si>
+  <si>
+    <t>2026-04-29T09:24:50.0374940Z</t>
+  </si>
+  <si>
+    <t>2026-04-30T12:50:55.5800170Z</t>
+  </si>
+  <si>
+    <t>Nice that you out data</t>
+  </si>
+  <si>
+    <t>2026-04-30T12:50:55.5800662Z</t>
+  </si>
+  <si>
+    <t>2026-04-30T12:53:34.6844581Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing more design or images </t>
+  </si>
+  <si>
+    <t>2026-04-30T12:53:34.6845397Z</t>
+  </si>
+  <si>
+    <t>2026-04-30T12:55:56.2698348Z</t>
+  </si>
+  <si>
+    <t>Good simple visuale but maybe too mich written</t>
+  </si>
+  <si>
+    <t>2026-04-30T12:55:56.2698758Z</t>
   </si>
 </sst>
 </file>
@@ -13645,8 +14608,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N1711" totalsRowShown="0">
-  <autoFilter ref="A1:N1711" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="responses" displayName="responses" ref="A1:N1826" totalsRowShown="0">
+  <autoFilter ref="A1:N1826" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Responseid" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SubmittedAt"/>
@@ -13964,7 +14927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1711"/>
+  <dimension ref="A1:N1826"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="14" width="20" bestFit="1" customWidth="1"/>
@@ -89033,7 +89996,7 @@
       </c>
     </row>
     <row r="1707" spans="1:14">
-      <c r="A1707" s="5">
+      <c r="A1707">
         <v>1711</v>
       </c>
       <c r="B1707" s="1" t="s">
@@ -89077,7 +90040,7 @@
       </c>
     </row>
     <row r="1708" spans="1:14">
-      <c r="A1708" s="5">
+      <c r="A1708">
         <v>1712</v>
       </c>
       <c r="B1708" s="1" t="s">
@@ -89121,7 +90084,7 @@
       </c>
     </row>
     <row r="1709" spans="1:14">
-      <c r="A1709" s="5">
+      <c r="A1709">
         <v>1713</v>
       </c>
       <c r="B1709" s="1" t="s">
@@ -89165,7 +90128,7 @@
       </c>
     </row>
     <row r="1710" spans="1:14">
-      <c r="A1710" s="5">
+      <c r="A1710">
         <v>1714</v>
       </c>
       <c r="B1710" s="1" t="s">
@@ -89209,7 +90172,7 @@
       </c>
     </row>
     <row r="1711" spans="1:14">
-      <c r="A1711" s="5">
+      <c r="A1711">
         <v>1715</v>
       </c>
       <c r="B1711" s="1" t="s">
@@ -89250,6 +90213,5066 @@
       </c>
       <c r="N1711" s="4" t="s">
         <v>4501</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:14">
+      <c r="A1712">
+        <v>1716</v>
+      </c>
+      <c r="B1712" s="1" t="s">
+        <v>4502</v>
+      </c>
+      <c r="C1712" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1712" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1712" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1712" s="3" t="s">
+        <v>4504</v>
+      </c>
+      <c r="N1712" s="4" t="s">
+        <v>4505</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:14">
+      <c r="A1713">
+        <v>1717</v>
+      </c>
+      <c r="B1713" s="1" t="s">
+        <v>4506</v>
+      </c>
+      <c r="C1713" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1713" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1713" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1713" s="3" t="s">
+        <v>4507</v>
+      </c>
+      <c r="N1713" s="4" t="s">
+        <v>4508</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:14">
+      <c r="A1714">
+        <v>1718</v>
+      </c>
+      <c r="B1714" s="1" t="s">
+        <v>4509</v>
+      </c>
+      <c r="C1714" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1714" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1714" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1714" s="3" t="s">
+        <v>4510</v>
+      </c>
+      <c r="N1714" s="4" t="s">
+        <v>4511</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:14">
+      <c r="A1715">
+        <v>1719</v>
+      </c>
+      <c r="B1715" s="1" t="s">
+        <v>4512</v>
+      </c>
+      <c r="C1715" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1715" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1715" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1715" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1715" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1715" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1715" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1715" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1715" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1715" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1715" s="3" t="s">
+        <v>4513</v>
+      </c>
+      <c r="N1715" s="4" t="s">
+        <v>4514</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:14">
+      <c r="A1716">
+        <v>1720</v>
+      </c>
+      <c r="B1716" s="1" t="s">
+        <v>4515</v>
+      </c>
+      <c r="C1716" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1716" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1716" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1716" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1716" s="3" t="s">
+        <v>4516</v>
+      </c>
+      <c r="N1716" s="4" t="s">
+        <v>4517</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:14">
+      <c r="A1717">
+        <v>1721</v>
+      </c>
+      <c r="B1717" s="1" t="s">
+        <v>4518</v>
+      </c>
+      <c r="C1717" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1717" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1717" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1717" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1717" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1717" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1717" s="3" t="s">
+        <v>4519</v>
+      </c>
+      <c r="N1717" s="4" t="s">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:14">
+      <c r="A1718">
+        <v>1723</v>
+      </c>
+      <c r="B1718" s="1" t="s">
+        <v>4521</v>
+      </c>
+      <c r="C1718" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1718" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1718" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1718" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1718" s="3" t="s">
+        <v>4522</v>
+      </c>
+      <c r="N1718" s="4" t="s">
+        <v>4523</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:14">
+      <c r="A1719">
+        <v>1722</v>
+      </c>
+      <c r="B1719" s="1" t="s">
+        <v>4524</v>
+      </c>
+      <c r="C1719" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1719" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1719" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1719" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1719" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1719" s="3" t="s">
+        <v>4525</v>
+      </c>
+      <c r="N1719" s="4" t="s">
+        <v>4526</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:14">
+      <c r="A1720">
+        <v>1724</v>
+      </c>
+      <c r="B1720" s="1" t="s">
+        <v>4527</v>
+      </c>
+      <c r="C1720" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1720" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E1720" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1720" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1720" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1720" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1720" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1720" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1720" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1720" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1720" s="3" t="s">
+        <v>4528</v>
+      </c>
+      <c r="N1720" s="4" t="s">
+        <v>4529</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:14">
+      <c r="A1721">
+        <v>1725</v>
+      </c>
+      <c r="B1721" s="1" t="s">
+        <v>4530</v>
+      </c>
+      <c r="C1721" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1721" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1721" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1721" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1721" s="3" t="s">
+        <v>4531</v>
+      </c>
+      <c r="N1721" s="4" t="s">
+        <v>4532</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:14">
+      <c r="A1722">
+        <v>1726</v>
+      </c>
+      <c r="B1722" s="1" t="s">
+        <v>4533</v>
+      </c>
+      <c r="C1722" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1722" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1722" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1722" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1722" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1722" s="3" t="s">
+        <v>4534</v>
+      </c>
+      <c r="N1722" s="4" t="s">
+        <v>4535</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:14">
+      <c r="A1723">
+        <v>1727</v>
+      </c>
+      <c r="B1723" s="1" t="s">
+        <v>4536</v>
+      </c>
+      <c r="C1723" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1723" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1723" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1723" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1723" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N1723" s="4" t="s">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:14">
+      <c r="A1724">
+        <v>1728</v>
+      </c>
+      <c r="B1724" s="1" t="s">
+        <v>4538</v>
+      </c>
+      <c r="C1724" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1724" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1724" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1724" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1724" s="3" t="s">
+        <v>4539</v>
+      </c>
+      <c r="N1724" s="4" t="s">
+        <v>4540</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:14">
+      <c r="A1725">
+        <v>1729</v>
+      </c>
+      <c r="B1725" s="1" t="s">
+        <v>4541</v>
+      </c>
+      <c r="C1725" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1725" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1725" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1725" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1725" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1725" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1725" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1725" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="N1725" s="4" t="s">
+        <v>4542</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:14">
+      <c r="A1726">
+        <v>1730</v>
+      </c>
+      <c r="B1726" s="1" t="s">
+        <v>4543</v>
+      </c>
+      <c r="C1726" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1726" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1726" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1726" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1726" s="3" t="s">
+        <v>4544</v>
+      </c>
+      <c r="N1726" s="4" t="s">
+        <v>4545</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:14">
+      <c r="A1727">
+        <v>1731</v>
+      </c>
+      <c r="B1727" s="1" t="s">
+        <v>4546</v>
+      </c>
+      <c r="C1727" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1727" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1727" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1727" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1727" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1727" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1727" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1727" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1727" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1727" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1727" s="3" t="s">
+        <v>4547</v>
+      </c>
+      <c r="N1727" s="4" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:14">
+      <c r="A1728">
+        <v>1732</v>
+      </c>
+      <c r="B1728" s="1" t="s">
+        <v>4549</v>
+      </c>
+      <c r="C1728" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1728" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1728" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1728" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1728" s="3" t="s">
+        <v>4550</v>
+      </c>
+      <c r="N1728" s="4" t="s">
+        <v>4551</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:14">
+      <c r="A1729">
+        <v>1733</v>
+      </c>
+      <c r="B1729" s="1" t="s">
+        <v>4552</v>
+      </c>
+      <c r="C1729" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1729" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1729" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1729" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1729" s="3" t="s">
+        <v>4553</v>
+      </c>
+      <c r="N1729" s="4" t="s">
+        <v>4554</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:14">
+      <c r="A1730">
+        <v>1734</v>
+      </c>
+      <c r="B1730" s="1" t="s">
+        <v>4555</v>
+      </c>
+      <c r="C1730" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1730" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1730" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1730" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1730" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1730" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1730" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1730" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1730" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1730" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1730" s="3" t="s">
+        <v>4556</v>
+      </c>
+      <c r="N1730" s="4" t="s">
+        <v>4557</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:14">
+      <c r="A1731">
+        <v>1735</v>
+      </c>
+      <c r="B1731" s="1" t="s">
+        <v>4558</v>
+      </c>
+      <c r="C1731" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1731" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1731" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1731" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1731" s="3" t="s">
+        <v>4559</v>
+      </c>
+      <c r="N1731" s="4" t="s">
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:14">
+      <c r="A1732">
+        <v>1736</v>
+      </c>
+      <c r="B1732" s="1" t="s">
+        <v>4561</v>
+      </c>
+      <c r="C1732" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1732" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1732" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1732" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1732" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1732" s="3" t="s">
+        <v>4562</v>
+      </c>
+      <c r="N1732" s="4" t="s">
+        <v>4563</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:14">
+      <c r="A1733">
+        <v>1737</v>
+      </c>
+      <c r="B1733" s="1" t="s">
+        <v>4564</v>
+      </c>
+      <c r="C1733" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1733" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E1733" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1733" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1733" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1733" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1733" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1733" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1733" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1733" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1733" s="3" t="s">
+        <v>4565</v>
+      </c>
+      <c r="N1733" s="4" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:14">
+      <c r="A1734">
+        <v>1738</v>
+      </c>
+      <c r="B1734" s="1" t="s">
+        <v>4567</v>
+      </c>
+      <c r="C1734" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1734" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1734" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1734" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1734" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N1734" s="4" t="s">
+        <v>4568</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:14">
+      <c r="A1735">
+        <v>1739</v>
+      </c>
+      <c r="B1735" s="1" t="s">
+        <v>4569</v>
+      </c>
+      <c r="C1735" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1735" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1735" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1735" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1735" s="3" t="s">
+        <v>4570</v>
+      </c>
+      <c r="N1735" s="4" t="s">
+        <v>4571</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:14">
+      <c r="A1736">
+        <v>1740</v>
+      </c>
+      <c r="B1736" s="1" t="s">
+        <v>4572</v>
+      </c>
+      <c r="C1736" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1736" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1736" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1736" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1736" s="3" t="s">
+        <v>4573</v>
+      </c>
+      <c r="N1736" s="4" t="s">
+        <v>4574</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:14">
+      <c r="A1737">
+        <v>1741</v>
+      </c>
+      <c r="B1737" s="1" t="s">
+        <v>4575</v>
+      </c>
+      <c r="C1737" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1737" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1737" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1737" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1737" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1737" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1737" s="3" t="s">
+        <v>4576</v>
+      </c>
+      <c r="N1737" s="4" t="s">
+        <v>4577</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:14">
+      <c r="A1738">
+        <v>1742</v>
+      </c>
+      <c r="B1738" s="1" t="s">
+        <v>4578</v>
+      </c>
+      <c r="C1738" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1738" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1738" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1738" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1738" s="3" t="s">
+        <v>4579</v>
+      </c>
+      <c r="N1738" s="4" t="s">
+        <v>4580</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:14">
+      <c r="A1739">
+        <v>1743</v>
+      </c>
+      <c r="B1739" s="1" t="s">
+        <v>4581</v>
+      </c>
+      <c r="C1739" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D1739" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E1739" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1739" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1739" s="3" t="s">
+        <v>4582</v>
+      </c>
+      <c r="N1739" s="4" t="s">
+        <v>4583</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:14">
+      <c r="A1740">
+        <v>1744</v>
+      </c>
+      <c r="B1740" s="1" t="s">
+        <v>4584</v>
+      </c>
+      <c r="C1740" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1740" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1740" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1740" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1740" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1740" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1740" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1740" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1740" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1740" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1740" s="3" t="s">
+        <v>4513</v>
+      </c>
+      <c r="N1740" s="4" t="s">
+        <v>4585</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:14">
+      <c r="A1741">
+        <v>1745</v>
+      </c>
+      <c r="B1741" s="1" t="s">
+        <v>4586</v>
+      </c>
+      <c r="C1741" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1741" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1741" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1741" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1741" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N1741" s="4" t="s">
+        <v>4587</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:14">
+      <c r="A1742">
+        <v>1746</v>
+      </c>
+      <c r="B1742" s="1" t="s">
+        <v>4588</v>
+      </c>
+      <c r="C1742" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1742" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1742" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1742" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1742" s="3" t="s">
+        <v>4589</v>
+      </c>
+      <c r="N1742" s="4" t="s">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:14">
+      <c r="A1743">
+        <v>1747</v>
+      </c>
+      <c r="B1743" s="1" t="s">
+        <v>4591</v>
+      </c>
+      <c r="C1743" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1743" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1743" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1743" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1743" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1743" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1743" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1743" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1743" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1743" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1743" s="3" t="s">
+        <v>4593</v>
+      </c>
+      <c r="N1743" s="4" t="s">
+        <v>4594</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:14">
+      <c r="A1744">
+        <v>1748</v>
+      </c>
+      <c r="B1744" s="1" t="s">
+        <v>4595</v>
+      </c>
+      <c r="C1744" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D1744" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E1744" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1744" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1744" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1744" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1744" s="3" t="s">
+        <v>4596</v>
+      </c>
+      <c r="N1744" s="4" t="s">
+        <v>4597</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:14">
+      <c r="A1745">
+        <v>1749</v>
+      </c>
+      <c r="B1745" s="1" t="s">
+        <v>4598</v>
+      </c>
+      <c r="C1745" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1745" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1745" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1745" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1745" s="3" t="s">
+        <v>4599</v>
+      </c>
+      <c r="N1745" s="4" t="s">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:14">
+      <c r="A1746">
+        <v>1750</v>
+      </c>
+      <c r="B1746" s="1" t="s">
+        <v>4601</v>
+      </c>
+      <c r="C1746" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1746" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1746" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1746" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1746" s="3" t="s">
+        <v>4602</v>
+      </c>
+      <c r="N1746" s="4" t="s">
+        <v>4603</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:14">
+      <c r="A1747">
+        <v>1751</v>
+      </c>
+      <c r="B1747" s="1" t="s">
+        <v>4604</v>
+      </c>
+      <c r="C1747" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1747" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1747" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1747" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1747" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1747" s="3" t="s">
+        <v>4605</v>
+      </c>
+      <c r="N1747" s="4" t="s">
+        <v>4606</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:14">
+      <c r="A1748">
+        <v>1752</v>
+      </c>
+      <c r="B1748" s="1" t="s">
+        <v>4607</v>
+      </c>
+      <c r="C1748" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1748" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1748" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1748" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1748" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1748" s="3" t="s">
+        <v>4608</v>
+      </c>
+      <c r="N1748" s="4" t="s">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:14">
+      <c r="A1749">
+        <v>1753</v>
+      </c>
+      <c r="B1749" s="1" t="s">
+        <v>4610</v>
+      </c>
+      <c r="C1749" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1749" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1749" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1749" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1749" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1749" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1749" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1749" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1749" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1749" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1749" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N1749" s="4" t="s">
+        <v>4611</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:14">
+      <c r="A1750">
+        <v>1754</v>
+      </c>
+      <c r="B1750" s="1" t="s">
+        <v>4612</v>
+      </c>
+      <c r="C1750" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1750" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1750" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1750" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1750" s="3" t="s">
+        <v>4613</v>
+      </c>
+      <c r="N1750" s="4" t="s">
+        <v>4614</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:14">
+      <c r="A1751">
+        <v>1755</v>
+      </c>
+      <c r="B1751" s="1" t="s">
+        <v>4615</v>
+      </c>
+      <c r="C1751" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1751" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1751" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1751" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1751" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1751" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1751" s="3" t="s">
+        <v>4616</v>
+      </c>
+      <c r="N1751" s="4" t="s">
+        <v>4617</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:14">
+      <c r="A1752">
+        <v>1756</v>
+      </c>
+      <c r="B1752" s="1" t="s">
+        <v>4618</v>
+      </c>
+      <c r="C1752" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1752" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1752" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1752" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1752" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1752" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1752" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1752" s="3" t="s">
+        <v>4619</v>
+      </c>
+      <c r="N1752" s="4" t="s">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:14">
+      <c r="A1753">
+        <v>1757</v>
+      </c>
+      <c r="B1753" s="1" t="s">
+        <v>4621</v>
+      </c>
+      <c r="C1753" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1753" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1753" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1753" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1753" s="3" t="s">
+        <v>4622</v>
+      </c>
+      <c r="N1753" s="4" t="s">
+        <v>4623</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:14">
+      <c r="A1754">
+        <v>1758</v>
+      </c>
+      <c r="B1754" s="1" t="s">
+        <v>4624</v>
+      </c>
+      <c r="C1754" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1754" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1754" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1754" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1754" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1754" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1754" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1754" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1754" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1754" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1754" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="N1754" s="4" t="s">
+        <v>4625</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:14">
+      <c r="A1755">
+        <v>1759</v>
+      </c>
+      <c r="B1755" s="1" t="s">
+        <v>4626</v>
+      </c>
+      <c r="C1755" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1755" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1755" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1755" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1755" s="3" t="s">
+        <v>4627</v>
+      </c>
+      <c r="N1755" s="4" t="s">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:14">
+      <c r="A1756">
+        <v>1760</v>
+      </c>
+      <c r="B1756" s="1" t="s">
+        <v>4629</v>
+      </c>
+      <c r="C1756" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1756" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1756" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1756" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1756" s="3" t="s">
+        <v>4630</v>
+      </c>
+      <c r="N1756" s="4" t="s">
+        <v>4631</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:14">
+      <c r="A1757">
+        <v>1761</v>
+      </c>
+      <c r="B1757" s="1" t="s">
+        <v>4632</v>
+      </c>
+      <c r="C1757" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1757" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1757" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1757" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1757" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1757" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1757" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1757" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1757" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1757" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1757" s="3" t="s">
+        <v>4633</v>
+      </c>
+      <c r="N1757" s="4" t="s">
+        <v>4634</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:14">
+      <c r="A1758">
+        <v>1762</v>
+      </c>
+      <c r="B1758" s="1" t="s">
+        <v>4635</v>
+      </c>
+      <c r="C1758" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1758" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1758" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1758" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1758" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1758" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1758" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1758" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1758" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1758" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1758" s="3" t="s">
+        <v>4636</v>
+      </c>
+      <c r="N1758" s="4" t="s">
+        <v>4637</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:14">
+      <c r="A1759">
+        <v>1763</v>
+      </c>
+      <c r="B1759" s="1" t="s">
+        <v>4638</v>
+      </c>
+      <c r="C1759" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1759" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E1759" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1759" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1759" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1759" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1759" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1759" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1759" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1759" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1759" s="3" t="s">
+        <v>4639</v>
+      </c>
+      <c r="N1759" s="4" t="s">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:14">
+      <c r="A1760">
+        <v>1764</v>
+      </c>
+      <c r="B1760" s="1" t="s">
+        <v>4641</v>
+      </c>
+      <c r="C1760" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1760" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1760" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1760" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1760" s="3" t="s">
+        <v>2843</v>
+      </c>
+      <c r="N1760" s="4" t="s">
+        <v>4642</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:14">
+      <c r="A1761">
+        <v>1765</v>
+      </c>
+      <c r="B1761" s="1" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C1761" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1761" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1761" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1761" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1761" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1761" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1761" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1761" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="N1761" s="4" t="s">
+        <v>4644</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:14">
+      <c r="A1762">
+        <v>1766</v>
+      </c>
+      <c r="B1762" s="1" t="s">
+        <v>4645</v>
+      </c>
+      <c r="C1762" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1762" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1762" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1762" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1762" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1762" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1762" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1762" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1762" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1762" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1762" s="3" t="s">
+        <v>4646</v>
+      </c>
+      <c r="N1762" s="4" t="s">
+        <v>4647</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:14">
+      <c r="A1763">
+        <v>1767</v>
+      </c>
+      <c r="B1763" s="1" t="s">
+        <v>4648</v>
+      </c>
+      <c r="C1763" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1763" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1763" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1763" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1763" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1763" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1763" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1763" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1763" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="N1763" s="4" t="s">
+        <v>4649</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:14">
+      <c r="A1764">
+        <v>1768</v>
+      </c>
+      <c r="B1764" s="1" t="s">
+        <v>4650</v>
+      </c>
+      <c r="C1764" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1764" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1764" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1764" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1764" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1764" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1764" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1764" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1764" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1764" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1764" s="3" t="s">
+        <v>4651</v>
+      </c>
+      <c r="N1764" s="4" t="s">
+        <v>4652</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:14">
+      <c r="A1765">
+        <v>1769</v>
+      </c>
+      <c r="B1765" s="1" t="s">
+        <v>4653</v>
+      </c>
+      <c r="C1765" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1765" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1765" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1765" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1765" s="3" t="s">
+        <v>4654</v>
+      </c>
+      <c r="N1765" s="4" t="s">
+        <v>4655</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:14">
+      <c r="A1766">
+        <v>1770</v>
+      </c>
+      <c r="B1766" s="1" t="s">
+        <v>4656</v>
+      </c>
+      <c r="C1766" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1766" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1766" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1766" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1766" s="3" t="s">
+        <v>4657</v>
+      </c>
+      <c r="N1766" s="4" t="s">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:14">
+      <c r="A1767">
+        <v>1771</v>
+      </c>
+      <c r="B1767" s="1" t="s">
+        <v>4659</v>
+      </c>
+      <c r="C1767" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1767" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1767" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1767" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1767" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="N1767" s="4" t="s">
+        <v>4660</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:14">
+      <c r="A1768">
+        <v>1772</v>
+      </c>
+      <c r="B1768" s="1" t="s">
+        <v>4661</v>
+      </c>
+      <c r="C1768" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1768" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1768" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1768" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1768" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1768" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1768" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1768" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1768" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1768" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1768" s="3" t="s">
+        <v>4662</v>
+      </c>
+      <c r="N1768" s="4" t="s">
+        <v>4663</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:14">
+      <c r="A1769">
+        <v>1773</v>
+      </c>
+      <c r="B1769" s="1" t="s">
+        <v>4664</v>
+      </c>
+      <c r="C1769" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1769" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1769" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1769" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1769" s="3" t="s">
+        <v>4665</v>
+      </c>
+      <c r="N1769" s="4" t="s">
+        <v>4666</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:14">
+      <c r="A1770">
+        <v>1774</v>
+      </c>
+      <c r="B1770" s="1" t="s">
+        <v>4667</v>
+      </c>
+      <c r="C1770" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D1770" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E1770" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1770" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1770" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1770" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1770" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1770" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1770" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1770" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1770" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1770" s="4" t="s">
+        <v>4668</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:14">
+      <c r="A1771">
+        <v>1775</v>
+      </c>
+      <c r="B1771" s="1" t="s">
+        <v>4669</v>
+      </c>
+      <c r="C1771" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1771" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1771" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1771" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1771" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1771" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1771" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1771" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1771" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1771" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1771" s="3" t="s">
+        <v>4670</v>
+      </c>
+      <c r="N1771" s="4" t="s">
+        <v>4671</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:14">
+      <c r="A1772">
+        <v>1776</v>
+      </c>
+      <c r="B1772" s="1" t="s">
+        <v>4672</v>
+      </c>
+      <c r="C1772" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1772" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1772" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1772" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1772" s="3" t="s">
+        <v>4673</v>
+      </c>
+      <c r="N1772" s="4" t="s">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:14">
+      <c r="A1773">
+        <v>1777</v>
+      </c>
+      <c r="B1773" s="1" t="s">
+        <v>4675</v>
+      </c>
+      <c r="C1773" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1773" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1773" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1773" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1773" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1773" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1773" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1773" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1773" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1773" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1773" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N1773" s="4" t="s">
+        <v>4676</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:14">
+      <c r="A1774">
+        <v>1778</v>
+      </c>
+      <c r="B1774" s="1" t="s">
+        <v>4677</v>
+      </c>
+      <c r="C1774" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1774" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1774" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1774" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1774" s="3" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N1774" s="4" t="s">
+        <v>4678</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:14">
+      <c r="A1775">
+        <v>1779</v>
+      </c>
+      <c r="B1775" s="1" t="s">
+        <v>4679</v>
+      </c>
+      <c r="C1775" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D1775" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E1775" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1775" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1775" s="3" t="s">
+        <v>4680</v>
+      </c>
+      <c r="N1775" s="4" t="s">
+        <v>4681</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:14">
+      <c r="A1776">
+        <v>1780</v>
+      </c>
+      <c r="B1776" s="1" t="s">
+        <v>4682</v>
+      </c>
+      <c r="C1776" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1776" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1776" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1776" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1776" s="3" t="s">
+        <v>4683</v>
+      </c>
+      <c r="N1776" s="4" t="s">
+        <v>4684</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:14">
+      <c r="A1777">
+        <v>1781</v>
+      </c>
+      <c r="B1777" s="1" t="s">
+        <v>4685</v>
+      </c>
+      <c r="C1777" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1777" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1777" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1777" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1777" s="3" t="s">
+        <v>4686</v>
+      </c>
+      <c r="N1777" s="4" t="s">
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:14">
+      <c r="A1778">
+        <v>1782</v>
+      </c>
+      <c r="B1778" s="1" t="s">
+        <v>4688</v>
+      </c>
+      <c r="C1778" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1778" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1778" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1778" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1778" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1778" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1778" s="3" t="s">
+        <v>4689</v>
+      </c>
+      <c r="N1778" s="4" t="s">
+        <v>4690</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:14">
+      <c r="A1779">
+        <v>1783</v>
+      </c>
+      <c r="B1779" s="1" t="s">
+        <v>4691</v>
+      </c>
+      <c r="C1779" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1779" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1779" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1779" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1779" s="3" t="s">
+        <v>4693</v>
+      </c>
+      <c r="N1779" s="4" t="s">
+        <v>4694</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:14">
+      <c r="A1780">
+        <v>1784</v>
+      </c>
+      <c r="B1780" s="1" t="s">
+        <v>4695</v>
+      </c>
+      <c r="C1780" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1780" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1780" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1780" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1780" s="3" t="s">
+        <v>4696</v>
+      </c>
+      <c r="N1780" s="4" t="s">
+        <v>4697</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:14">
+      <c r="A1781">
+        <v>1785</v>
+      </c>
+      <c r="B1781" s="1" t="s">
+        <v>4698</v>
+      </c>
+      <c r="C1781" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1781" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1781" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1781" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1781" s="3" t="s">
+        <v>4599</v>
+      </c>
+      <c r="N1781" s="4" t="s">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:14">
+      <c r="A1782">
+        <v>1786</v>
+      </c>
+      <c r="B1782" s="1" t="s">
+        <v>4700</v>
+      </c>
+      <c r="C1782" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1782" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E1782" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1782" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1782" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1782" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1782" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1782" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1782" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1782" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1782" s="3" t="s">
+        <v>4026</v>
+      </c>
+      <c r="N1782" s="4" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:14">
+      <c r="A1783">
+        <v>1787</v>
+      </c>
+      <c r="B1783" s="1" t="s">
+        <v>4702</v>
+      </c>
+      <c r="C1783" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1783" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1783" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1783" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1783" s="3" t="s">
+        <v>4703</v>
+      </c>
+      <c r="N1783" s="4" t="s">
+        <v>4704</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:14">
+      <c r="A1784">
+        <v>1788</v>
+      </c>
+      <c r="B1784" s="1" t="s">
+        <v>4705</v>
+      </c>
+      <c r="C1784" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1784" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1784" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1784" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1784" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1784" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1784" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1784" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1784" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1784" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1784" s="3" t="s">
+        <v>4706</v>
+      </c>
+      <c r="N1784" s="4" t="s">
+        <v>4707</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:14">
+      <c r="A1785">
+        <v>1789</v>
+      </c>
+      <c r="B1785" s="1" t="s">
+        <v>4708</v>
+      </c>
+      <c r="C1785" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1785" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1785" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1785" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1785" s="3" t="s">
+        <v>4709</v>
+      </c>
+      <c r="N1785" s="4" t="s">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:14">
+      <c r="A1786">
+        <v>1790</v>
+      </c>
+      <c r="B1786" s="1" t="s">
+        <v>4711</v>
+      </c>
+      <c r="C1786" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1786" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1786" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1786" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1786" s="3" t="s">
+        <v>4712</v>
+      </c>
+      <c r="N1786" s="4" t="s">
+        <v>4713</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:14">
+      <c r="A1787">
+        <v>1791</v>
+      </c>
+      <c r="B1787" s="1" t="s">
+        <v>4714</v>
+      </c>
+      <c r="C1787" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1787" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1787" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1787" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1787" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1787" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1787" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1787" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1787" s="3" t="s">
+        <v>4715</v>
+      </c>
+      <c r="N1787" s="4" t="s">
+        <v>4716</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:14">
+      <c r="A1788">
+        <v>1792</v>
+      </c>
+      <c r="B1788" s="1" t="s">
+        <v>4717</v>
+      </c>
+      <c r="C1788" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1788" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1788" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1788" s="3" t="s">
+        <v>4718</v>
+      </c>
+      <c r="N1788" s="4" t="s">
+        <v>4719</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:14">
+      <c r="A1789">
+        <v>1793</v>
+      </c>
+      <c r="B1789" s="1" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C1789" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1789" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1789" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1789" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1789" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1789" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1789" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1789" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1789" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1789" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1789" s="3" t="s">
+        <v>4721</v>
+      </c>
+      <c r="N1789" s="4" t="s">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:14">
+      <c r="A1790">
+        <v>1794</v>
+      </c>
+      <c r="B1790" s="1" t="s">
+        <v>4723</v>
+      </c>
+      <c r="C1790" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1790" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1790" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1790" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1790" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1790" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1790" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1790" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1790" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1790" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1790" s="3" t="s">
+        <v>4724</v>
+      </c>
+      <c r="N1790" s="4" t="s">
+        <v>4725</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:14">
+      <c r="A1791">
+        <v>1795</v>
+      </c>
+      <c r="B1791" s="1" t="s">
+        <v>4726</v>
+      </c>
+      <c r="C1791" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1791" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1791" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1791" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1791" s="3" t="s">
+        <v>4630</v>
+      </c>
+      <c r="N1791" s="4" t="s">
+        <v>4727</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:14">
+      <c r="A1792">
+        <v>1796</v>
+      </c>
+      <c r="B1792" s="1" t="s">
+        <v>4728</v>
+      </c>
+      <c r="C1792" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1792" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1792" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1792" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1792" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1792" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1792" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1792" s="3" t="s">
+        <v>4729</v>
+      </c>
+      <c r="N1792" s="4" t="s">
+        <v>4730</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:14">
+      <c r="A1793">
+        <v>1797</v>
+      </c>
+      <c r="B1793" s="1" t="s">
+        <v>4731</v>
+      </c>
+      <c r="C1793" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1793" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1793" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1793" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1793" s="3" t="s">
+        <v>1507</v>
+      </c>
+      <c r="N1793" s="4" t="s">
+        <v>4732</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:14">
+      <c r="A1794">
+        <v>1798</v>
+      </c>
+      <c r="B1794" s="1" t="s">
+        <v>4733</v>
+      </c>
+      <c r="C1794" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D1794" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E1794" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1794" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1794" s="3" t="s">
+        <v>4734</v>
+      </c>
+      <c r="N1794" s="4" t="s">
+        <v>4735</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:14">
+      <c r="A1795">
+        <v>1799</v>
+      </c>
+      <c r="B1795" s="1" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C1795" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1795" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1795" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1795" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1795" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1795" s="3" t="s">
+        <v>4737</v>
+      </c>
+      <c r="N1795" s="4" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:14">
+      <c r="A1796">
+        <v>1800</v>
+      </c>
+      <c r="B1796" s="1" t="s">
+        <v>4739</v>
+      </c>
+      <c r="C1796" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1796" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1796" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1796" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1796" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1796" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1796" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1796" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1796" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1796" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1796" s="3" t="s">
+        <v>4740</v>
+      </c>
+      <c r="N1796" s="4" t="s">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:14">
+      <c r="A1797">
+        <v>1801</v>
+      </c>
+      <c r="B1797" s="1" t="s">
+        <v>4742</v>
+      </c>
+      <c r="C1797" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1797" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1797" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1797" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1797" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1797" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1797" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1797" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1797" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1797" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1797" s="3" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N1797" s="4" t="s">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:14">
+      <c r="A1798">
+        <v>1802</v>
+      </c>
+      <c r="B1798" s="1" t="s">
+        <v>4744</v>
+      </c>
+      <c r="C1798" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1798" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1798" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1798" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1798" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1798" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1798" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1798" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1798" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1798" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1798" s="3" t="s">
+        <v>4745</v>
+      </c>
+      <c r="N1798" s="4" t="s">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:14">
+      <c r="A1799">
+        <v>1803</v>
+      </c>
+      <c r="B1799" s="1" t="s">
+        <v>4747</v>
+      </c>
+      <c r="C1799" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D1799" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E1799" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1799" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1799" s="3" t="s">
+        <v>4748</v>
+      </c>
+      <c r="N1799" s="4" t="s">
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:14">
+      <c r="A1800">
+        <v>1804</v>
+      </c>
+      <c r="B1800" s="1" t="s">
+        <v>4750</v>
+      </c>
+      <c r="C1800" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1800" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1800" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1800" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1800" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1800" s="3" t="s">
+        <v>4751</v>
+      </c>
+      <c r="N1800" s="4" t="s">
+        <v>4752</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:14">
+      <c r="A1801">
+        <v>1805</v>
+      </c>
+      <c r="B1801" s="1" t="s">
+        <v>4753</v>
+      </c>
+      <c r="C1801" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1801" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1801" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1801" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1801" s="3" t="s">
+        <v>2843</v>
+      </c>
+      <c r="N1801" s="4" t="s">
+        <v>4754</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:14">
+      <c r="A1802">
+        <v>1806</v>
+      </c>
+      <c r="B1802" s="1" t="s">
+        <v>4755</v>
+      </c>
+      <c r="C1802" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1802" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1802" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1802" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1802" s="3" t="s">
+        <v>4756</v>
+      </c>
+      <c r="N1802" s="4" t="s">
+        <v>4757</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:14">
+      <c r="A1803">
+        <v>1807</v>
+      </c>
+      <c r="B1803" s="1" t="s">
+        <v>4758</v>
+      </c>
+      <c r="C1803" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1803" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1803" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1803" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1803" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1803" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1803" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1803" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1803" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1803" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1803" s="3" t="s">
+        <v>4759</v>
+      </c>
+      <c r="N1803" s="4" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:14">
+      <c r="A1804">
+        <v>1808</v>
+      </c>
+      <c r="B1804" s="1" t="s">
+        <v>4761</v>
+      </c>
+      <c r="C1804" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1804" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1804" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1804" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1804" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1804" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1804" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1804" s="3" t="s">
+        <v>4762</v>
+      </c>
+      <c r="N1804" s="4" t="s">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:14">
+      <c r="A1805">
+        <v>1810</v>
+      </c>
+      <c r="B1805" s="1" t="s">
+        <v>4764</v>
+      </c>
+      <c r="C1805" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1805" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1805" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1805" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1805" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1805" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1805" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1805" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1805" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1805" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1805" s="3" t="s">
+        <v>4765</v>
+      </c>
+      <c r="N1805" s="4" t="s">
+        <v>4766</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:14">
+      <c r="A1806">
+        <v>1809</v>
+      </c>
+      <c r="B1806" s="1" t="s">
+        <v>4767</v>
+      </c>
+      <c r="C1806" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1806" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1806" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1806" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1806" s="3" t="s">
+        <v>4768</v>
+      </c>
+      <c r="N1806" s="4" t="s">
+        <v>4769</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:14">
+      <c r="A1807">
+        <v>1811</v>
+      </c>
+      <c r="B1807" s="1" t="s">
+        <v>4770</v>
+      </c>
+      <c r="C1807" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1807" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1807" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1807" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1807" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1807" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1807" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1807" s="3" t="s">
+        <v>4771</v>
+      </c>
+      <c r="N1807" s="4" t="s">
+        <v>4772</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:14">
+      <c r="A1808">
+        <v>1812</v>
+      </c>
+      <c r="B1808" s="1" t="s">
+        <v>4773</v>
+      </c>
+      <c r="C1808" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1808" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1808" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1808" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1808" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1808" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1808" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1808" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1808" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1808" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1808" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N1808" s="4" t="s">
+        <v>4774</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:14">
+      <c r="A1809">
+        <v>1813</v>
+      </c>
+      <c r="B1809" s="1" t="s">
+        <v>4775</v>
+      </c>
+      <c r="C1809" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1809" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1809" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1809" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1809" s="3" t="s">
+        <v>4776</v>
+      </c>
+      <c r="N1809" s="4" t="s">
+        <v>4777</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:14">
+      <c r="A1810">
+        <v>1814</v>
+      </c>
+      <c r="B1810" s="1" t="s">
+        <v>4778</v>
+      </c>
+      <c r="C1810" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1810" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1810" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1810" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1810" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1810" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1810" s="3" t="s">
+        <v>4779</v>
+      </c>
+      <c r="N1810" s="4" t="s">
+        <v>4780</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:14">
+      <c r="A1811">
+        <v>1815</v>
+      </c>
+      <c r="B1811" s="1" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C1811" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1811" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E1811" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1811" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1811" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1811" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1811" s="3" t="s">
+        <v>4026</v>
+      </c>
+      <c r="N1811" s="4" t="s">
+        <v>4782</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:14">
+      <c r="A1812">
+        <v>1816</v>
+      </c>
+      <c r="B1812" s="1" t="s">
+        <v>4783</v>
+      </c>
+      <c r="C1812" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D1812" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E1812" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1812" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1812" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1812" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1812" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1812" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1812" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1812" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1812" s="3" t="s">
+        <v>4784</v>
+      </c>
+      <c r="N1812" s="4" t="s">
+        <v>4785</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:14">
+      <c r="A1813">
+        <v>1817</v>
+      </c>
+      <c r="B1813" s="1" t="s">
+        <v>4786</v>
+      </c>
+      <c r="C1813" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1813" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1813" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1813" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1813" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1813" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1813" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1813" s="3" t="s">
+        <v>4787</v>
+      </c>
+      <c r="N1813" s="4" t="s">
+        <v>4788</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:14">
+      <c r="A1814">
+        <v>1818</v>
+      </c>
+      <c r="B1814" s="1" t="s">
+        <v>4789</v>
+      </c>
+      <c r="C1814" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1814" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1814" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1814" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1814" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1814" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1814" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1814" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1814" s="3" t="s">
+        <v>4790</v>
+      </c>
+      <c r="N1814" s="4" t="s">
+        <v>4791</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:14">
+      <c r="A1815">
+        <v>1819</v>
+      </c>
+      <c r="B1815" s="1" t="s">
+        <v>4792</v>
+      </c>
+      <c r="C1815" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1815" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1815" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1815" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1815" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1815" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1815" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N1815" s="4" t="s">
+        <v>4793</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:14">
+      <c r="A1816">
+        <v>1820</v>
+      </c>
+      <c r="B1816" s="1" t="s">
+        <v>4794</v>
+      </c>
+      <c r="C1816" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1816" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1816" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1816" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1816" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1816" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1816" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1816" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1816" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1816" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1816" s="3" t="s">
+        <v>4795</v>
+      </c>
+      <c r="N1816" s="4" t="s">
+        <v>4796</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:14">
+      <c r="A1817">
+        <v>1821</v>
+      </c>
+      <c r="B1817" s="1" t="s">
+        <v>4797</v>
+      </c>
+      <c r="C1817" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1817" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1817" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1817" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N1817" s="4" t="s">
+        <v>4798</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:14">
+      <c r="A1818">
+        <v>1822</v>
+      </c>
+      <c r="B1818" s="1" t="s">
+        <v>4799</v>
+      </c>
+      <c r="C1818" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1818" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1818" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1818" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1818" s="3" t="s">
+        <v>4800</v>
+      </c>
+      <c r="N1818" s="4" t="s">
+        <v>4801</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:14">
+      <c r="A1819">
+        <v>1823</v>
+      </c>
+      <c r="B1819" s="1" t="s">
+        <v>4802</v>
+      </c>
+      <c r="C1819" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1819" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1819" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1819" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1819" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1819" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1819" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1819" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1819" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1819" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1819" s="3" t="s">
+        <v>2931</v>
+      </c>
+      <c r="N1819" s="4" t="s">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:14">
+      <c r="A1820">
+        <v>1824</v>
+      </c>
+      <c r="B1820" s="1" t="s">
+        <v>4804</v>
+      </c>
+      <c r="C1820" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1820" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1820" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1820" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1820" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1820" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1820" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1820" s="3" t="s">
+        <v>4805</v>
+      </c>
+      <c r="N1820" s="4" t="s">
+        <v>4806</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:14">
+      <c r="A1821">
+        <v>1825</v>
+      </c>
+      <c r="B1821" s="1" t="s">
+        <v>4807</v>
+      </c>
+      <c r="C1821" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1821" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1821" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1821" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1821" s="3" t="s">
+        <v>4808</v>
+      </c>
+      <c r="N1821" s="4" t="s">
+        <v>4809</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:14">
+      <c r="A1822">
+        <v>1826</v>
+      </c>
+      <c r="B1822" s="1" t="s">
+        <v>4810</v>
+      </c>
+      <c r="C1822" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1822" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1822" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1822" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1822" s="3" t="s">
+        <v>4808</v>
+      </c>
+      <c r="N1822" s="4" t="s">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:14">
+      <c r="A1823">
+        <v>1827</v>
+      </c>
+      <c r="B1823" s="1" t="s">
+        <v>4812</v>
+      </c>
+      <c r="C1823" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1823" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1823" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1823" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1823" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1823" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1823" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1823" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1823" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1823" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1823" s="3" t="s">
+        <v>4808</v>
+      </c>
+      <c r="N1823" s="4" t="s">
+        <v>4813</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:14">
+      <c r="A1824" s="5">
+        <v>1828</v>
+      </c>
+      <c r="B1824" s="1" t="s">
+        <v>4814</v>
+      </c>
+      <c r="C1824" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1824" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1824" s="2" t="s">
+        <v>4503</v>
+      </c>
+      <c r="F1824" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1824" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1824" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1824" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1824" s="3" t="s">
+        <v>4815</v>
+      </c>
+      <c r="N1824" s="4" t="s">
+        <v>4816</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:14">
+      <c r="A1825" s="5">
+        <v>1829</v>
+      </c>
+      <c r="B1825" s="1" t="s">
+        <v>4817</v>
+      </c>
+      <c r="C1825" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1825" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1825" s="2" t="s">
+        <v>4592</v>
+      </c>
+      <c r="F1825" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1825" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1825" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1825" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1825" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1825" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1825" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1825" s="3" t="s">
+        <v>4818</v>
+      </c>
+      <c r="N1825" s="4" t="s">
+        <v>4819</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:14">
+      <c r="A1826" s="5">
+        <v>1830</v>
+      </c>
+      <c r="B1826" s="1" t="s">
+        <v>4820</v>
+      </c>
+      <c r="C1826" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1826" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1826" s="2" t="s">
+        <v>4692</v>
+      </c>
+      <c r="F1826" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1826" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1826" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1826" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1826" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1826" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1826" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1826" s="3" t="s">
+        <v>4821</v>
+      </c>
+      <c r="N1826" s="4" t="s">
+        <v>4822</v>
       </c>
     </row>
   </sheetData>
